--- a/research/traditional_assets/database/data/belgium/belgium_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_construction_supplies.xlsx
@@ -647,10 +647,10 @@
         <v>0.2054461615154536</v>
       </c>
       <c r="X2">
-        <v>0.09115411397108877</v>
+        <v>0.09113293315272061</v>
       </c>
       <c r="Y2">
-        <v>0.1142920475443649</v>
+        <v>0.114313228362733</v>
       </c>
       <c r="Z2">
         <v>1.218982938545635</v>
@@ -659,10 +659,10 @@
         <v>0.1551815634783099</v>
       </c>
       <c r="AB2">
-        <v>0.08143778119576159</v>
+        <v>0.08142165357652151</v>
       </c>
       <c r="AC2">
-        <v>0.07374378228254833</v>
+        <v>0.07375990990178841</v>
       </c>
       <c r="AD2">
         <v>969.9</v>
@@ -781,10 +781,10 @@
         <v>0.2054461615154536</v>
       </c>
       <c r="X3">
-        <v>0.09115411397108877</v>
+        <v>0.09113293315272061</v>
       </c>
       <c r="Y3">
-        <v>0.1142920475443649</v>
+        <v>0.114313228362733</v>
       </c>
       <c r="Z3">
         <v>1.218982938545635</v>
@@ -793,10 +793,10 @@
         <v>0.1551815634783099</v>
       </c>
       <c r="AB3">
-        <v>0.08143778119576159</v>
+        <v>0.08142165357652151</v>
       </c>
       <c r="AC3">
-        <v>0.07374378228254833</v>
+        <v>0.07375990990178841</v>
       </c>
       <c r="AD3">
         <v>969.9</v>
@@ -1133,49 +1133,49 @@
         <v>10.4756637168142</v>
       </c>
       <c r="F2">
-        <v>4.56128120814571</v>
+        <v>4.52851929269472</v>
       </c>
       <c r="G2">
         <v>1.60023098498598</v>
       </c>
       <c r="H2">
-        <v>2.68298960567563</v>
+        <v>2.81713908595941</v>
       </c>
       <c r="I2">
         <v>0.238574310030993</v>
       </c>
       <c r="J2">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="K2">
         <v>3095.5</v>
       </c>
       <c r="L2">
-        <v>2514.3804965353</v>
+        <v>2475.44530578231</v>
       </c>
       <c r="M2">
         <v>3842.2</v>
       </c>
       <c r="N2">
-        <v>3917.3404965353</v>
+        <v>3959.71330578231</v>
       </c>
       <c r="O2">
         <v>969.9</v>
       </c>
       <c r="P2">
-        <v>1626.16</v>
+        <v>1707.468</v>
       </c>
       <c r="Q2">
-        <v>0.0814377811957616</v>
+        <v>0.08142165357652149</v>
       </c>
       <c r="R2">
-        <v>0.07968271732878369</v>
+        <v>0.07870629611139519</v>
       </c>
       <c r="S2">
         <v>0.0504274624969006</v>
       </c>
       <c r="T2">
-        <v>0.0478774624969006</v>
+        <v>0.0459274624969006</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0911541139710888</v>
+        <v>0.0911329331527206</v>
       </c>
       <c r="X2">
-        <v>0.100886220550039</v>
+        <v>0.102442692866719</v>
       </c>
       <c r="Y2">
         <v>0.88362324529063</v>
       </c>
       <c r="Z2">
-        <v>1.07323152656558</v>
+        <v>1.10407151296114</v>
       </c>
       <c r="AA2">
         <v>969.9</v>
@@ -1230,7 +1230,7 @@
         <v>3095.5</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963755</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08252414703335935</v>
+        <v>0.08250699649463347</v>
       </c>
       <c r="C2">
-        <v>4020.316273191411</v>
+        <v>4020.357562425989</v>
       </c>
       <c r="D2">
-        <v>3797.116273191411</v>
+        <v>3797.157562425989</v>
       </c>
       <c r="E2">
         <v>-969.9</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08252414703335935</v>
+        <v>0.08250699649463347</v>
       </c>
       <c r="T2">
         <v>0.7154876843770529</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08240661129074495</v>
+        <v>0.08237900362836591</v>
       </c>
       <c r="C3">
-        <v>3984.488850665997</v>
+        <v>3984.960346585092</v>
       </c>
       <c r="D3">
-        <v>3801.942850665997</v>
+        <v>3802.414346585092</v>
       </c>
       <c r="E3">
         <v>-929.246</v>
@@ -1533,37 +1533,37 @@
         <v>473.5</v>
       </c>
       <c r="M3">
-        <v>2.343159013798661</v>
+        <v>2.286243413798661</v>
       </c>
       <c r="N3">
-        <v>471.1568409862014</v>
+        <v>471.2137565862013</v>
       </c>
       <c r="O3">
-        <v>117.7892102465503</v>
+        <v>117.8034391465503</v>
       </c>
       <c r="P3">
-        <v>353.367630739651</v>
+        <v>353.410317439651</v>
       </c>
       <c r="Q3">
-        <v>485.967630739651</v>
+        <v>486.010317439651</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08280236026846055</v>
+        <v>0.082785079801411</v>
       </c>
       <c r="T3">
         <v>0.7209080456223336</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>202.0776213699537</v>
+        <v>207.1083057657739</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08228907554813056</v>
+        <v>0.08225101076209833</v>
       </c>
       <c r="C4">
-        <v>3948.673714042763</v>
+        <v>3949.57770590389</v>
       </c>
       <c r="D4">
-        <v>3806.781714042763</v>
+        <v>3807.68570590389</v>
       </c>
       <c r="E4">
         <v>-888.592</v>
@@ -1615,37 +1615,37 @@
         <v>473.5</v>
       </c>
       <c r="M4">
-        <v>4.686318027597323</v>
+        <v>4.572486827597323</v>
       </c>
       <c r="N4">
-        <v>468.8136819724027</v>
+        <v>468.9275131724027</v>
       </c>
       <c r="O4">
-        <v>117.2034204931007</v>
+        <v>117.2318782931007</v>
       </c>
       <c r="P4">
-        <v>351.610261479302</v>
+        <v>351.695634879302</v>
       </c>
       <c r="Q4">
-        <v>484.210261479302</v>
+        <v>484.295634879302</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08308625132468628</v>
+        <v>0.08306883827771461</v>
       </c>
       <c r="T4">
         <v>0.726439026484865</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>101.0388106849769</v>
+        <v>103.554152882887</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08217153980551616</v>
+        <v>0.08212301789583075</v>
       </c>
       <c r="C5">
-        <v>3912.870910291558</v>
+        <v>3914.209701083998</v>
       </c>
       <c r="D5">
-        <v>3811.632910291558</v>
+        <v>3812.971701083999</v>
       </c>
       <c r="E5">
         <v>-847.938</v>
@@ -1697,37 +1697,37 @@
         <v>473.5</v>
       </c>
       <c r="M5">
-        <v>7.029477041395984</v>
+        <v>6.858730241395985</v>
       </c>
       <c r="N5">
-        <v>466.470522958604</v>
+        <v>466.641269758604</v>
       </c>
       <c r="O5">
-        <v>116.617630739651</v>
+        <v>116.660317439651</v>
       </c>
       <c r="P5">
-        <v>349.852892218953</v>
+        <v>349.980952318953</v>
       </c>
       <c r="Q5">
-        <v>482.452892218953</v>
+        <v>482.5809523189531</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.0833759958047517</v>
+        <v>0.08335844744425126</v>
       </c>
       <c r="T5">
         <v>0.7320840481899227</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>67.3592071233179</v>
+        <v>69.03610192192464</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08205400406290178</v>
+        <v>0.08199502502956317</v>
       </c>
       <c r="C6">
-        <v>3877.080486621962</v>
+        <v>3878.856393164574</v>
       </c>
       <c r="D6">
-        <v>3816.496486621963</v>
+        <v>3818.272393164575</v>
       </c>
       <c r="E6">
         <v>-807.284</v>
@@ -1779,37 +1779,37 @@
         <v>473.5</v>
       </c>
       <c r="M6">
-        <v>9.372636055194645</v>
+        <v>9.144973655194645</v>
       </c>
       <c r="N6">
-        <v>464.1273639448054</v>
+        <v>464.3550263448054</v>
       </c>
       <c r="O6">
-        <v>116.0318409862013</v>
+        <v>116.0887565862013</v>
       </c>
       <c r="P6">
-        <v>348.095522958604</v>
+        <v>348.266269758604</v>
       </c>
       <c r="Q6">
-        <v>480.695522958604</v>
+        <v>480.8662697586041</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08367177662815183</v>
+        <v>0.08365409013509077</v>
       </c>
       <c r="T6">
         <v>0.7378466745138358</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.51940534248843</v>
+        <v>51.77707644144348</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08193646832028738</v>
+        <v>0.08186703216329559</v>
       </c>
       <c r="C7">
-        <v>3841.302490484823</v>
+        <v>3843.51784352467</v>
       </c>
       <c r="D7">
-        <v>3821.372490484823</v>
+        <v>3823.58784352467</v>
       </c>
       <c r="E7">
         <v>-766.63</v>
@@ -1861,37 +1861,37 @@
         <v>473.5</v>
       </c>
       <c r="M7">
-        <v>11.71579506899331</v>
+        <v>11.43121706899331</v>
       </c>
       <c r="N7">
-        <v>461.7842049310067</v>
+        <v>462.0687829310067</v>
       </c>
       <c r="O7">
-        <v>115.4460512327517</v>
+        <v>115.5171957327517</v>
       </c>
       <c r="P7">
-        <v>346.338153698255</v>
+        <v>346.551587198255</v>
       </c>
       <c r="Q7">
-        <v>478.9381536982551</v>
+        <v>479.151587198255</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08397378441625511</v>
+        <v>0.08395595688257954</v>
       </c>
       <c r="T7">
         <v>0.7437306192866734</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.41552427399074</v>
+        <v>41.42166115315479</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08181893257767299</v>
+        <v>0.081739039297028</v>
       </c>
       <c r="C8">
-        <v>3805.536969573785</v>
+        <v>3808.194113885596</v>
       </c>
       <c r="D8">
-        <v>3826.260969573786</v>
+        <v>3828.918113885597</v>
       </c>
       <c r="E8">
         <v>-725.976</v>
@@ -1943,37 +1943,37 @@
         <v>473.5</v>
       </c>
       <c r="M8">
-        <v>14.05895408279197</v>
+        <v>13.71746048279197</v>
       </c>
       <c r="N8">
-        <v>459.441045917208</v>
+        <v>459.782539517208</v>
       </c>
       <c r="O8">
-        <v>114.860261479302</v>
+        <v>114.945634879302</v>
       </c>
       <c r="P8">
-        <v>344.580784437906</v>
+        <v>344.836904637906</v>
       </c>
       <c r="Q8">
-        <v>477.180784437906</v>
+        <v>477.436904637906</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08428221790197761</v>
+        <v>0.08426424632682337</v>
       </c>
       <c r="T8">
         <v>0.7497397543738267</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.67960356165895</v>
+        <v>34.51805096096232</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.0817013968350586</v>
+        <v>0.08161104643076043</v>
       </c>
       <c r="C9">
-        <v>3769.78397182686</v>
+        <v>3772.885266313316</v>
       </c>
       <c r="D9">
-        <v>3831.16197182686</v>
+        <v>3834.263266313316</v>
       </c>
       <c r="E9">
         <v>-685.3219999999999</v>
@@ -2025,37 +2025,37 @@
         <v>473.5</v>
       </c>
       <c r="M9">
-        <v>16.40211309659063</v>
+        <v>16.00370389659063</v>
       </c>
       <c r="N9">
-        <v>457.0978869034093</v>
+        <v>457.4962961034093</v>
       </c>
       <c r="O9">
-        <v>114.2744717258523</v>
+        <v>114.3740740258523</v>
       </c>
       <c r="P9">
-        <v>342.823415177557</v>
+        <v>343.122222077557</v>
       </c>
       <c r="Q9">
-        <v>475.423415177557</v>
+        <v>475.722222077557</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0845972843658877</v>
+        <v>0.0845791656515886</v>
       </c>
       <c r="T9">
         <v>0.7558781181725317</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.8682316242791</v>
+        <v>29.58690082368199</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08158386109244421</v>
+        <v>0.08148305356449284</v>
       </c>
       <c r="C10">
-        <v>3734.043545427984</v>
+        <v>3737.591363220854</v>
       </c>
       <c r="D10">
-        <v>3836.075545427984</v>
+        <v>3839.623363220854</v>
       </c>
       <c r="E10">
         <v>-644.6679999999999</v>
@@ -2107,37 +2107,37 @@
         <v>473.5</v>
       </c>
       <c r="M10">
-        <v>18.74527211038929</v>
+        <v>18.28994731038929</v>
       </c>
       <c r="N10">
-        <v>454.7547278896107</v>
+        <v>455.2100526896107</v>
       </c>
       <c r="O10">
-        <v>113.6886819724027</v>
+        <v>113.8025131724027</v>
       </c>
       <c r="P10">
-        <v>341.066045917208</v>
+        <v>341.4075395172081</v>
       </c>
       <c r="Q10">
-        <v>473.6660459172081</v>
+        <v>474.0075395172081</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08491920010075235</v>
+        <v>0.08490093104863131</v>
       </c>
       <c r="T10">
         <v>0.762149924662513</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.25970267124421</v>
+        <v>25.88853822072175</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08146632534982981</v>
+        <v>0.08135506069822528</v>
       </c>
       <c r="C11">
-        <v>3698.3157388086</v>
+        <v>3702.312467370719</v>
       </c>
       <c r="D11">
-        <v>3841.0017388086</v>
+        <v>3844.998467370719</v>
       </c>
       <c r="E11">
         <v>-604.014</v>
@@ -2189,37 +2189,37 @@
         <v>473.5</v>
       </c>
       <c r="M11">
-        <v>21.08843112418795</v>
+        <v>20.57619072418795</v>
       </c>
       <c r="N11">
-        <v>452.4115688758121</v>
+        <v>452.9238092758121</v>
       </c>
       <c r="O11">
-        <v>113.102892218953</v>
+        <v>113.230952318953</v>
       </c>
       <c r="P11">
-        <v>339.3086766568591</v>
+        <v>339.692856956859</v>
       </c>
       <c r="Q11">
-        <v>471.9086766568591</v>
+        <v>472.2928569568591</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08524819090671293</v>
+        <v>0.085229768212642</v>
       </c>
       <c r="T11">
         <v>0.7685595730533727</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.45306904110597</v>
+        <v>23.01203397397489</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08134878960721542</v>
+        <v>0.08122706783195768</v>
       </c>
       <c r="C12">
-        <v>3662.600600649249</v>
+        <v>3667.048641877365</v>
       </c>
       <c r="D12">
-        <v>3845.940600649249</v>
+        <v>3850.388641877365</v>
       </c>
       <c r="E12">
         <v>-563.3599999999999</v>
@@ -2271,37 +2271,37 @@
         <v>473.5</v>
       </c>
       <c r="M12">
-        <v>23.43159013798661</v>
+        <v>22.86243413798661</v>
       </c>
       <c r="N12">
-        <v>450.0684098620134</v>
+        <v>450.6375658620134</v>
       </c>
       <c r="O12">
-        <v>112.5171024655033</v>
+        <v>112.6593914655033</v>
       </c>
       <c r="P12">
-        <v>337.55130739651</v>
+        <v>337.97817439651</v>
       </c>
       <c r="Q12">
-        <v>470.15130739651</v>
+        <v>470.5781743965101</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08558449261947262</v>
+        <v>0.08556591286918626</v>
       </c>
       <c r="T12">
         <v>0.7751116580751406</v>
       </c>
       <c r="U12">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.20776213699537</v>
+        <v>20.71083057657739</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08123125386460103</v>
+        <v>0.08109907496569012</v>
       </c>
       <c r="C13">
-        <v>3626.898179881172</v>
+        <v>3631.799950209648</v>
       </c>
       <c r="D13">
-        <v>3850.892179881173</v>
+        <v>3855.793950209648</v>
       </c>
       <c r="E13">
         <v>-522.7059999999999</v>
@@ -2353,37 +2353,37 @@
         <v>473.5</v>
       </c>
       <c r="M13">
-        <v>25.77474915178528</v>
+        <v>25.14867755178528</v>
       </c>
       <c r="N13">
-        <v>447.7252508482147</v>
+        <v>448.3513224482147</v>
       </c>
       <c r="O13">
-        <v>111.9313127120537</v>
+        <v>112.0878306120537</v>
       </c>
       <c r="P13">
-        <v>335.793938136161</v>
+        <v>336.2634918361611</v>
       </c>
       <c r="Q13">
-        <v>468.3939381361611</v>
+        <v>468.8634918361611</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.0859283516740921</v>
+        <v>0.08590961133823714</v>
       </c>
       <c r="T13">
         <v>0.7818109809625663</v>
       </c>
       <c r="U13">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.37069285181397</v>
+        <v>18.82802779688854</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08111371812198664</v>
+        <v>0.08097108209942254</v>
       </c>
       <c r="C14">
-        <v>3591.20852568793</v>
+        <v>3596.566456193329</v>
       </c>
       <c r="D14">
-        <v>3855.856525687931</v>
+        <v>3861.214456193329</v>
       </c>
       <c r="E14">
         <v>-482.052</v>
@@ -2435,37 +2435,37 @@
         <v>473.5</v>
       </c>
       <c r="M14">
-        <v>28.11790816558393</v>
+        <v>27.43492096558394</v>
       </c>
       <c r="N14">
-        <v>445.3820918344161</v>
+        <v>446.065079034416</v>
       </c>
       <c r="O14">
-        <v>111.345522958604</v>
+        <v>111.516269758604</v>
       </c>
       <c r="P14">
-        <v>334.0365688758121</v>
+        <v>334.548809275812</v>
       </c>
       <c r="Q14">
-        <v>466.6365688758121</v>
+        <v>467.148809275812</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08628002570722565</v>
+        <v>0.08626112113613008</v>
       </c>
       <c r="T14">
         <v>0.7886625611883424</v>
       </c>
       <c r="U14">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.83980178082948</v>
+        <v>17.25902548048116</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08099618237937224</v>
+        <v>0.08084308923315496</v>
       </c>
       <c r="C15">
-        <v>3555.531687507029</v>
+        <v>3561.34822401358</v>
       </c>
       <c r="D15">
-        <v>3860.833687507029</v>
+        <v>3866.650224013581</v>
       </c>
       <c r="E15">
         <v>-441.3979999999999</v>
@@ -2517,37 +2517,37 @@
         <v>473.5</v>
       </c>
       <c r="M15">
-        <v>30.4610671793826</v>
+        <v>29.7211643793826</v>
       </c>
       <c r="N15">
-        <v>443.0389328206174</v>
+        <v>443.7788356206174</v>
       </c>
       <c r="O15">
-        <v>110.7597332051543</v>
+        <v>110.9447089051544</v>
       </c>
       <c r="P15">
-        <v>332.279199615463</v>
+        <v>332.8341267154631</v>
       </c>
       <c r="Q15">
-        <v>464.8791996154631</v>
+        <v>465.4341267154631</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.086639784200891</v>
+        <v>0.08662071161903205</v>
       </c>
       <c r="T15">
         <v>0.7956716490055157</v>
       </c>
       <c r="U15">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.54443241307336</v>
+        <v>15.93140813582876</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08087864663675785</v>
+        <v>0.08071509636688738</v>
       </c>
       <c r="C16">
-        <v>3519.867715031558</v>
+        <v>3526.145318217518</v>
       </c>
       <c r="D16">
-        <v>3865.823715031558</v>
+        <v>3872.101318217518</v>
       </c>
       <c r="E16">
         <v>-400.7439999999999</v>
@@ -2599,37 +2599,37 @@
         <v>473.5</v>
       </c>
       <c r="M16">
-        <v>32.80422619318126</v>
+        <v>32.00740779318127</v>
       </c>
       <c r="N16">
-        <v>440.6957738068187</v>
+        <v>441.4925922068188</v>
       </c>
       <c r="O16">
-        <v>110.1739434517047</v>
+        <v>110.3731480517047</v>
       </c>
       <c r="P16">
-        <v>330.521830355114</v>
+        <v>331.1194441551141</v>
       </c>
       <c r="Q16">
-        <v>463.1218303551141</v>
+        <v>463.7194441551141</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08700790917115322</v>
+        <v>0.08698866467130384</v>
       </c>
       <c r="T16">
         <v>0.8028437388649489</v>
       </c>
       <c r="U16">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.43411581213955</v>
+        <v>14.79345041184099</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08076111089414345</v>
+        <v>0.0805871035006198</v>
       </c>
       <c r="C17">
-        <v>3484.216658211851</v>
+        <v>3490.957803716763</v>
       </c>
       <c r="D17">
-        <v>3870.826658211851</v>
+        <v>3877.567803716763</v>
       </c>
       <c r="E17">
         <v>-360.09</v>
@@ -2681,37 +2681,37 @@
         <v>473.5</v>
       </c>
       <c r="M17">
-        <v>35.14738520697991</v>
+        <v>34.29365120697992</v>
       </c>
       <c r="N17">
-        <v>438.3526147930201</v>
+        <v>439.2063487930201</v>
       </c>
       <c r="O17">
-        <v>109.588153698255</v>
+        <v>109.801587198255</v>
       </c>
       <c r="P17">
-        <v>328.7644610947651</v>
+        <v>329.4047615947651</v>
       </c>
       <c r="Q17">
-        <v>461.3644610947651</v>
+        <v>462.0047615947651</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08738469590542161</v>
+        <v>0.08736527544245261</v>
       </c>
       <c r="T17">
         <v>0.8101845837798981</v>
       </c>
       <c r="U17">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.47184142466358</v>
+        <v>13.80722038438493</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08077557515152907</v>
+        <v>0.08045911063435222</v>
       </c>
       <c r="C18">
-        <v>3442.946284265847</v>
+        <v>3455.785745790007</v>
       </c>
       <c r="D18">
-        <v>3870.210284265847</v>
+        <v>3883.049745790007</v>
       </c>
       <c r="E18">
         <v>-319.4359999999999</v>
@@ -2763,45 +2763,45 @@
         <v>473.5</v>
       </c>
       <c r="M18">
-        <v>38.20605462077858</v>
+        <v>36.57989462077858</v>
       </c>
       <c r="N18">
-        <v>435.2939453792214</v>
+        <v>436.9201053792214</v>
       </c>
       <c r="O18">
-        <v>108.8234863448054</v>
+        <v>109.2300263448054</v>
       </c>
       <c r="P18">
-        <v>326.4704590344161</v>
+        <v>327.690079034416</v>
       </c>
       <c r="Q18">
-        <v>459.0704590344161</v>
+        <v>460.2900790344161</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08777045375241069</v>
+        <v>0.08775085313672397</v>
       </c>
       <c r="T18">
         <v>0.8177002107166318</v>
       </c>
       <c r="U18">
-        <v>0.0587366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04405246249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>12.39332364201993</v>
+        <v>12.94426911036087</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08066628940891467</v>
+        <v>0.08052236776808465</v>
       </c>
       <c r="C19">
-        <v>3406.954209458095</v>
+        <v>3412.42050306722</v>
       </c>
       <c r="D19">
-        <v>3874.872209458095</v>
+        <v>3880.338503067219</v>
       </c>
       <c r="E19">
         <v>-278.7819999999999</v>
@@ -2845,37 +2845,37 @@
         <v>473.5</v>
       </c>
       <c r="M19">
-        <v>40.59393303457724</v>
+        <v>39.90281503457724</v>
       </c>
       <c r="N19">
-        <v>432.9060669654228</v>
+        <v>433.5971849654227</v>
       </c>
       <c r="O19">
-        <v>108.2265167413557</v>
+        <v>108.3992962413557</v>
       </c>
       <c r="P19">
-        <v>324.6795502240671</v>
+        <v>325.1978887240671</v>
       </c>
       <c r="Q19">
-        <v>457.2795502240671</v>
+        <v>457.7978887240671</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08816550696920672</v>
+        <v>0.08814572185977296</v>
       </c>
       <c r="T19">
         <v>0.8253969370976244</v>
       </c>
       <c r="U19">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.66430460425405</v>
+        <v>11.86633072352652</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08055700366630028</v>
+        <v>0.08040562490181707</v>
       </c>
       <c r="C20">
-        <v>3370.973379392087</v>
+        <v>3376.773137603532</v>
       </c>
       <c r="D20">
-        <v>3879.545379392086</v>
+        <v>3885.345137603531</v>
       </c>
       <c r="E20">
         <v>-238.128</v>
@@ -2927,37 +2927,37 @@
         <v>473.5</v>
       </c>
       <c r="M20">
-        <v>42.98181144837589</v>
+        <v>42.25003944837589</v>
       </c>
       <c r="N20">
-        <v>430.5181885516241</v>
+        <v>431.2499605516241</v>
       </c>
       <c r="O20">
-        <v>107.629547137906</v>
+        <v>107.812490137906</v>
       </c>
       <c r="P20">
-        <v>322.8886414137181</v>
+        <v>323.4374704137181</v>
       </c>
       <c r="Q20">
-        <v>455.4886414137181</v>
+        <v>456.0374704137181</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08857019563031485</v>
+        <v>0.08855022152728655</v>
       </c>
       <c r="T20">
         <v>0.8332813885122994</v>
       </c>
       <c r="U20">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.0162876817955</v>
+        <v>11.20709012777505</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08044771792368589</v>
+        <v>0.08028888203554951</v>
       </c>
       <c r="C21">
-        <v>3335.003834801067</v>
+        <v>3341.13870852322</v>
       </c>
       <c r="D21">
-        <v>3884.229834801067</v>
+        <v>3890.36470852322</v>
       </c>
       <c r="E21">
         <v>-197.4739999999999</v>
@@ -3009,37 +3009,37 @@
         <v>473.5</v>
       </c>
       <c r="M21">
-        <v>45.36968986217456</v>
+        <v>44.59726386217456</v>
       </c>
       <c r="N21">
-        <v>428.1303101378255</v>
+        <v>428.9027361378255</v>
       </c>
       <c r="O21">
-        <v>107.0325775344564</v>
+        <v>107.2256840344564</v>
       </c>
       <c r="P21">
-        <v>321.0977326033691</v>
+        <v>321.6770521033691</v>
       </c>
       <c r="Q21">
-        <v>453.6977326033691</v>
+        <v>454.2770521033691</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08898487660404295</v>
+        <v>0.08896470884091159</v>
       </c>
       <c r="T21">
         <v>0.8413605177396827</v>
       </c>
       <c r="U21">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.43648306696415</v>
+        <v>10.61724327894478</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08033843218107149</v>
+        <v>0.08017213916928191</v>
       </c>
       <c r="C22">
-        <v>3299.045616615259</v>
+        <v>3305.51726602962</v>
       </c>
       <c r="D22">
-        <v>3888.925616615259</v>
+        <v>3895.39726602962</v>
       </c>
       <c r="E22">
         <v>-156.8199999999999</v>
@@ -3091,37 +3091,37 @@
         <v>473.5</v>
       </c>
       <c r="M22">
-        <v>47.75756827597323</v>
+        <v>46.94448827597322</v>
       </c>
       <c r="N22">
-        <v>425.7424317240268</v>
+        <v>426.5555117240268</v>
       </c>
       <c r="O22">
-        <v>106.4356079310067</v>
+        <v>106.6388779310067</v>
       </c>
       <c r="P22">
-        <v>319.3068237930201</v>
+        <v>319.9166337930201</v>
       </c>
       <c r="Q22">
-        <v>451.9068237930201</v>
+        <v>452.5166337930201</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08940992460211422</v>
+        <v>0.08938955833737725</v>
       </c>
       <c r="T22">
         <v>0.8496416251977503</v>
       </c>
       <c r="U22">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.914658913615945</v>
+        <v>10.08638111499755</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.0805756464384571</v>
+        <v>0.08032314630301435</v>
       </c>
       <c r="C23">
-        <v>3248.213398171465</v>
+        <v>3258.356110110852</v>
       </c>
       <c r="D23">
-        <v>3878.747398171465</v>
+        <v>3888.890110110852</v>
       </c>
       <c r="E23">
         <v>-116.1659999999999</v>
@@ -3173,37 +3173,37 @@
         <v>473.5</v>
       </c>
       <c r="M23">
-        <v>52.02366148977189</v>
+        <v>50.74306048977189</v>
       </c>
       <c r="N23">
-        <v>421.4763385102281</v>
+        <v>422.7569395102281</v>
       </c>
       <c r="O23">
-        <v>105.369084627557</v>
+        <v>105.689234877557</v>
       </c>
       <c r="P23">
-        <v>316.1072538826711</v>
+        <v>317.0677046326711</v>
       </c>
       <c r="Q23">
-        <v>448.7072538826711</v>
+        <v>449.6677046326711</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08984573330899745</v>
+        <v>0.08982516351729775</v>
       </c>
       <c r="T23">
         <v>0.8581323809458957</v>
       </c>
       <c r="U23">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.101627729395641</v>
+        <v>9.33132521826195</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08048286069584271</v>
+        <v>0.08021915343674677</v>
       </c>
       <c r="C24">
-        <v>3211.534231413723</v>
+        <v>3222.181007464746</v>
       </c>
       <c r="D24">
-        <v>3882.722231413723</v>
+        <v>3893.369007464747</v>
       </c>
       <c r="E24">
         <v>-75.51199999999994</v>
@@ -3255,37 +3255,37 @@
         <v>473.5</v>
       </c>
       <c r="M24">
-        <v>54.50097870357055</v>
+        <v>53.15939670357054</v>
       </c>
       <c r="N24">
-        <v>418.9990212964295</v>
+        <v>420.3406032964294</v>
       </c>
       <c r="O24">
-        <v>104.7497553241074</v>
+        <v>105.0851508241074</v>
       </c>
       <c r="P24">
-        <v>314.2492659723221</v>
+        <v>315.2554524723221</v>
       </c>
       <c r="Q24">
-        <v>446.8492659723221</v>
+        <v>447.8554524723221</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09029271659810845</v>
+        <v>0.09027193806080594</v>
       </c>
       <c r="T24">
         <v>0.8668408483798909</v>
       </c>
       <c r="U24">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.687917378059478</v>
+        <v>8.907174071977316</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08039007495322832</v>
+        <v>0.08011516057047917</v>
       </c>
       <c r="C25">
-        <v>3174.863219611678</v>
+        <v>3186.016233550801</v>
       </c>
       <c r="D25">
-        <v>3886.705219611678</v>
+        <v>3897.8582335508</v>
       </c>
       <c r="E25">
         <v>-34.85799999999995</v>
@@ -3337,37 +3337,37 @@
         <v>473.5</v>
       </c>
       <c r="M25">
-        <v>56.97829591736921</v>
+        <v>55.57573291736921</v>
       </c>
       <c r="N25">
-        <v>416.5217040826308</v>
+        <v>417.9242670826308</v>
       </c>
       <c r="O25">
-        <v>104.1304260206577</v>
+        <v>104.4810667706577</v>
       </c>
       <c r="P25">
-        <v>312.3912780619731</v>
+        <v>313.4432003119731</v>
       </c>
       <c r="Q25">
-        <v>444.9912780619731</v>
+        <v>446.0432003119731</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09075130984278076</v>
+        <v>0.09073031713791174</v>
       </c>
       <c r="T25">
         <v>0.8757755097732108</v>
       </c>
       <c r="U25">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.310181839882977</v>
+        <v>8.519905634065259</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08029728921061394</v>
+        <v>0.0800111677042116</v>
       </c>
       <c r="C26">
-        <v>3138.200387887741</v>
+        <v>3149.861824138708</v>
       </c>
       <c r="D26">
-        <v>3890.696387887741</v>
+        <v>3902.357824138708</v>
       </c>
       <c r="E26">
         <v>5.796000000000049</v>
@@ -3419,37 +3419,37 @@
         <v>473.5</v>
       </c>
       <c r="M26">
-        <v>59.45561313116787</v>
+        <v>57.99206913116787</v>
       </c>
       <c r="N26">
-        <v>414.0443868688321</v>
+        <v>415.5079308688321</v>
       </c>
       <c r="O26">
-        <v>103.511096717208</v>
+        <v>103.876982717208</v>
       </c>
       <c r="P26">
-        <v>310.5332901516241</v>
+        <v>311.6309481516241</v>
       </c>
       <c r="Q26">
-        <v>443.1332901516241</v>
+        <v>444.2309481516241</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09122197133073394</v>
+        <v>0.09120075882230982</v>
       </c>
       <c r="T26">
         <v>0.884945293834776</v>
       </c>
       <c r="U26">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.963924263221188</v>
+        <v>8.164909565979208</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08048575346799952</v>
+        <v>0.07990717483794403</v>
       </c>
       <c r="C27">
-        <v>3089.448185391051</v>
+        <v>3113.71781516352</v>
       </c>
       <c r="D27">
-        <v>3882.59818539105</v>
+        <v>3906.86781516352</v>
       </c>
       <c r="E27">
         <v>46.45000000000005</v>
@@ -3501,45 +3501,45 @@
         <v>473.5</v>
       </c>
       <c r="M27">
-        <v>63.45745534496653</v>
+        <v>60.40840534496653</v>
       </c>
       <c r="N27">
-        <v>410.0425446550335</v>
+        <v>413.0915946550335</v>
       </c>
       <c r="O27">
-        <v>102.5106361637584</v>
+        <v>103.2728986637584</v>
       </c>
       <c r="P27">
-        <v>307.5319084912751</v>
+        <v>309.8186959912751</v>
       </c>
       <c r="Q27">
-        <v>440.1319084912751</v>
+        <v>442.4186959912751</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09170518379169917</v>
+        <v>0.09168374561829185</v>
       </c>
       <c r="T27">
         <v>0.8943596054713161</v>
       </c>
       <c r="U27">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04682746249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.461692206628298</v>
+        <v>7.838313183340039</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08040421772538515</v>
+        <v>0.07995918197167645</v>
       </c>
       <c r="C28">
-        <v>3052.293588927794</v>
+        <v>3070.8070532778</v>
       </c>
       <c r="D28">
-        <v>3886.097588927794</v>
+        <v>3904.6110532778</v>
       </c>
       <c r="E28">
         <v>87.10400000000016</v>
@@ -3583,37 +3583,37 @@
         <v>473.5</v>
       </c>
       <c r="M28">
-        <v>65.9957535587652</v>
+        <v>63.6703447587652</v>
       </c>
       <c r="N28">
-        <v>407.5042464412348</v>
+        <v>409.8296552412348</v>
       </c>
       <c r="O28">
-        <v>101.8760616103087</v>
+        <v>102.4574138103087</v>
       </c>
       <c r="P28">
-        <v>305.6281848309261</v>
+        <v>307.3722414309261</v>
       </c>
       <c r="Q28">
-        <v>438.2281848309261</v>
+        <v>439.9722414309261</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09220145604890675</v>
+        <v>0.09217978611146257</v>
       </c>
       <c r="T28">
         <v>0.9040283579628979</v>
       </c>
       <c r="U28">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.1747040448349</v>
+        <v>7.436743146185266</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08032268198277076</v>
+        <v>0.07986118910540888</v>
       </c>
       <c r="C29">
-        <v>3015.145306212036</v>
+        <v>3034.407462735966</v>
       </c>
       <c r="D29">
-        <v>3889.603306212036</v>
+        <v>3908.865462735967</v>
       </c>
       <c r="E29">
         <v>127.7580000000002</v>
@@ -3665,37 +3665,37 @@
         <v>473.5</v>
       </c>
       <c r="M29">
-        <v>68.53405177256386</v>
+        <v>66.11920417256385</v>
       </c>
       <c r="N29">
-        <v>404.9659482274361</v>
+        <v>407.3807958274361</v>
       </c>
       <c r="O29">
-        <v>101.241487056859</v>
+        <v>101.845198956859</v>
       </c>
       <c r="P29">
-        <v>303.7244611705771</v>
+        <v>305.5355968705771</v>
       </c>
       <c r="Q29">
-        <v>436.3244611705771</v>
+        <v>438.1355968705772</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09271132480631178</v>
+        <v>0.09268941675513112</v>
       </c>
       <c r="T29">
         <v>0.9139620077830163</v>
       </c>
       <c r="U29">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.908974265396571</v>
+        <v>7.161308214845071</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08024114624015635</v>
+        <v>0.0797631962391413</v>
       </c>
       <c r="C30">
-        <v>2978.003354346435</v>
+        <v>2998.017153396592</v>
       </c>
       <c r="D30">
-        <v>3893.115354346435</v>
+        <v>3913.129153396592</v>
       </c>
       <c r="E30">
         <v>168.4120000000001</v>
@@ -3747,37 +3747,37 @@
         <v>473.5</v>
       </c>
       <c r="M30">
-        <v>71.07234998636252</v>
+        <v>68.56806358636253</v>
       </c>
       <c r="N30">
-        <v>402.4276500136375</v>
+        <v>404.9319364136375</v>
       </c>
       <c r="O30">
-        <v>100.6069125034094</v>
+        <v>101.2329841034094</v>
       </c>
       <c r="P30">
-        <v>301.8207375102281</v>
+        <v>303.6989523102281</v>
       </c>
       <c r="Q30">
-        <v>434.4207375102282</v>
+        <v>436.2989523102281</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09323535658475582</v>
+        <v>0.09321320380556825</v>
       </c>
       <c r="T30">
         <v>0.9241715923203601</v>
       </c>
       <c r="U30">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.662225184489551</v>
+        <v>6.905547207172031</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08015961049754194</v>
+        <v>0.07966520337287371</v>
       </c>
       <c r="C31">
-        <v>2940.867750495474</v>
+        <v>2961.636155663939</v>
       </c>
       <c r="D31">
-        <v>3896.633750495473</v>
+        <v>3917.402155663939</v>
       </c>
       <c r="E31">
         <v>209.0659999999999</v>
@@ -3829,37 +3829,37 @@
         <v>473.5</v>
       </c>
       <c r="M31">
-        <v>73.61064820016117</v>
+        <v>71.01692300016117</v>
       </c>
       <c r="N31">
-        <v>399.8893517998388</v>
+        <v>402.4830769998388</v>
       </c>
       <c r="O31">
-        <v>99.97233794995971</v>
+        <v>100.6207692499597</v>
       </c>
       <c r="P31">
-        <v>299.9170138498791</v>
+        <v>301.8623077498791</v>
       </c>
       <c r="Q31">
-        <v>432.5170138498792</v>
+        <v>434.4623077498791</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09377414982174759</v>
+        <v>0.0937517454208064</v>
       </c>
       <c r="T31">
         <v>0.9346687707883331</v>
       </c>
       <c r="U31">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.43249328157612</v>
+        <v>6.667424889683343</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08007807475492756</v>
+        <v>0.07956721050660613</v>
       </c>
       <c r="C32">
-        <v>2903.738511885739</v>
+        <v>2925.264500075211</v>
       </c>
       <c r="D32">
-        <v>3900.158511885739</v>
+        <v>3921.684500075211</v>
       </c>
       <c r="E32">
         <v>249.7199999999999</v>
@@ -3911,37 +3911,37 @@
         <v>473.5</v>
       </c>
       <c r="M32">
-        <v>76.14894641395983</v>
+        <v>73.46578241395983</v>
       </c>
       <c r="N32">
-        <v>397.3510535860402</v>
+        <v>400.0342175860402</v>
       </c>
       <c r="O32">
-        <v>99.33776339651004</v>
+        <v>100.00855439651</v>
       </c>
       <c r="P32">
-        <v>298.0132901895302</v>
+        <v>300.0256631895302</v>
       </c>
       <c r="Q32">
-        <v>430.6132901895302</v>
+        <v>432.6256631895302</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09432833715122485</v>
+        <v>0.09430567393933709</v>
       </c>
       <c r="T32">
         <v>0.9454658686411056</v>
       </c>
       <c r="U32">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.218076838856915</v>
+        <v>6.445177393360565</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08032203901231318</v>
+        <v>0.07946921764033854</v>
       </c>
       <c r="C33">
-        <v>2852.556976557121</v>
+        <v>2888.902217301292</v>
       </c>
       <c r="D33">
-        <v>3889.630976557121</v>
+        <v>3925.976217301292</v>
       </c>
       <c r="E33">
         <v>290.3740000000001</v>
@@ -3993,45 +3993,45 @@
         <v>473.5</v>
       </c>
       <c r="M33">
-        <v>80.4516282277585</v>
+        <v>75.9146418277585</v>
       </c>
       <c r="N33">
-        <v>393.0483717722415</v>
+        <v>397.5853581722415</v>
       </c>
       <c r="O33">
-        <v>98.26209294306037</v>
+        <v>99.39633954306038</v>
       </c>
       <c r="P33">
-        <v>294.7862788291811</v>
+        <v>298.1890186291811</v>
       </c>
       <c r="Q33">
-        <v>427.3862788291812</v>
+        <v>430.7890186291812</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09489858788155653</v>
+        <v>0.09487565835695562</v>
       </c>
       <c r="T33">
         <v>0.9565759258519294</v>
       </c>
       <c r="U33">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>5.885524139542854</v>
+        <v>6.237268445187643</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08025100326969878</v>
+        <v>0.07961122477407097</v>
       </c>
       <c r="C34">
-        <v>2814.962438385787</v>
+        <v>2842.031893712426</v>
       </c>
       <c r="D34">
-        <v>3892.690438385787</v>
+        <v>3919.759893712425</v>
       </c>
       <c r="E34">
         <v>331.0280000000001</v>
@@ -4075,37 +4075,37 @@
         <v>473.5</v>
       </c>
       <c r="M34">
-        <v>83.04684204155717</v>
+        <v>79.66442924155716</v>
       </c>
       <c r="N34">
-        <v>390.4531579584428</v>
+        <v>393.8355707584428</v>
       </c>
       <c r="O34">
-        <v>97.61328948961071</v>
+        <v>98.45889268961071</v>
       </c>
       <c r="P34">
-        <v>292.8398684688322</v>
+        <v>295.3766780688321</v>
       </c>
       <c r="Q34">
-        <v>425.4398684688322</v>
+        <v>427.9766780688321</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09548561069219205</v>
+        <v>0.09546240702215117</v>
       </c>
       <c r="T34">
         <v>0.9680127494513069</v>
       </c>
       <c r="U34">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.70160151018214</v>
+        <v>5.943681571661816</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08017996752708439</v>
+        <v>0.0795207319078034</v>
       </c>
       <c r="C35">
-        <v>2777.372716956737</v>
+        <v>2805.336916667322</v>
       </c>
       <c r="D35">
-        <v>3895.754716956737</v>
+        <v>3923.718916667322</v>
       </c>
       <c r="E35">
         <v>371.6820000000001</v>
@@ -4157,37 +4157,37 @@
         <v>473.5</v>
       </c>
       <c r="M35">
-        <v>85.64205585535582</v>
+        <v>82.15394265535582</v>
       </c>
       <c r="N35">
-        <v>387.8579441446442</v>
+        <v>391.3460573446442</v>
       </c>
       <c r="O35">
-        <v>96.96448603616105</v>
+        <v>97.83651433616104</v>
       </c>
       <c r="P35">
-        <v>290.8934581084832</v>
+        <v>293.5095430084831</v>
       </c>
       <c r="Q35">
-        <v>423.4934581084832</v>
+        <v>426.1095430084832</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09609015657180181</v>
+        <v>0.09606667057287495</v>
       </c>
       <c r="T35">
         <v>0.9797909707700688</v>
       </c>
       <c r="U35">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.528825706843288</v>
+        <v>5.763570008884185</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08010893178446998</v>
+        <v>0.07943023904153582</v>
       </c>
       <c r="C36">
-        <v>2739.78782365398</v>
+        <v>2768.649945066455</v>
       </c>
       <c r="D36">
-        <v>3898.82382365398</v>
+        <v>3927.685945066455</v>
       </c>
       <c r="E36">
         <v>412.3360000000001</v>
@@ -4239,37 +4239,37 @@
         <v>473.5</v>
       </c>
       <c r="M36">
-        <v>88.23726966915449</v>
+        <v>84.64345606915448</v>
       </c>
       <c r="N36">
-        <v>385.2627303308455</v>
+        <v>388.8565439308455</v>
       </c>
       <c r="O36">
-        <v>96.31568258271137</v>
+        <v>97.21413598271138</v>
       </c>
       <c r="P36">
-        <v>288.9470477481341</v>
+        <v>291.6424079481342</v>
       </c>
       <c r="Q36">
-        <v>421.5470477481342</v>
+        <v>424.2424079481342</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09671302202352092</v>
+        <v>0.09668924514028732</v>
       </c>
       <c r="T36">
         <v>0.9919261078863688</v>
       </c>
       <c r="U36">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.366213186053779</v>
+        <v>5.594053243917004</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.0800378960418556</v>
+        <v>0.07933974617526825</v>
       </c>
       <c r="C37">
-        <v>2702.207769897416</v>
+        <v>2731.971003215822</v>
       </c>
       <c r="D37">
-        <v>3901.897769897416</v>
+        <v>3931.661003215822</v>
       </c>
       <c r="E37">
         <v>452.9900000000001</v>
@@ -4321,37 +4321,37 @@
         <v>473.5</v>
       </c>
       <c r="M37">
-        <v>90.83248348295315</v>
+        <v>87.13296948295314</v>
       </c>
       <c r="N37">
-        <v>382.6675165170469</v>
+        <v>386.3670305170468</v>
       </c>
       <c r="O37">
-        <v>95.66687912926172</v>
+        <v>96.59175762926171</v>
       </c>
       <c r="P37">
-        <v>287.0006373877852</v>
+        <v>289.7752728877851</v>
       </c>
       <c r="Q37">
-        <v>419.6006373877852</v>
+        <v>422.3752728877852</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09735505256606217</v>
+        <v>0.09733097584823547</v>
       </c>
       <c r="T37">
         <v>1.004434633837017</v>
       </c>
       <c r="U37">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.212892809309386</v>
+        <v>5.434223151233661</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07996686029924122</v>
+        <v>0.07924925330900068</v>
       </c>
       <c r="C38">
-        <v>2664.632567143</v>
+        <v>2695.300115519914</v>
       </c>
       <c r="D38">
-        <v>3904.976567143</v>
+        <v>3935.644115519914</v>
       </c>
       <c r="E38">
         <v>493.6439999999999</v>
@@ -4403,37 +4403,37 @@
         <v>473.5</v>
       </c>
       <c r="M38">
-        <v>93.42769729675179</v>
+        <v>89.62248289675179</v>
       </c>
       <c r="N38">
-        <v>380.0723027032482</v>
+        <v>383.8775171032482</v>
       </c>
       <c r="O38">
-        <v>95.01807567581206</v>
+        <v>95.96937927581206</v>
       </c>
       <c r="P38">
-        <v>285.0542270274362</v>
+        <v>287.9081378274362</v>
       </c>
       <c r="Q38">
-        <v>417.6542270274362</v>
+        <v>420.5081378274362</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09801714656305782</v>
+        <v>0.09799276064080698</v>
       </c>
       <c r="T38">
         <v>1.017334051223622</v>
       </c>
       <c r="U38">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.068090231273015</v>
+        <v>5.283272508143837</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07989582455662682</v>
+        <v>0.07915876044273309</v>
       </c>
       <c r="C39">
-        <v>2627.062226882864</v>
+        <v>2658.63730648222</v>
       </c>
       <c r="D39">
-        <v>3908.060226882864</v>
+        <v>3939.63530648222</v>
       </c>
       <c r="E39">
         <v>534.2980000000001</v>
@@ -4485,37 +4485,37 @@
         <v>473.5</v>
       </c>
       <c r="M39">
-        <v>96.02291111055047</v>
+        <v>92.11199631055047</v>
       </c>
       <c r="N39">
-        <v>377.4770888894495</v>
+        <v>381.3880036894495</v>
       </c>
       <c r="O39">
-        <v>94.36927222236238</v>
+        <v>95.34700092236238</v>
       </c>
       <c r="P39">
-        <v>283.1078166670871</v>
+        <v>286.0410027670872</v>
       </c>
       <c r="Q39">
-        <v>415.7078166670872</v>
+        <v>418.6410027670872</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09870025941710096</v>
+        <v>0.09867555447441251</v>
       </c>
       <c r="T39">
         <v>1.030642973924088</v>
       </c>
       <c r="U39">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.931114819616987</v>
+        <v>5.140481359275084</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07982478881401243</v>
+        <v>0.07906826757646551</v>
       </c>
       <c r="C40">
-        <v>2589.496760645474</v>
+        <v>2621.982600705727</v>
       </c>
       <c r="D40">
-        <v>3911.148760645474</v>
+        <v>3943.634600705727</v>
       </c>
       <c r="E40">
         <v>574.9520000000001</v>
@@ -4567,37 +4567,37 @@
         <v>473.5</v>
       </c>
       <c r="M40">
-        <v>98.61812492434913</v>
+        <v>94.60150972434913</v>
       </c>
       <c r="N40">
-        <v>374.8818750756509</v>
+        <v>378.8984902756509</v>
       </c>
       <c r="O40">
-        <v>93.72046876891272</v>
+        <v>94.72462256891272</v>
       </c>
       <c r="P40">
-        <v>281.1614063067382</v>
+        <v>284.1738677067382</v>
       </c>
       <c r="Q40">
-        <v>413.7614063067382</v>
+        <v>416.7738677067382</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09940540816966163</v>
+        <v>0.09938037391555371</v>
       </c>
       <c r="T40">
         <v>1.044381216711666</v>
       </c>
       <c r="U40">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.801348640153382</v>
+        <v>5.005205534031004</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07975375307139804</v>
+        <v>0.07897777471019793</v>
       </c>
       <c r="C41">
-        <v>2551.936179995768</v>
+        <v>2585.336022893423</v>
       </c>
       <c r="D41">
-        <v>3914.242179995768</v>
+        <v>3947.642022893423</v>
       </c>
       <c r="E41">
         <v>615.6060000000001</v>
@@ -4649,37 +4649,37 @@
         <v>473.5</v>
       </c>
       <c r="M41">
-        <v>101.2133387381478</v>
+        <v>97.09102313814779</v>
       </c>
       <c r="N41">
-        <v>372.2866612618522</v>
+        <v>376.4089768618522</v>
       </c>
       <c r="O41">
-        <v>93.07166531546305</v>
+        <v>94.10224421546306</v>
       </c>
       <c r="P41">
-        <v>279.2149959463891</v>
+        <v>282.3067326463892</v>
       </c>
       <c r="Q41">
-        <v>411.8149959463892</v>
+        <v>414.9067326463892</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1001336765534538</v>
+        <v>0.1001083021908307</v>
       </c>
       <c r="T41">
         <v>1.058569893689</v>
       </c>
       <c r="U41">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.678237136559705</v>
+        <v>4.876866930594311</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07968271732878365</v>
+        <v>0.07888728184393036</v>
       </c>
       <c r="C42">
-        <v>2514.380496535297</v>
+        <v>2548.697597848811</v>
       </c>
       <c r="D42">
-        <v>3917.340496535297</v>
+        <v>3951.657597848811</v>
       </c>
       <c r="E42">
         <v>656.2600000000001</v>
@@ -4731,37 +4731,37 @@
         <v>473.5</v>
       </c>
       <c r="M42">
-        <v>103.8085525519464</v>
+        <v>99.58053655194645</v>
       </c>
       <c r="N42">
-        <v>369.6914474480536</v>
+        <v>373.9194634480535</v>
       </c>
       <c r="O42">
-        <v>92.42286186201339</v>
+        <v>93.47986586201338</v>
       </c>
       <c r="P42">
-        <v>277.2685855860402</v>
+        <v>280.4395975860401</v>
       </c>
       <c r="Q42">
-        <v>409.8685855860402</v>
+        <v>413.0395975860401</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.100886220550039</v>
+        <v>0.1008604947419502</v>
       </c>
       <c r="T42">
         <v>1.073231526565579</v>
       </c>
       <c r="U42">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.561281208145713</v>
+        <v>4.754945257329453</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08041118158616925</v>
+        <v>0.07879678897766279</v>
       </c>
       <c r="C43">
-        <v>2442.184463108745</v>
+        <v>2512.067350476417</v>
       </c>
       <c r="D43">
-        <v>3885.798463108746</v>
+        <v>3955.681350476417</v>
       </c>
       <c r="E43">
         <v>696.9140000000001</v>
@@ -4813,45 +4813,45 @@
         <v>473.5</v>
       </c>
       <c r="M43">
-        <v>110.7374827657451</v>
+        <v>102.0700499657451</v>
       </c>
       <c r="N43">
-        <v>362.7625172342549</v>
+        <v>371.4299500342549</v>
       </c>
       <c r="O43">
-        <v>90.69062930856373</v>
+        <v>92.85748750856372</v>
       </c>
       <c r="P43">
-        <v>272.0718879256912</v>
+        <v>278.5724625256912</v>
       </c>
       <c r="Q43">
-        <v>404.6718879256912</v>
+        <v>411.1724625256912</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1016642745126102</v>
+        <v>0.1016381853456501</v>
       </c>
       <c r="T43">
         <v>1.088390163946449</v>
       </c>
       <c r="U43">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.275878304021462</v>
+        <v>4.638970982760442</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08035964584355486</v>
+        <v>0.07870629611139521</v>
       </c>
       <c r="C44">
-        <v>2403.745221671196</v>
+        <v>2475.445305782309</v>
       </c>
       <c r="D44">
-        <v>3888.013221671196</v>
+        <v>3959.713305782309</v>
       </c>
       <c r="E44">
         <v>737.5680000000001</v>
@@ -4895,45 +4895,45 @@
         <v>473.5</v>
       </c>
       <c r="M44">
-        <v>113.4383969795438</v>
+        <v>104.5595633795438</v>
       </c>
       <c r="N44">
-        <v>360.0616030204562</v>
+        <v>368.9404366204562</v>
       </c>
       <c r="O44">
-        <v>90.01540075511406</v>
+        <v>92.23510915511406</v>
       </c>
       <c r="P44">
-        <v>270.0462022653422</v>
+        <v>276.7053274653422</v>
       </c>
       <c r="Q44">
-        <v>402.6462022653422</v>
+        <v>409.3053274653422</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1024691579221666</v>
+        <v>0.1024426928667189</v>
       </c>
       <c r="T44">
         <v>1.104071512961142</v>
       </c>
       <c r="U44">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.174071677735236</v>
+        <v>4.528519292694718</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08030811010094047</v>
+        <v>0.07942205324512763</v>
       </c>
       <c r="C45">
-        <v>2365.308506331117</v>
+        <v>2403.123189867158</v>
       </c>
       <c r="D45">
-        <v>3890.230506331117</v>
+        <v>3928.045189867158</v>
       </c>
       <c r="E45">
         <v>778.2220000000001</v>
@@ -4977,37 +4977,37 @@
         <v>473.5</v>
       </c>
       <c r="M45">
-        <v>116.1393111933424</v>
+        <v>111.4193817933424</v>
       </c>
       <c r="N45">
-        <v>357.3606888066575</v>
+        <v>362.0806182066576</v>
       </c>
       <c r="O45">
-        <v>89.34017220166439</v>
+        <v>90.52015455166439</v>
       </c>
       <c r="P45">
-        <v>268.0205166049932</v>
+        <v>271.5604636549932</v>
       </c>
       <c r="Q45">
-        <v>400.6205166049932</v>
+        <v>404.1604636549932</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1033022828548653</v>
+        <v>0.1032754287218603</v>
       </c>
       <c r="T45">
         <v>1.12030308474828</v>
       </c>
       <c r="U45">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.0770002433693</v>
+        <v>4.249709452510109</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08114757435832608</v>
+        <v>0.07935031037886005</v>
       </c>
       <c r="C46">
-        <v>2288.849231148025</v>
+        <v>2365.620537239349</v>
       </c>
       <c r="D46">
-        <v>3854.425231148025</v>
+        <v>3931.196537239349</v>
       </c>
       <c r="E46">
         <v>818.8760000000001</v>
@@ -5059,45 +5059,45 @@
         <v>473.5</v>
       </c>
       <c r="M46">
-        <v>123.6699206071411</v>
+        <v>114.0105302071411</v>
       </c>
       <c r="N46">
-        <v>349.8300793928589</v>
+        <v>359.4894697928589</v>
       </c>
       <c r="O46">
-        <v>87.45751984821473</v>
+        <v>89.87236744821473</v>
       </c>
       <c r="P46">
-        <v>262.3725595446442</v>
+        <v>269.6171023446442</v>
       </c>
       <c r="Q46">
-        <v>394.9725595446442</v>
+        <v>402.2171023446442</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1041651622494461</v>
+        <v>0.1041379051432568</v>
       </c>
       <c r="T46">
         <v>1.137114355527816</v>
       </c>
       <c r="U46">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.828740227821078</v>
+        <v>4.153125146771242</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08111628861571168</v>
+        <v>0.07927856751259246</v>
       </c>
       <c r="C47">
-        <v>2249.51781909586</v>
+        <v>2328.12294512561</v>
       </c>
       <c r="D47">
-        <v>3855.747819095861</v>
+        <v>3934.352945125611</v>
       </c>
       <c r="E47">
         <v>859.5300000000001</v>
@@ -5141,45 +5141,45 @@
         <v>473.5</v>
       </c>
       <c r="M47">
-        <v>126.4806006209398</v>
+        <v>116.6016786209398</v>
       </c>
       <c r="N47">
-        <v>347.0193993790602</v>
+        <v>356.8983213790602</v>
       </c>
       <c r="O47">
-        <v>86.75484984476506</v>
+        <v>89.22458034476506</v>
       </c>
       <c r="P47">
-        <v>260.2645495342952</v>
+        <v>267.6737410342952</v>
       </c>
       <c r="Q47">
-        <v>392.8645495342952</v>
+        <v>400.2737410342952</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1050594190765571</v>
+        <v>0.1050317443436131</v>
       </c>
       <c r="T47">
         <v>1.15453694524479</v>
       </c>
       <c r="U47">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.743657111647276</v>
+        <v>4.060833476842992</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08108500287309729</v>
+        <v>0.08041432464632489</v>
       </c>
       <c r="C48">
-        <v>2210.187315007506</v>
+        <v>2238.087594887545</v>
       </c>
       <c r="D48">
-        <v>3857.071315007507</v>
+        <v>3884.971594887545</v>
       </c>
       <c r="E48">
         <v>900.1840000000001</v>
@@ -5223,37 +5223,37 @@
         <v>473.5</v>
       </c>
       <c r="M48">
-        <v>129.2912806347384</v>
+        <v>125.7381210347384</v>
       </c>
       <c r="N48">
-        <v>344.2087193652616</v>
+        <v>347.7618789652616</v>
       </c>
       <c r="O48">
-        <v>86.05217984131539</v>
+        <v>86.9404697413154</v>
       </c>
       <c r="P48">
-        <v>258.1565395239462</v>
+        <v>260.8214092239462</v>
       </c>
       <c r="Q48">
-        <v>390.7565395239462</v>
+        <v>393.4214092239462</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1059867965268945</v>
+        <v>0.1059586886995382</v>
       </c>
       <c r="T48">
         <v>1.172604816062392</v>
       </c>
       <c r="U48">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.662273261394074</v>
+        <v>3.7657632872467</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.0810537171304829</v>
+        <v>0.08036883178005731</v>
       </c>
       <c r="C49">
-        <v>2170.857719818267</v>
+        <v>2199.38772605856</v>
       </c>
       <c r="D49">
-        <v>3858.395719818267</v>
+        <v>3886.92572605856</v>
       </c>
       <c r="E49">
         <v>940.8380000000001</v>
@@ -5305,37 +5305,37 @@
         <v>473.5</v>
       </c>
       <c r="M49">
-        <v>132.1019606485371</v>
+        <v>128.4715584485371</v>
       </c>
       <c r="N49">
-        <v>341.3980393514629</v>
+        <v>345.0284415514629</v>
       </c>
       <c r="O49">
-        <v>85.34950983786572</v>
+        <v>86.25711038786574</v>
       </c>
       <c r="P49">
-        <v>256.0485295135971</v>
+        <v>258.7713311635972</v>
       </c>
       <c r="Q49">
-        <v>388.6485295135972</v>
+        <v>391.3713311635972</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1069491693527163</v>
+        <v>0.1069206120877624</v>
       </c>
       <c r="T49">
         <v>1.191354493325942</v>
       </c>
       <c r="U49">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.584352553704839</v>
+        <v>3.685640664113792</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08102243138786849</v>
+        <v>0.08032333891378973</v>
       </c>
       <c r="C50">
-        <v>2131.529034464733</v>
+        <v>2160.68982406525</v>
       </c>
       <c r="D50">
-        <v>3859.721034464733</v>
+        <v>3888.881824065249</v>
       </c>
       <c r="E50">
         <v>981.4920000000001</v>
@@ -5387,37 +5387,37 @@
         <v>473.5</v>
       </c>
       <c r="M50">
-        <v>134.9126406623357</v>
+        <v>131.2049958623357</v>
       </c>
       <c r="N50">
-        <v>338.5873593376642</v>
+        <v>342.2950041376643</v>
       </c>
       <c r="O50">
-        <v>84.64683983441606</v>
+        <v>85.57375103441606</v>
       </c>
       <c r="P50">
-        <v>253.9405195032482</v>
+        <v>256.7212531032482</v>
       </c>
       <c r="Q50">
-        <v>386.5405195032482</v>
+        <v>389.3212531032482</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1079485565179927</v>
+        <v>0.1079195325293797</v>
       </c>
       <c r="T50">
         <v>1.210825312022705</v>
       </c>
       <c r="U50">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.509678542169321</v>
+        <v>3.608856483611421</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.0827183956452541</v>
+        <v>0.08027784604752214</v>
       </c>
       <c r="C51">
-        <v>2020.320306070894</v>
+        <v>2121.993891878541</v>
       </c>
       <c r="D51">
-        <v>3789.166306070894</v>
+        <v>3890.839891878541</v>
       </c>
       <c r="E51">
         <v>1022.146</v>
@@ -5469,45 +5469,45 @@
         <v>473.5</v>
       </c>
       <c r="M51">
-        <v>147.0859368761344</v>
+        <v>133.9384332761344</v>
       </c>
       <c r="N51">
-        <v>326.4140631238656</v>
+        <v>339.5615667238656</v>
       </c>
       <c r="O51">
-        <v>81.6035157809664</v>
+        <v>84.8903916809664</v>
       </c>
       <c r="P51">
-        <v>244.8105473428992</v>
+        <v>254.6711750428992</v>
       </c>
       <c r="Q51">
-        <v>377.4105473428992</v>
+        <v>387.2711750428992</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1089871353368095</v>
+        <v>0.1089576263216488</v>
       </c>
       <c r="T51">
         <v>1.231059692236988</v>
       </c>
       <c r="U51">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.05537746249690058</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.219206472463434</v>
+        <v>3.535206351292821</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08272235990263971</v>
+        <v>0.08128235318125457</v>
       </c>
       <c r="C52">
-        <v>1979.504408449928</v>
+        <v>2038.558552288423</v>
       </c>
       <c r="D52">
-        <v>3789.004408449929</v>
+        <v>3848.058552288423</v>
       </c>
       <c r="E52">
         <v>1062.8</v>
@@ -5551,37 +5551,37 @@
         <v>473.5</v>
       </c>
       <c r="M52">
-        <v>150.0876906899331</v>
+        <v>142.3634306899331</v>
       </c>
       <c r="N52">
-        <v>323.4123093100669</v>
+        <v>331.1365693100669</v>
       </c>
       <c r="O52">
-        <v>80.85307732751673</v>
+        <v>82.78414232751673</v>
       </c>
       <c r="P52">
-        <v>242.5592319825502</v>
+        <v>248.3524269825502</v>
       </c>
       <c r="Q52">
-        <v>375.1592319825502</v>
+        <v>380.9524269825502</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1100672573083789</v>
+        <v>0.1100372438656086</v>
       </c>
       <c r="T52">
         <v>1.252103447659842</v>
       </c>
       <c r="U52">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.154822343014165</v>
+        <v>3.325994587973093</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08272632416002532</v>
+        <v>0.081257860314987</v>
       </c>
       <c r="C53">
-        <v>1938.688524662993</v>
+        <v>1998.93649533035</v>
       </c>
       <c r="D53">
-        <v>3788.842524662994</v>
+        <v>3849.090495330351</v>
       </c>
       <c r="E53">
         <v>1103.454</v>
@@ -5633,37 +5633,37 @@
         <v>473.5</v>
       </c>
       <c r="M53">
-        <v>153.0894445037318</v>
+        <v>145.2106993037317</v>
       </c>
       <c r="N53">
-        <v>320.4105554962682</v>
+        <v>328.2893006962682</v>
       </c>
       <c r="O53">
-        <v>80.10263887406705</v>
+        <v>82.07232517406706</v>
       </c>
       <c r="P53">
-        <v>240.3079166222012</v>
+        <v>246.2169755222012</v>
       </c>
       <c r="Q53">
-        <v>372.9079166222012</v>
+        <v>378.8169755222012</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1111914658910327</v>
+        <v>0.1111609274317708</v>
       </c>
       <c r="T53">
         <v>1.274006131875467</v>
       </c>
       <c r="U53">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.092963081386436</v>
+        <v>3.260779007816758</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08273028841741094</v>
+        <v>0.08123336744871942</v>
       </c>
       <c r="C54">
-        <v>1897.872654708314</v>
+        <v>1959.314991998</v>
       </c>
       <c r="D54">
-        <v>3788.680654708315</v>
+        <v>3850.122991998</v>
       </c>
       <c r="E54">
         <v>1144.108</v>
@@ -5715,37 +5715,37 @@
         <v>473.5</v>
       </c>
       <c r="M54">
-        <v>156.0911983175304</v>
+        <v>148.0579679175304</v>
       </c>
       <c r="N54">
-        <v>317.4088016824696</v>
+        <v>325.4420320824696</v>
       </c>
       <c r="O54">
-        <v>79.35220042061739</v>
+        <v>81.3605080206174</v>
       </c>
       <c r="P54">
-        <v>238.0566012618522</v>
+        <v>244.0815240618522</v>
       </c>
       <c r="Q54">
-        <v>370.6566012618522</v>
+        <v>376.6815240618522</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1123625164979638</v>
+        <v>0.1123314311465232</v>
       </c>
       <c r="T54">
         <v>1.296821427933408</v>
       </c>
       <c r="U54">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.033483022129005</v>
+        <v>3.198071719204898</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08643100267479654</v>
+        <v>0.08120887458245185</v>
       </c>
       <c r="C55">
-        <v>1711.911469223592</v>
+        <v>1919.69404273701</v>
       </c>
       <c r="D55">
-        <v>3643.373469223593</v>
+        <v>3851.156042737011</v>
       </c>
       <c r="E55">
         <v>1184.762</v>
@@ -5797,45 +5797,45 @@
         <v>473.5</v>
       </c>
       <c r="M55">
-        <v>179.1313087313291</v>
+        <v>150.9052365313291</v>
       </c>
       <c r="N55">
-        <v>294.3686912686709</v>
+        <v>322.594763468671</v>
       </c>
       <c r="O55">
-        <v>73.59217281716774</v>
+        <v>80.64869086716774</v>
       </c>
       <c r="P55">
-        <v>220.7765184515032</v>
+        <v>241.9460726015032</v>
       </c>
       <c r="Q55">
-        <v>353.3765184515032</v>
+        <v>374.5460726015033</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1135833990456154</v>
+        <v>0.1135517435299884</v>
       </c>
       <c r="T55">
         <v>1.32060758765339</v>
       </c>
       <c r="U55">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.643312346420587</v>
+        <v>3.137730743370843</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08650471693218215</v>
+        <v>0.08118438171618426</v>
       </c>
       <c r="C56">
-        <v>1668.47623816471</v>
+        <v>1880.073647993504</v>
       </c>
       <c r="D56">
-        <v>3640.592238164711</v>
+        <v>3852.189647993504</v>
       </c>
       <c r="E56">
         <v>1225.416</v>
@@ -5879,45 +5879,45 @@
         <v>473.5</v>
       </c>
       <c r="M56">
-        <v>182.5111447451277</v>
+        <v>153.7525051451277</v>
       </c>
       <c r="N56">
-        <v>290.9888552548723</v>
+        <v>319.7474948548723</v>
       </c>
       <c r="O56">
-        <v>72.74721381371808</v>
+        <v>79.93687371371807</v>
       </c>
       <c r="P56">
-        <v>218.2416414411542</v>
+        <v>239.8106211411542</v>
       </c>
       <c r="Q56">
-        <v>350.8416414411543</v>
+        <v>372.4106211411543</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1148573634431649</v>
+        <v>0.1148251129736043</v>
       </c>
       <c r="T56">
         <v>1.345427928230763</v>
       </c>
       <c r="U56">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.594362117783169</v>
+        <v>3.079624618493605</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08657843118956776</v>
+        <v>0.08115988884991668</v>
       </c>
       <c r="C57">
-        <v>1625.045250066886</v>
+        <v>1840.453808214076</v>
       </c>
       <c r="D57">
-        <v>3637.815250066886</v>
+        <v>3853.223808214077</v>
       </c>
       <c r="E57">
         <v>1266.07</v>
@@ -5961,45 +5961,45 @@
         <v>473.5</v>
       </c>
       <c r="M57">
-        <v>185.8909807589264</v>
+        <v>156.5997737589264</v>
       </c>
       <c r="N57">
-        <v>287.6090192410736</v>
+        <v>316.9002262410736</v>
       </c>
       <c r="O57">
-        <v>71.9022548102684</v>
+        <v>79.2250565602684</v>
       </c>
       <c r="P57">
-        <v>215.7067644308052</v>
+        <v>237.6751696808052</v>
       </c>
       <c r="Q57">
-        <v>348.3067644308052</v>
+        <v>370.2751696808052</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1161879484806054</v>
+        <v>0.1161550766147142</v>
       </c>
       <c r="T57">
         <v>1.371351395056018</v>
       </c>
       <c r="U57">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.06235246249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.547191897459838</v>
+        <v>3.023631443611903</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08665214544695335</v>
+        <v>0.08441139598364911</v>
       </c>
       <c r="C58">
-        <v>1581.618495228124</v>
+        <v>1667.200543699896</v>
       </c>
       <c r="D58">
-        <v>3635.042495228125</v>
+        <v>3720.624543699897</v>
       </c>
       <c r="E58">
         <v>1306.724</v>
@@ -6043,37 +6043,37 @@
         <v>473.5</v>
       </c>
       <c r="M58">
-        <v>189.270816772725</v>
+        <v>177.2047095727251</v>
       </c>
       <c r="N58">
-        <v>284.229183227275</v>
+        <v>296.2952904272749</v>
       </c>
       <c r="O58">
-        <v>71.05729580681874</v>
+        <v>74.07382260681874</v>
       </c>
       <c r="P58">
-        <v>213.1718874204562</v>
+        <v>222.2214678204562</v>
       </c>
       <c r="Q58">
-        <v>345.7718874204563</v>
+        <v>354.8214678204562</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1175790146561115</v>
+        <v>0.1175454931486018</v>
       </c>
       <c r="T58">
         <v>1.398453201282422</v>
       </c>
       <c r="U58">
-        <v>0.08313661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.06235246249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.501706327862341</v>
+        <v>2.672050879131262</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08873510970433895</v>
+        <v>0.08444540311738154</v>
       </c>
       <c r="C59">
-        <v>1464.324369174611</v>
+        <v>1625.207909972298</v>
       </c>
       <c r="D59">
-        <v>3558.402369174611</v>
+        <v>3719.285909972299</v>
       </c>
       <c r="E59">
         <v>1347.378</v>
@@ -6125,45 +6125,45 @@
         <v>473.5</v>
       </c>
       <c r="M59">
-        <v>203.5418593865237</v>
+        <v>180.3690793865237</v>
       </c>
       <c r="N59">
-        <v>269.9581406134763</v>
+        <v>293.1309206134763</v>
       </c>
       <c r="O59">
-        <v>67.48953515336908</v>
+        <v>73.28273015336907</v>
       </c>
       <c r="P59">
-        <v>202.4686054601072</v>
+        <v>219.8481904601072</v>
       </c>
       <c r="Q59">
-        <v>335.0686054601073</v>
+        <v>352.4481904601072</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1190347815839666</v>
+        <v>0.1190005802189493</v>
       </c>
       <c r="T59">
         <v>1.426815556635635</v>
       </c>
       <c r="U59">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.326302812734106</v>
+        <v>2.625172793532468</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08884407396172458</v>
+        <v>0.08447941025111395</v>
       </c>
       <c r="C60">
-        <v>1419.750015173199</v>
+        <v>1583.216239145285</v>
       </c>
       <c r="D60">
-        <v>3554.482015173199</v>
+        <v>3717.948239145285</v>
       </c>
       <c r="E60">
         <v>1388.032</v>
@@ -6207,45 +6207,45 @@
         <v>473.5</v>
       </c>
       <c r="M60">
-        <v>207.1127692003223</v>
+        <v>183.5334492003224</v>
       </c>
       <c r="N60">
-        <v>266.3872307996777</v>
+        <v>289.9665507996776</v>
       </c>
       <c r="O60">
-        <v>66.59680769991942</v>
+        <v>72.49163769991941</v>
       </c>
       <c r="P60">
-        <v>199.7904230997583</v>
+        <v>217.4749130997582</v>
       </c>
       <c r="Q60">
-        <v>332.3904230997583</v>
+        <v>350.0749130997582</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1205598707464815</v>
+        <v>0.1205249571497896</v>
       </c>
       <c r="T60">
         <v>1.456528500339</v>
       </c>
       <c r="U60">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.286194143549036</v>
+        <v>2.579911193643977</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08895303821911019</v>
+        <v>0.08451341738484638</v>
       </c>
       <c r="C61">
-        <v>1375.184289910221</v>
+        <v>1541.225530180282</v>
       </c>
       <c r="D61">
-        <v>3550.570289910221</v>
+        <v>3716.611530180282</v>
       </c>
       <c r="E61">
         <v>1428.686</v>
@@ -6289,45 +6289,45 @@
         <v>473.5</v>
       </c>
       <c r="M61">
-        <v>210.683679014121</v>
+        <v>186.697819014121</v>
       </c>
       <c r="N61">
-        <v>262.816320985879</v>
+        <v>286.802180985879</v>
       </c>
       <c r="O61">
-        <v>65.70408024646976</v>
+        <v>71.70054524646974</v>
       </c>
       <c r="P61">
-        <v>197.1122407394093</v>
+        <v>215.1016357394092</v>
       </c>
       <c r="Q61">
-        <v>329.7122407394093</v>
+        <v>347.7016357394093</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1221593545022898</v>
+        <v>0.1221236939309147</v>
       </c>
       <c r="T61">
         <v>1.487690855930335</v>
       </c>
       <c r="U61">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.247445090268544</v>
+        <v>2.536183885277131</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08906200247649579</v>
+        <v>0.08630242451857881</v>
       </c>
       <c r="C62">
-        <v>1330.627164929083</v>
+        <v>1431.581656449361</v>
       </c>
       <c r="D62">
-        <v>3546.667164929083</v>
+        <v>3647.621656449361</v>
       </c>
       <c r="E62">
         <v>1469.34</v>
@@ -6371,37 +6371,37 @@
         <v>473.5</v>
       </c>
       <c r="M62">
-        <v>214.2545888279196</v>
+        <v>199.3752248279197</v>
       </c>
       <c r="N62">
-        <v>259.2454111720804</v>
+        <v>274.1247751720804</v>
       </c>
       <c r="O62">
-        <v>64.81135279302009</v>
+        <v>68.53119379302009</v>
       </c>
       <c r="P62">
-        <v>194.4340583790603</v>
+        <v>205.5935813790603</v>
       </c>
       <c r="Q62">
-        <v>327.0340583790603</v>
+        <v>338.1935813790603</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1238388124458886</v>
+        <v>0.1238023675510961</v>
       </c>
       <c r="T62">
         <v>1.520411329301237</v>
       </c>
       <c r="U62">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.209987672097402</v>
+        <v>2.374918951984515</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08917096673388139</v>
+        <v>0.08636568165231123</v>
       </c>
       <c r="C63">
-        <v>1286.078611898184</v>
+        <v>1388.535109619098</v>
       </c>
       <c r="D63">
-        <v>3542.772611898184</v>
+        <v>3645.229109619098</v>
       </c>
       <c r="E63">
         <v>1509.994</v>
@@ -6453,37 +6453,37 @@
         <v>473.5</v>
       </c>
       <c r="M63">
-        <v>217.8254986417183</v>
+        <v>202.6981452417183</v>
       </c>
       <c r="N63">
-        <v>255.6745013582817</v>
+        <v>270.8018547582817</v>
       </c>
       <c r="O63">
-        <v>63.91862533957043</v>
+        <v>67.70046368957043</v>
       </c>
       <c r="P63">
-        <v>191.7558760187113</v>
+        <v>203.1013910687113</v>
       </c>
       <c r="Q63">
-        <v>324.3558760187113</v>
+        <v>335.7013910687113</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.125604396437877</v>
+        <v>0.1255671269979535</v>
       </c>
       <c r="T63">
         <v>1.554809775665519</v>
       </c>
       <c r="U63">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.173758365997444</v>
+        <v>2.335985854410998</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08927993099126701</v>
+        <v>0.08642893878604366</v>
       </c>
       <c r="C64">
-        <v>1241.538602610227</v>
+        <v>1345.491699368595</v>
       </c>
       <c r="D64">
-        <v>3538.886602610227</v>
+        <v>3642.839699368596</v>
       </c>
       <c r="E64">
         <v>1550.648</v>
@@ -6535,37 +6535,37 @@
         <v>473.5</v>
       </c>
       <c r="M64">
-        <v>221.396408455517</v>
+        <v>206.021065655517</v>
       </c>
       <c r="N64">
-        <v>252.103591544483</v>
+        <v>267.478934344483</v>
       </c>
       <c r="O64">
-        <v>63.02589788612075</v>
+        <v>66.86973358612074</v>
       </c>
       <c r="P64">
-        <v>189.0776936583623</v>
+        <v>200.6092007583622</v>
       </c>
       <c r="Q64">
-        <v>321.6776936583623</v>
+        <v>333.2092007583623</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.127462905903128</v>
+        <v>0.1274247685209613</v>
       </c>
       <c r="T64">
         <v>1.591018666575289</v>
       </c>
       <c r="U64">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.138697747191033</v>
+        <v>2.298308663210821</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08938889524865262</v>
+        <v>0.08649219591977605</v>
       </c>
       <c r="C65">
-        <v>1197.007108981542</v>
+        <v>1302.451419533905</v>
       </c>
       <c r="D65">
-        <v>3535.009108981542</v>
+        <v>3640.453419533905</v>
       </c>
       <c r="E65">
         <v>1591.302</v>
@@ -6617,37 +6617,37 @@
         <v>473.5</v>
       </c>
       <c r="M65">
-        <v>224.9673182693157</v>
+        <v>209.3439860693157</v>
       </c>
       <c r="N65">
-        <v>248.5326817306843</v>
+        <v>264.1560139306844</v>
       </c>
       <c r="O65">
-        <v>62.13317043267109</v>
+        <v>66.03900348267109</v>
       </c>
       <c r="P65">
-        <v>186.3995112980133</v>
+        <v>198.1170104480133</v>
       </c>
       <c r="Q65">
-        <v>318.9995112980133</v>
+        <v>330.7170104480133</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1294218753394737</v>
+        <v>0.1293828230992668</v>
       </c>
       <c r="T65">
         <v>1.629184794831533</v>
       </c>
       <c r="U65">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.104750163902287</v>
+        <v>2.261827573318586</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08949785950603822</v>
+        <v>0.08655545305350848</v>
       </c>
       <c r="C66">
-        <v>1152.484103051407</v>
+        <v>1259.414263967219</v>
       </c>
       <c r="D66">
-        <v>3531.140103051408</v>
+        <v>3638.070263967219</v>
       </c>
       <c r="E66">
         <v>1631.956</v>
@@ -6699,37 +6699,37 @@
         <v>473.5</v>
       </c>
       <c r="M66">
-        <v>228.5382280831143</v>
+        <v>212.6669064831143</v>
       </c>
       <c r="N66">
-        <v>244.9617719168857</v>
+        <v>260.8330935168857</v>
       </c>
       <c r="O66">
-        <v>61.24044297922142</v>
+        <v>65.20827337922142</v>
       </c>
       <c r="P66">
-        <v>183.7213289376643</v>
+        <v>195.6248201376643</v>
       </c>
       <c r="Q66">
-        <v>316.3213289376642</v>
+        <v>328.2248201376643</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1314896764111718</v>
+        <v>0.1314496584874781</v>
       </c>
       <c r="T66">
         <v>1.669471263546457</v>
       </c>
       <c r="U66">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.071863442591313</v>
+        <v>2.226486517485482</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08960682376342383</v>
+        <v>0.0866187101872409</v>
       </c>
       <c r="C67">
-        <v>1107.969556981376</v>
+        <v>1216.380226536819</v>
       </c>
       <c r="D67">
-        <v>3527.279556981376</v>
+        <v>3635.69022653682</v>
       </c>
       <c r="E67">
         <v>1672.61</v>
@@ -6781,37 +6781,37 @@
         <v>473.5</v>
       </c>
       <c r="M67">
-        <v>232.109137896913</v>
+        <v>215.989826896913</v>
       </c>
       <c r="N67">
-        <v>241.390862103087</v>
+        <v>257.510173103087</v>
       </c>
       <c r="O67">
-        <v>60.34771552577175</v>
+        <v>64.37754327577176</v>
       </c>
       <c r="P67">
-        <v>181.0431465773153</v>
+        <v>193.1326298273153</v>
       </c>
       <c r="Q67">
-        <v>313.6431465773153</v>
+        <v>325.7326298273153</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1336756375441099</v>
+        <v>0.1336345987550158</v>
       </c>
       <c r="T67">
         <v>1.712059816187948</v>
       </c>
       <c r="U67">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.039988620397601</v>
+        <v>2.192232878754937</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08971578802080943</v>
+        <v>0.08668196732097333</v>
       </c>
       <c r="C68">
-        <v>1063.46344305461</v>
+        <v>1173.349301127022</v>
       </c>
       <c r="D68">
-        <v>3523.427443054611</v>
+        <v>3633.313301127022</v>
       </c>
       <c r="E68">
         <v>1713.264</v>
@@ -6863,37 +6863,37 @@
         <v>473.5</v>
       </c>
       <c r="M68">
-        <v>235.6800477107116</v>
+        <v>219.3127473107116</v>
       </c>
       <c r="N68">
-        <v>237.8199522892884</v>
+        <v>254.1872526892884</v>
       </c>
       <c r="O68">
-        <v>59.45498807232209</v>
+        <v>63.54681317232209</v>
       </c>
       <c r="P68">
-        <v>178.3649642169663</v>
+        <v>190.6404395169663</v>
       </c>
       <c r="Q68">
-        <v>310.9649642169663</v>
+        <v>323.2404395169663</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1359901846260443</v>
+        <v>0.135948064920644</v>
       </c>
       <c r="T68">
         <v>1.757153577808351</v>
       </c>
       <c r="U68">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.009079701906728</v>
+        <v>2.159017229076832</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.09801550227819503</v>
+        <v>0.08674522445470575</v>
       </c>
       <c r="C69">
-        <v>752.2258066465502</v>
+        <v>1130.321481638126</v>
       </c>
       <c r="D69">
-        <v>3252.843806646551</v>
+        <v>3630.939481638127</v>
       </c>
       <c r="E69">
         <v>1753.918</v>
@@ -6945,45 +6945,45 @@
         <v>473.5</v>
       </c>
       <c r="M69">
-        <v>283.6491909245103</v>
+        <v>222.6356677245103</v>
       </c>
       <c r="N69">
-        <v>189.8508090754897</v>
+        <v>250.8643322754897</v>
       </c>
       <c r="O69">
-        <v>47.46270226887242</v>
+        <v>62.71608306887242</v>
       </c>
       <c r="P69">
-        <v>142.3881068066173</v>
+        <v>188.1482492066173</v>
       </c>
       <c r="Q69">
-        <v>274.9881068066173</v>
+        <v>320.7482492066173</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.138445007288702</v>
+        <v>0.1384017411569163</v>
       </c>
       <c r="T69">
         <v>1.804980294678475</v>
       </c>
       <c r="U69">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.669315531825423</v>
+        <v>2.126793091329416</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09824671653558065</v>
+        <v>0.08680848158843818</v>
       </c>
       <c r="C70">
-        <v>704.6275982063476</v>
+        <v>1087.296761986361</v>
       </c>
       <c r="D70">
-        <v>3245.899598206348</v>
+        <v>3628.568761986362</v>
       </c>
       <c r="E70">
         <v>1794.572</v>
@@ -7027,45 +7027,45 @@
         <v>473.5</v>
       </c>
       <c r="M70">
-        <v>287.882760938309</v>
+        <v>225.958588138309</v>
       </c>
       <c r="N70">
-        <v>185.617239061691</v>
+        <v>247.541411861691</v>
       </c>
       <c r="O70">
-        <v>46.40430976542275</v>
+        <v>61.88535296542275</v>
       </c>
       <c r="P70">
-        <v>139.2129292962683</v>
+        <v>185.6560588962683</v>
       </c>
       <c r="Q70">
-        <v>271.8129292962683</v>
+        <v>318.2560588962683</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1410532563677758</v>
+        <v>0.1410087721579556</v>
       </c>
       <c r="T70">
         <v>1.855796181352981</v>
       </c>
       <c r="U70">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.644766774004461</v>
+        <v>2.095516722339278</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09847793079296627</v>
+        <v>0.08687173872217059</v>
       </c>
       <c r="C71">
-        <v>657.0589757580169</v>
+        <v>1044.275136103835</v>
       </c>
       <c r="D71">
-        <v>3238.984975758017</v>
+        <v>3626.201136103835</v>
       </c>
       <c r="E71">
         <v>1835.226</v>
@@ -7109,45 +7109,45 @@
         <v>473.5</v>
       </c>
       <c r="M71">
-        <v>292.1163309521077</v>
+        <v>229.2815085521076</v>
       </c>
       <c r="N71">
-        <v>181.3836690478923</v>
+        <v>244.2184914478924</v>
       </c>
       <c r="O71">
-        <v>45.34591726197309</v>
+        <v>61.05462286197309</v>
       </c>
       <c r="P71">
-        <v>136.0377517859193</v>
+        <v>183.1638685859193</v>
       </c>
       <c r="Q71">
-        <v>268.6377517859192</v>
+        <v>315.7638685859193</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1438297795809834</v>
+        <v>0.143783998707449</v>
       </c>
       <c r="T71">
         <v>1.909890512329069</v>
       </c>
       <c r="U71">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.620929574381208</v>
+        <v>2.065146914769143</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09870914505035186</v>
+        <v>0.086934995855903</v>
       </c>
       <c r="C72">
-        <v>609.5197506255868</v>
+        <v>1001.256597938482</v>
       </c>
       <c r="D72">
-        <v>3232.099750625587</v>
+        <v>3623.836597938482</v>
       </c>
       <c r="E72">
         <v>1875.88</v>
@@ -7191,45 +7191,45 @@
         <v>473.5</v>
       </c>
       <c r="M72">
-        <v>296.3499009659063</v>
+        <v>232.6044289659063</v>
       </c>
       <c r="N72">
-        <v>177.1500990340937</v>
+        <v>240.8955710340937</v>
       </c>
       <c r="O72">
-        <v>44.28752475852342</v>
+        <v>60.22389275852343</v>
       </c>
       <c r="P72">
-        <v>132.8625742755702</v>
+        <v>180.6716782755703</v>
       </c>
       <c r="Q72">
-        <v>265.4625742755703</v>
+        <v>313.2716782755703</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1467914043417382</v>
+        <v>0.1467442403602421</v>
       </c>
       <c r="T72">
         <v>1.967591132036896</v>
       </c>
       <c r="U72">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.597773437604334</v>
+        <v>2.035644815986727</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.09894035930773748</v>
+        <v>0.08699825298963546</v>
       </c>
       <c r="C73">
-        <v>562.0097357339791</v>
+        <v>958.2411414540102</v>
       </c>
       <c r="D73">
-        <v>3225.243735733979</v>
+        <v>3621.47514145401</v>
       </c>
       <c r="E73">
         <v>1916.534</v>
@@ -7273,45 +7273,45 @@
         <v>473.5</v>
       </c>
       <c r="M73">
-        <v>300.5834709797049</v>
+        <v>235.9273493797049</v>
       </c>
       <c r="N73">
-        <v>172.9165290202951</v>
+        <v>237.5726506202951</v>
       </c>
       <c r="O73">
-        <v>43.22913225507376</v>
+        <v>59.39316265507377</v>
       </c>
       <c r="P73">
-        <v>129.6873967652213</v>
+        <v>178.1794879652213</v>
       </c>
       <c r="Q73">
-        <v>262.2873967652213</v>
+        <v>310.7794879652213</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1499572790859934</v>
+        <v>0.1499086366097794</v>
       </c>
       <c r="T73">
         <v>2.029271104828021</v>
       </c>
       <c r="U73">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.57526958637047</v>
+        <v>2.006973762240436</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09917157356512307</v>
+        <v>0.09472951012336786</v>
       </c>
       <c r="C74">
-        <v>514.5287455920734</v>
+        <v>650.4360433405727</v>
       </c>
       <c r="D74">
-        <v>3218.416745592073</v>
+        <v>3354.324043340573</v>
       </c>
       <c r="E74">
         <v>1957.188</v>
@@ -7355,37 +7355,37 @@
         <v>473.5</v>
       </c>
       <c r="M74">
-        <v>304.8170409935036</v>
+        <v>280.8149193935036</v>
       </c>
       <c r="N74">
-        <v>168.6829590064964</v>
+        <v>192.6850806064964</v>
       </c>
       <c r="O74">
-        <v>42.17073975162411</v>
+        <v>48.1712701516241</v>
       </c>
       <c r="P74">
-        <v>126.5122192548723</v>
+        <v>144.5138104548723</v>
       </c>
       <c r="Q74">
-        <v>259.1122192548723</v>
+        <v>277.1138104548724</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1533492877405524</v>
+        <v>0.1532990611628552</v>
       </c>
       <c r="T74">
         <v>2.095356789961369</v>
       </c>
       <c r="U74">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.07810246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.553390842115325</v>
+        <v>1.686163972422307</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.09940278782250868</v>
+        <v>0.09489926725710028</v>
       </c>
       <c r="C75">
-        <v>467.0765962759715</v>
+        <v>604.3576458696302</v>
       </c>
       <c r="D75">
-        <v>3211.618596275972</v>
+        <v>3348.899645869631</v>
       </c>
       <c r="E75">
         <v>1997.842</v>
@@ -7437,37 +7437,37 @@
         <v>473.5</v>
       </c>
       <c r="M75">
-        <v>309.0506110073023</v>
+        <v>284.7151266073023</v>
       </c>
       <c r="N75">
-        <v>164.4493889926977</v>
+        <v>188.7848733926977</v>
       </c>
       <c r="O75">
-        <v>41.11234724817443</v>
+        <v>47.19621834817443</v>
       </c>
       <c r="P75">
-        <v>123.3370417445233</v>
+        <v>141.5886550445233</v>
       </c>
       <c r="Q75">
-        <v>255.9370417445233</v>
+        <v>274.1886550445233</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1569925562954491</v>
+        <v>0.156940628275418</v>
       </c>
       <c r="T75">
         <v>2.166337711030521</v>
       </c>
       <c r="U75">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.07810246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.532111515511005</v>
+        <v>1.663065835813782</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09963400207989428</v>
+        <v>0.0950690243908327</v>
       </c>
       <c r="C76">
-        <v>419.6531054124889</v>
+        <v>558.2967640481124</v>
       </c>
       <c r="D76">
-        <v>3204.849105412489</v>
+        <v>3343.492764048113</v>
       </c>
       <c r="E76">
         <v>2038.496</v>
@@ -7519,37 +7519,37 @@
         <v>473.5</v>
       </c>
       <c r="M76">
-        <v>313.2841810211009</v>
+        <v>288.6153338211009</v>
       </c>
       <c r="N76">
-        <v>160.2158189788991</v>
+        <v>184.8846661788991</v>
       </c>
       <c r="O76">
-        <v>40.05395474472476</v>
+        <v>46.22116654472477</v>
       </c>
       <c r="P76">
-        <v>120.1618642341743</v>
+        <v>138.6634996341743</v>
       </c>
       <c r="Q76">
-        <v>252.7618642341743</v>
+        <v>271.2634996341743</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1609160762776456</v>
+        <v>0.1608623159351011</v>
       </c>
       <c r="T76">
         <v>2.242778702951146</v>
       </c>
       <c r="U76">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.07810246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.511407305841937</v>
+        <v>1.64059197316765</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1399016128156171</v>
+        <v>0.09523878152456514</v>
       </c>
       <c r="C77">
-        <v>-481.5656882940066</v>
+        <v>512.2533131744167</v>
       </c>
       <c r="D77">
-        <v>2344.284311705994</v>
+        <v>3338.103313174417</v>
       </c>
       <c r="E77">
         <v>2079.15</v>
@@ -7601,45 +7601,45 @@
         <v>473.5</v>
       </c>
       <c r="M77">
-        <v>516.9256210348997</v>
+        <v>292.5155410348996</v>
       </c>
       <c r="N77">
-        <v>-43.42562103489968</v>
+        <v>180.9844589651004</v>
       </c>
       <c r="O77">
-        <v>-10.85640525872492</v>
+        <v>45.24611474127509</v>
       </c>
       <c r="P77">
-        <v>-32.56921577617476</v>
+        <v>135.7383442238253</v>
       </c>
       <c r="Q77">
-        <v>100.0307842238253</v>
+        <v>268.3383442238253</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1674673052646333</v>
+        <v>0.1650977386075588</v>
       </c>
       <c r="T77">
-        <v>2.370414714577659</v>
+        <v>2.325334974225422</v>
       </c>
       <c r="U77">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V77">
-        <v>0.2289981289049088</v>
+        <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.130713048665945</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.9159925156196352</v>
+        <v>1.618717413525415</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1411389789822424</v>
+        <v>0.09540853865829754</v>
       </c>
       <c r="C78">
-        <v>-541.4046036363266</v>
+        <v>466.227209092192</v>
       </c>
       <c r="D78">
-        <v>2325.099396363674</v>
+        <v>3332.731209092192</v>
       </c>
       <c r="E78">
         <v>2119.804</v>
@@ -7683,45 +7683,45 @@
         <v>473.5</v>
       </c>
       <c r="M78">
-        <v>523.8179626486983</v>
+        <v>296.4157482486983</v>
       </c>
       <c r="N78">
-        <v>-50.31796264869831</v>
+        <v>177.0842517513017</v>
       </c>
       <c r="O78">
-        <v>-12.57949066217458</v>
+        <v>44.27106293782543</v>
       </c>
       <c r="P78">
-        <v>-37.73847198652373</v>
+        <v>132.8131888134763</v>
       </c>
       <c r="Q78">
-        <v>94.86152801347629</v>
+        <v>265.4131888134763</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1725367763173263</v>
+        <v>0.169686113169388</v>
       </c>
       <c r="T78">
-        <v>2.469181994351728</v>
+        <v>2.414770934772553</v>
       </c>
       <c r="U78">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V78">
-        <v>0.2259849956298442</v>
+        <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.1312238850869528</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.9039399825193769</v>
+        <v>1.597418500189554</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1423763451488678</v>
+        <v>0.09557829579202998</v>
       </c>
       <c r="C79">
-        <v>-600.9320607438794</v>
+        <v>420.2183681859547</v>
       </c>
       <c r="D79">
-        <v>2306.225939256121</v>
+        <v>3327.376368185955</v>
       </c>
       <c r="E79">
         <v>2160.458</v>
@@ -7765,45 +7765,45 @@
         <v>473.5</v>
       </c>
       <c r="M79">
-        <v>530.7103042624969</v>
+        <v>300.315955462497</v>
       </c>
       <c r="N79">
-        <v>-57.21030426249695</v>
+        <v>173.184044537503</v>
       </c>
       <c r="O79">
-        <v>-14.30257606562424</v>
+        <v>43.29601113437576</v>
       </c>
       <c r="P79">
-        <v>-42.90772819687271</v>
+        <v>129.8880334031273</v>
       </c>
       <c r="Q79">
-        <v>89.69227180312731</v>
+        <v>262.4880334031273</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1780470709398188</v>
+        <v>0.1746734768235502</v>
       </c>
       <c r="T79">
-        <v>2.576537733236585</v>
+        <v>2.511983935367262</v>
       </c>
       <c r="U79">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V79">
-        <v>0.2230501255567294</v>
+        <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.1317214530294928</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.8922005022269175</v>
+        <v>1.576672805381897</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1436137113154931</v>
+        <v>0.09574805292576238</v>
       </c>
       <c r="C80">
-        <v>-660.1555831171513</v>
+        <v>374.2267073767566</v>
       </c>
       <c r="D80">
-        <v>2287.656416882849</v>
+        <v>3322.038707376757</v>
       </c>
       <c r="E80">
         <v>2201.112</v>
@@ -7847,45 +7847,45 @@
         <v>473.5</v>
       </c>
       <c r="M80">
-        <v>537.6026458762957</v>
+        <v>304.2161626762956</v>
       </c>
       <c r="N80">
-        <v>-64.1026458762957</v>
+        <v>169.2838373237044</v>
       </c>
       <c r="O80">
-        <v>-16.02566146907392</v>
+        <v>42.3209593309261</v>
       </c>
       <c r="P80">
-        <v>-48.07698440722177</v>
+        <v>126.9628779927783</v>
       </c>
       <c r="Q80">
-        <v>84.52301559277825</v>
+        <v>259.5628779927783</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1840583014370833</v>
+        <v>0.1801142371735452</v>
       </c>
       <c r="T80">
-        <v>2.69365308474734</v>
+        <v>2.61803448147058</v>
       </c>
       <c r="U80">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V80">
-        <v>0.2201905085624123</v>
+        <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.13220626281966</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.8807620342496493</v>
+        <v>1.556459051466745</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1448510774821185</v>
+        <v>0.09591781005949482</v>
       </c>
       <c r="C81">
-        <v>-719.0824538779584</v>
+        <v>328.2521441178824</v>
       </c>
       <c r="D81">
-        <v>2269.383546122042</v>
+        <v>3316.718144117883</v>
       </c>
       <c r="E81">
         <v>2241.766</v>
@@ -7929,45 +7929,45 @@
         <v>473.5</v>
       </c>
       <c r="M81">
-        <v>544.4949874900943</v>
+        <v>308.1163698900942</v>
       </c>
       <c r="N81">
-        <v>-70.99498749009433</v>
+        <v>165.3836301099058</v>
       </c>
       <c r="O81">
-        <v>-17.74874687252358</v>
+        <v>41.34590752747644</v>
       </c>
       <c r="P81">
-        <v>-53.24624061757075</v>
+        <v>124.0377225824293</v>
       </c>
       <c r="Q81">
-        <v>79.35375938242927</v>
+        <v>256.6377225824293</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1906420300769444</v>
+        <v>0.1860731651759208</v>
       </c>
       <c r="T81">
-        <v>2.821922279259118</v>
+        <v>2.734185079583738</v>
       </c>
       <c r="U81">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V81">
-        <v>0.21740328693504</v>
+        <v>0.25</v>
       </c>
       <c r="W81">
-        <v>0.1326787989442533</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8696131477401601</v>
+        <v>1.536757038157039</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1460884436487438</v>
+        <v>0.09608756719322724</v>
       </c>
       <c r="C82">
-        <v>-777.7197252936076</v>
+        <v>282.2945963905995</v>
       </c>
       <c r="D82">
-        <v>2251.400274706393</v>
+        <v>3311.4145963906</v>
       </c>
       <c r="E82">
         <v>2282.42</v>
@@ -8011,45 +8011,45 @@
         <v>473.5</v>
       </c>
       <c r="M82">
-        <v>551.387329103893</v>
+        <v>312.0165771038929</v>
       </c>
       <c r="N82">
-        <v>-77.88732910389297</v>
+        <v>161.4834228961071</v>
       </c>
       <c r="O82">
-        <v>-19.47183227597324</v>
+        <v>40.37085572402677</v>
       </c>
       <c r="P82">
-        <v>-58.41549682791972</v>
+        <v>121.1125671720803</v>
       </c>
       <c r="Q82">
-        <v>74.1845031720803</v>
+        <v>253.7125671720803</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1978841315807916</v>
+        <v>0.1926279859785339</v>
       </c>
       <c r="T82">
-        <v>2.963018393222073</v>
+        <v>2.861950737508212</v>
       </c>
       <c r="U82">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V82">
-        <v>0.214685745848352</v>
+        <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.1331395216657318</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.8587429833934082</v>
+        <v>1.517547575180076</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1473258098153691</v>
+        <v>0.1330101660175697</v>
       </c>
       <c r="C83">
-        <v>-836.0742278517828</v>
+        <v>-612.859602256533</v>
       </c>
       <c r="D83">
-        <v>2233.699772148218</v>
+        <v>2456.914397743467</v>
       </c>
       <c r="E83">
         <v>2323.074</v>
@@ -8093,37 +8093,37 @@
         <v>473.5</v>
       </c>
       <c r="M83">
-        <v>558.2796707176916</v>
+        <v>502.9577075176916</v>
       </c>
       <c r="N83">
-        <v>-84.7796707176916</v>
+        <v>-29.45770751769157</v>
       </c>
       <c r="O83">
-        <v>-21.1949176794229</v>
+        <v>-7.364426879422894</v>
       </c>
       <c r="P83">
-        <v>-63.5847530382687</v>
+        <v>-22.09328063826868</v>
       </c>
       <c r="Q83">
-        <v>69.01524696173132</v>
+        <v>110.5067193617313</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.205888559558728</v>
+        <v>0.2021641185176785</v>
       </c>
       <c r="T83">
-        <v>3.118966729707446</v>
+        <v>3.047827710290302</v>
       </c>
       <c r="U83">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V83">
-        <v>0.2120353045415823</v>
+        <v>0.2353577611609345</v>
       </c>
       <c r="W83">
-        <v>0.1335888685175442</v>
+        <v>0.1167888685175442</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.848141218166329</v>
+        <v>0.9414310446437379</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1485631759819944</v>
+        <v>0.134079532184195</v>
       </c>
       <c r="C84">
-        <v>-894.1525789106936</v>
+        <v>-671.739507835227</v>
       </c>
       <c r="D84">
-        <v>2216.275421089307</v>
+        <v>2438.688492164773</v>
       </c>
       <c r="E84">
         <v>2363.728</v>
@@ -8175,37 +8175,37 @@
         <v>473.5</v>
       </c>
       <c r="M84">
-        <v>565.1720123314902</v>
+        <v>509.1670619314903</v>
       </c>
       <c r="N84">
-        <v>-91.67201233149024</v>
+        <v>-35.66706193149025</v>
       </c>
       <c r="O84">
-        <v>-22.91800308287256</v>
+        <v>-8.916765482872563</v>
       </c>
       <c r="P84">
-        <v>-68.75400924861768</v>
+        <v>-26.75029644861769</v>
       </c>
       <c r="Q84">
-        <v>63.84599075138235</v>
+        <v>105.8497035513823</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2147823684231017</v>
+        <v>0.2108510139908829</v>
       </c>
       <c r="T84">
-        <v>3.292242659135637</v>
+        <v>3.217151471973096</v>
       </c>
       <c r="U84">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V84">
-        <v>0.2094495081447337</v>
+        <v>0.2324875445614109</v>
       </c>
       <c r="W84">
-        <v>0.1340272556900441</v>
+        <v>0.1172272556900441</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8377980325789348</v>
+        <v>0.9299501782456436</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1498005421486198</v>
+        <v>0.1351488983508204</v>
       </c>
       <c r="C85">
-        <v>-951.9611909474925</v>
+        <v>-730.3509974104177</v>
       </c>
       <c r="D85">
-        <v>2199.120809052508</v>
+        <v>2420.731002589583</v>
       </c>
       <c r="E85">
         <v>2404.382</v>
@@ -8257,37 +8257,37 @@
         <v>473.5</v>
       </c>
       <c r="M85">
-        <v>572.064353945289</v>
+        <v>515.3764163452889</v>
       </c>
       <c r="N85">
-        <v>-98.56435394528899</v>
+        <v>-41.87641634528893</v>
       </c>
       <c r="O85">
-        <v>-24.64108848632225</v>
+        <v>-10.46910408632223</v>
       </c>
       <c r="P85">
-        <v>-73.92326545896674</v>
+        <v>-31.4073122589667</v>
       </c>
       <c r="Q85">
-        <v>58.67673454103328</v>
+        <v>101.1926877410333</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2247225077421078</v>
+        <v>0.2205598971668172</v>
       </c>
       <c r="T85">
-        <v>3.48590399202597</v>
+        <v>3.406395676206808</v>
       </c>
       <c r="U85">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V85">
-        <v>0.2069260200947971</v>
+        <v>0.2296864898076589</v>
       </c>
       <c r="W85">
-        <v>0.1344550793162187</v>
+        <v>0.1176550793162187</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8277040803791884</v>
+        <v>0.9187459592306357</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1510379083152452</v>
+        <v>0.1362182645174458</v>
       </c>
       <c r="C86">
-        <v>-1009.506279426563</v>
+        <v>-788.6999571508341</v>
       </c>
       <c r="D86">
-        <v>2182.229720573437</v>
+        <v>2403.036042849166</v>
       </c>
       <c r="E86">
         <v>2445.036</v>
@@ -8339,37 +8339,37 @@
         <v>473.5</v>
       </c>
       <c r="M86">
-        <v>578.9566955590876</v>
+        <v>521.5857707590876</v>
       </c>
       <c r="N86">
-        <v>-105.4566955590876</v>
+        <v>-48.08577075908761</v>
       </c>
       <c r="O86">
-        <v>-26.36417388977191</v>
+        <v>-12.0214426897719</v>
       </c>
       <c r="P86">
-        <v>-79.09252166931572</v>
+        <v>-36.06432806931571</v>
       </c>
       <c r="Q86">
-        <v>53.50747833068431</v>
+        <v>96.53567193068432</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2359051644759894</v>
+        <v>0.2314823907397432</v>
       </c>
       <c r="T86">
-        <v>3.703772991527591</v>
+        <v>3.619295405969733</v>
       </c>
       <c r="U86">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V86">
-        <v>0.2044626150936686</v>
+        <v>0.2269521268337582</v>
       </c>
       <c r="W86">
-        <v>0.1348727166655796</v>
+        <v>0.1180727166655796</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8178504603746743</v>
+        <v>0.9078085073350329</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1522752744818705</v>
+        <v>0.1372876306840711</v>
       </c>
       <c r="C87">
-        <v>-1066.793870307967</v>
+        <v>-846.7921023682329</v>
       </c>
       <c r="D87">
-        <v>2165.596129692034</v>
+        <v>2385.597897631767</v>
       </c>
       <c r="E87">
         <v>2485.69</v>
@@ -8421,37 +8421,37 @@
         <v>473.5</v>
       </c>
       <c r="M87">
-        <v>585.8490371728863</v>
+        <v>527.7951251728863</v>
       </c>
       <c r="N87">
-        <v>-112.3490371728863</v>
+        <v>-54.29512517288629</v>
       </c>
       <c r="O87">
-        <v>-28.08725929322156</v>
+        <v>-13.57378129322157</v>
       </c>
       <c r="P87">
-        <v>-84.26177787966469</v>
+        <v>-40.72134387966472</v>
       </c>
       <c r="Q87">
-        <v>48.33822212033533</v>
+        <v>91.87865612033531</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2485788421077221</v>
+        <v>0.2438612167890594</v>
       </c>
       <c r="T87">
-        <v>3.950691190962764</v>
+        <v>3.860581766367715</v>
       </c>
       <c r="U87">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V87">
-        <v>0.2020571725631549</v>
+        <v>0.2242821018121846</v>
       </c>
       <c r="W87">
-        <v>0.135280527253779</v>
+        <v>0.118480527253779</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8082286902526195</v>
+        <v>0.8971284072487384</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1998894749821006</v>
+        <v>0.1383569968506964</v>
       </c>
       <c r="C88">
-        <v>-1598.581116657556</v>
+        <v>-904.6329836720365</v>
       </c>
       <c r="D88">
-        <v>1674.462883342444</v>
+        <v>2368.411016327964</v>
       </c>
       <c r="E88">
         <v>2526.344</v>
@@ -8503,45 +8503,45 @@
         <v>473.5</v>
       </c>
       <c r="M88">
-        <v>775.2453155866849</v>
+        <v>534.0044795866849</v>
       </c>
       <c r="N88">
-        <v>-301.7453155866849</v>
+        <v>-60.50447958668485</v>
       </c>
       <c r="O88">
-        <v>-75.43632889667123</v>
+        <v>-15.12611989667121</v>
       </c>
       <c r="P88">
-        <v>-226.3089866900137</v>
+        <v>-45.37835969001364</v>
       </c>
       <c r="Q88">
-        <v>-93.70898669001366</v>
+        <v>87.22164030998638</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.273669004641165</v>
+        <v>0.2580084465597065</v>
       </c>
       <c r="T88">
-        <v>4.439516766009887</v>
+        <v>4.136337606822551</v>
       </c>
       <c r="U88">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V88">
-        <v>0.1526936024249524</v>
+        <v>0.2216741703957639</v>
       </c>
       <c r="W88">
-        <v>0.1878788538748111</v>
+        <v>0.118878853874811</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.6107744096998096</v>
+        <v>0.8866966815830556</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2016488411487259</v>
+        <v>0.1394263630173218</v>
       </c>
       <c r="C89">
-        <v>-1653.150428036482</v>
+        <v>-962.2279928598364</v>
       </c>
       <c r="D89">
-        <v>1660.547571963518</v>
+        <v>2351.470007140164</v>
       </c>
       <c r="E89">
         <v>2566.998</v>
@@ -8585,45 +8585,45 @@
         <v>473.5</v>
       </c>
       <c r="M89">
-        <v>784.2597960004836</v>
+        <v>540.2138340004835</v>
       </c>
       <c r="N89">
-        <v>-310.7597960004836</v>
+        <v>-66.71383400048353</v>
       </c>
       <c r="O89">
-        <v>-77.68994900012089</v>
+        <v>-16.67845850012088</v>
       </c>
       <c r="P89">
-        <v>-233.0698470003627</v>
+        <v>-50.03537550036265</v>
       </c>
       <c r="Q89">
-        <v>-100.4698470003626</v>
+        <v>82.56462449963738</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2911973896135623</v>
+        <v>0.2743321732181455</v>
       </c>
       <c r="T89">
-        <v>4.781018055702955</v>
+        <v>4.454517422731978</v>
       </c>
       <c r="U89">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V89">
-        <v>0.1509385035465046</v>
+        <v>0.2191261914256976</v>
       </c>
       <c r="W89">
-        <v>0.1882680235620263</v>
+        <v>0.1192680235620262</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.6037540141860186</v>
+        <v>0.8765047657027906</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2034082073153513</v>
+        <v>0.1404957291839471</v>
       </c>
       <c r="C90">
-        <v>-1707.490364395786</v>
+        <v>-1019.582368556871</v>
       </c>
       <c r="D90">
-        <v>1646.861635604214</v>
+        <v>2334.76963144313</v>
       </c>
       <c r="E90">
         <v>2607.652</v>
@@ -8667,45 +8667,45 @@
         <v>473.5</v>
       </c>
       <c r="M90">
-        <v>793.2742764142822</v>
+        <v>546.4231884142822</v>
       </c>
       <c r="N90">
-        <v>-319.7742764142822</v>
+        <v>-72.92318841428221</v>
       </c>
       <c r="O90">
-        <v>-79.94356910357055</v>
+        <v>-18.23079710357055</v>
       </c>
       <c r="P90">
-        <v>-239.8307073107117</v>
+        <v>-54.69239131071166</v>
       </c>
       <c r="Q90">
-        <v>-107.2307073107116</v>
+        <v>77.90760868928837</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3116471720813592</v>
+        <v>0.2933765209863243</v>
       </c>
       <c r="T90">
-        <v>5.179436227011534</v>
+        <v>4.825727207959644</v>
       </c>
       <c r="U90">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V90">
-        <v>0.1492232932789307</v>
+        <v>0.2166361210685874</v>
       </c>
       <c r="W90">
-        <v>0.1886483484836229</v>
+        <v>0.1196483484836229</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.596893173115723</v>
+        <v>0.8665444842743497</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2051675734819766</v>
+        <v>0.1415650953505724</v>
       </c>
       <c r="C91">
-        <v>-1761.606550778639</v>
+        <v>-1076.701201616904</v>
       </c>
       <c r="D91">
-        <v>1633.399449221361</v>
+        <v>2318.304798383097</v>
       </c>
       <c r="E91">
         <v>2648.306</v>
@@ -8749,45 +8749,45 @@
         <v>473.5</v>
       </c>
       <c r="M91">
-        <v>802.2887568280809</v>
+        <v>552.6325428280809</v>
       </c>
       <c r="N91">
-        <v>-328.7887568280809</v>
+        <v>-79.13254282808089</v>
       </c>
       <c r="O91">
-        <v>-82.19718920702022</v>
+        <v>-19.78313570702022</v>
       </c>
       <c r="P91">
-        <v>-246.5915676210606</v>
+        <v>-59.34940712106066</v>
       </c>
       <c r="Q91">
-        <v>-113.9915676210606</v>
+        <v>73.25059287893936</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3358150968160282</v>
+        <v>0.3158834774396265</v>
       </c>
       <c r="T91">
-        <v>5.650294065830765</v>
+        <v>5.264429681410521</v>
       </c>
       <c r="U91">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V91">
-        <v>0.1475466270623135</v>
+        <v>0.2142020073487156</v>
       </c>
       <c r="W91">
-        <v>0.189020126777768</v>
+        <v>0.120020126777768</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.5901865082492541</v>
+        <v>0.8568080293948626</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.206926939648602</v>
+        <v>0.1426344615171978</v>
       </c>
       <c r="C92">
-        <v>-1815.504429793005</v>
+        <v>-1133.589440296165</v>
       </c>
       <c r="D92">
-        <v>1620.155570206995</v>
+        <v>2302.070559703835</v>
       </c>
       <c r="E92">
         <v>2688.96</v>
@@ -8831,45 +8831,45 @@
         <v>473.5</v>
       </c>
       <c r="M92">
-        <v>811.3032372418796</v>
+        <v>558.8418972418796</v>
       </c>
       <c r="N92">
-        <v>-337.8032372418796</v>
+        <v>-85.34189724187956</v>
       </c>
       <c r="O92">
-        <v>-84.45080931046991</v>
+        <v>-21.33547431046989</v>
       </c>
       <c r="P92">
-        <v>-253.3524279314097</v>
+        <v>-64.00642293140967</v>
       </c>
       <c r="Q92">
-        <v>-120.7524279314097</v>
+        <v>68.59357706859035</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.364816606497631</v>
+        <v>0.3428918251835892</v>
       </c>
       <c r="T92">
-        <v>6.215323472413842</v>
+        <v>5.790872649551573</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V92">
-        <v>0.1459072200949545</v>
+        <v>0.211821985044841</v>
       </c>
       <c r="W92">
-        <v>0.1893836433320432</v>
+        <v>0.1203836433320432</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.583628880379818</v>
+        <v>0.8472879401793642</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2086863058152273</v>
+        <v>0.1437038276838231</v>
       </c>
       <c r="C93">
-        <v>-1869.189268948235</v>
+        <v>-1190.251895211427</v>
       </c>
       <c r="D93">
-        <v>1607.124731051765</v>
+        <v>2286.062104788573</v>
       </c>
       <c r="E93">
         <v>2729.614</v>
@@ -8913,45 +8913,45 @@
         <v>473.5</v>
       </c>
       <c r="M93">
-        <v>820.3177176556783</v>
+        <v>565.0512516556782</v>
       </c>
       <c r="N93">
-        <v>-346.8177176556783</v>
+        <v>-91.55125165567824</v>
       </c>
       <c r="O93">
-        <v>-86.70442941391957</v>
+        <v>-22.88781291391956</v>
       </c>
       <c r="P93">
-        <v>-260.1132882417587</v>
+        <v>-68.66343874175868</v>
       </c>
       <c r="Q93">
-        <v>-127.5132882417587</v>
+        <v>63.93656125824134</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.400262896108479</v>
+        <v>0.3759020279817658</v>
       </c>
       <c r="T93">
-        <v>6.905914969348714</v>
+        <v>6.434302943946193</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V93">
-        <v>0.144303844049955</v>
+        <v>0.2094942709234691</v>
       </c>
       <c r="W93">
-        <v>0.1897391705114991</v>
+        <v>0.1207391705114991</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.57721537619982</v>
+        <v>0.8379770836938766</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2104456719818527</v>
+        <v>0.1447731938504485</v>
       </c>
       <c r="C94">
-        <v>-1922.666167640434</v>
+        <v>-1246.693244092636</v>
       </c>
       <c r="D94">
-        <v>1594.301832359566</v>
+        <v>2270.274755907365</v>
       </c>
       <c r="E94">
         <v>2770.268</v>
@@ -8995,45 +8995,45 @@
         <v>473.5</v>
       </c>
       <c r="M94">
-        <v>829.3321980694769</v>
+        <v>571.2606060694769</v>
       </c>
       <c r="N94">
-        <v>-355.8321980694769</v>
+        <v>-97.76060606947692</v>
       </c>
       <c r="O94">
-        <v>-88.95804951736923</v>
+        <v>-24.44015151736923</v>
       </c>
       <c r="P94">
-        <v>-266.8741485521077</v>
+        <v>-73.32045455210769</v>
       </c>
       <c r="Q94">
-        <v>-134.2741485521077</v>
+        <v>59.27954544789233</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4445707581220391</v>
+        <v>0.4171647814794867</v>
       </c>
       <c r="T94">
-        <v>7.769154340517307</v>
+        <v>7.23859081193947</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V94">
-        <v>0.1427353240059337</v>
+        <v>0.2072171592829966</v>
       </c>
       <c r="W94">
-        <v>0.1900869688392278</v>
+        <v>0.1210869688392278</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.570941296023735</v>
+        <v>0.8288686371319866</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.212205038148478</v>
+        <v>0.1458425600170738</v>
       </c>
       <c r="C95">
-        <v>-1975.940063806069</v>
+        <v>-1302.918036339959</v>
       </c>
       <c r="D95">
-        <v>1581.681936193932</v>
+        <v>2254.703963660041</v>
       </c>
       <c r="E95">
         <v>2810.922</v>
@@ -9077,45 +9077,45 @@
         <v>473.5</v>
       </c>
       <c r="M95">
-        <v>838.3466784832756</v>
+        <v>577.4699604832755</v>
       </c>
       <c r="N95">
-        <v>-364.8466784832756</v>
+        <v>-103.9699604832755</v>
       </c>
       <c r="O95">
-        <v>-91.2116696208189</v>
+        <v>-25.99249012081887</v>
       </c>
       <c r="P95">
-        <v>-273.6350088624567</v>
+        <v>-77.97747036245661</v>
       </c>
       <c r="Q95">
-        <v>-141.0350088624567</v>
+        <v>54.62252963754341</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5015380092823303</v>
+        <v>0.4702168931194133</v>
       </c>
       <c r="T95">
-        <v>8.879033532019779</v>
+        <v>8.272675213645108</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V95">
-        <v>0.1412005355757624</v>
+        <v>0.20498901778533</v>
       </c>
       <c r="W95">
-        <v>0.1904272876330268</v>
+        <v>0.1214272876330268</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.5648021423030496</v>
+        <v>0.8199560711413202</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2139644043151034</v>
+        <v>0.1469119261836991</v>
       </c>
       <c r="C96">
-        <v>-2029.01574026205</v>
+        <v>-1358.9306973946</v>
       </c>
       <c r="D96">
-        <v>1569.26025973795</v>
+        <v>2239.3453026054</v>
       </c>
       <c r="E96">
         <v>2851.576</v>
@@ -9159,45 +9159,45 @@
         <v>473.5</v>
       </c>
       <c r="M96">
-        <v>847.3611588970742</v>
+        <v>583.6793148970742</v>
       </c>
       <c r="N96">
-        <v>-373.8611588970742</v>
+        <v>-110.1793148970742</v>
       </c>
       <c r="O96">
-        <v>-93.46528972426856</v>
+        <v>-27.54482872426854</v>
       </c>
       <c r="P96">
-        <v>-280.3958691728056</v>
+        <v>-82.63448617280562</v>
       </c>
       <c r="Q96">
-        <v>-147.7958691728056</v>
+        <v>49.9655138271944</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5774943441627188</v>
+        <v>0.540953041972649</v>
       </c>
       <c r="T96">
-        <v>10.35887245402308</v>
+        <v>9.651454415919297</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V96">
-        <v>0.1396984022185734</v>
+        <v>0.2028082835535712</v>
       </c>
       <c r="W96">
-        <v>0.1907603656014258</v>
+        <v>0.1217603656014258</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.5587936088742937</v>
+        <v>0.8112331342142849</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2157237704817287</v>
+        <v>0.1479812923503245</v>
       </c>
       <c r="C97">
-        <v>-2081.8978307494</v>
+        <v>-1414.735532932164</v>
       </c>
       <c r="D97">
-        <v>1557.0321692506</v>
+        <v>2224.194467067837</v>
       </c>
       <c r="E97">
         <v>2892.23</v>
@@ -9241,45 +9241,45 @@
         <v>473.5</v>
       </c>
       <c r="M97">
-        <v>856.375639310873</v>
+        <v>589.888669310873</v>
       </c>
       <c r="N97">
-        <v>-382.875639310873</v>
+        <v>-116.388669310873</v>
       </c>
       <c r="O97">
-        <v>-95.71890982771825</v>
+        <v>-29.09716732771824</v>
       </c>
       <c r="P97">
-        <v>-287.1567294831548</v>
+        <v>-87.29150198315472</v>
       </c>
       <c r="Q97">
-        <v>-154.5567294831548</v>
+        <v>45.30849801684531</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6838332129952629</v>
+        <v>0.6399836503671791</v>
       </c>
       <c r="T97">
-        <v>12.4306469448277</v>
+        <v>11.58174529910316</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V97">
-        <v>0.1382278927215358</v>
+        <v>0.2006734595161652</v>
       </c>
       <c r="W97">
-        <v>0.191086431402069</v>
+        <v>0.122086431402069</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5529115708861432</v>
+        <v>0.8026938380646607</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.217483136648354</v>
+        <v>0.2027185009225149</v>
       </c>
       <c r="C98">
-        <v>-2134.590825696532</v>
+        <v>-2027.523441011835</v>
       </c>
       <c r="D98">
-        <v>1544.993174303468</v>
+        <v>1652.060558988165</v>
       </c>
       <c r="E98">
         <v>2932.884</v>
@@ -9323,37 +9323,37 @@
         <v>473.5</v>
       </c>
       <c r="M98">
-        <v>865.3901197246715</v>
+        <v>806.8483597246715</v>
       </c>
       <c r="N98">
-        <v>-391.8901197246715</v>
+        <v>-333.3483597246715</v>
       </c>
       <c r="O98">
-        <v>-97.97252993116788</v>
+        <v>-83.33708993116787</v>
       </c>
       <c r="P98">
-        <v>-293.9175897935037</v>
+        <v>-250.0112697935036</v>
       </c>
       <c r="Q98">
-        <v>-161.3175897935037</v>
+        <v>-117.4112697935036</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8433415162440768</v>
+        <v>0.8342256230980984</v>
       </c>
       <c r="T98">
-        <v>15.53830868103459</v>
+        <v>15.3678828900225</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.1367880188390198</v>
+        <v>0.1467128222710823</v>
       </c>
       <c r="W98">
-        <v>0.1914057041651989</v>
+        <v>0.1764057041651989</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5471520753560793</v>
+        <v>0.5868512890843292</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2192425028149794</v>
+        <v>0.2043278670891402</v>
       </c>
       <c r="C99">
-        <v>-2187.099077717219</v>
+        <v>-2080.578274660985</v>
       </c>
       <c r="D99">
-        <v>1533.138922282781</v>
+        <v>1639.659725339015</v>
       </c>
       <c r="E99">
         <v>2973.538</v>
@@ -9405,37 +9405,37 @@
         <v>473.5</v>
       </c>
       <c r="M99">
-        <v>874.4046001384702</v>
+        <v>815.2530301384702</v>
       </c>
       <c r="N99">
-        <v>-400.9046001384702</v>
+        <v>-341.7530301384702</v>
       </c>
       <c r="O99">
-        <v>-100.2261500346175</v>
+        <v>-85.43825753461755</v>
       </c>
       <c r="P99">
-        <v>-300.6784501038526</v>
+        <v>-256.3147726038526</v>
       </c>
       <c r="Q99">
-        <v>-168.0784501038526</v>
+        <v>-123.7147726038526</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.109188688325436</v>
+        <v>1.097034164130798</v>
       </c>
       <c r="T99">
-        <v>20.71774490804612</v>
+        <v>20.49051052003</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.1353778330777928</v>
+        <v>0.1452003189487</v>
       </c>
       <c r="W99">
-        <v>0.191718393984759</v>
+        <v>0.176718393984759</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5415113323111713</v>
+        <v>0.5808012757948</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2210018689816047</v>
+        <v>0.2059372332557655</v>
       </c>
       <c r="C100">
-        <v>-2239.426806857381</v>
+        <v>-2133.448327003854</v>
       </c>
       <c r="D100">
-        <v>1521.465193142619</v>
+        <v>1627.443672996147</v>
       </c>
       <c r="E100">
         <v>3014.192</v>
@@ -9487,37 +9487,37 @@
         <v>473.5</v>
       </c>
       <c r="M100">
-        <v>883.4190805522688</v>
+        <v>823.6577005522688</v>
       </c>
       <c r="N100">
-        <v>-409.9190805522688</v>
+        <v>-350.1577005522688</v>
       </c>
       <c r="O100">
-        <v>-102.4797701380672</v>
+        <v>-87.5394251380672</v>
       </c>
       <c r="P100">
-        <v>-307.4393104142016</v>
+        <v>-262.6182754142016</v>
       </c>
       <c r="Q100">
-        <v>-174.8393104142016</v>
+        <v>-130.0182754142016</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.640883032488154</v>
+        <v>1.622651246196197</v>
       </c>
       <c r="T100">
-        <v>31.07661736206918</v>
+        <v>30.735765780045</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.1339964266178154</v>
+        <v>0.1437186830410602</v>
       </c>
       <c r="W100">
-        <v>0.1920247023794302</v>
+        <v>0.1770247023794302</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5359857064712614</v>
+        <v>0.5748747321642409</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.22276123514823</v>
+        <v>0.2075465994223909</v>
       </c>
       <c r="C101">
-        <v>-2291.578105603976</v>
+        <v>-2186.137697558345</v>
       </c>
       <c r="D101">
-        <v>1509.967894396024</v>
+        <v>1615.408302441655</v>
       </c>
       <c r="E101">
         <v>3054.846</v>
@@ -9569,37 +9569,37 @@
         <v>473.5</v>
       </c>
       <c r="M101">
-        <v>892.4335609660675</v>
+        <v>832.0623709660674</v>
       </c>
       <c r="N101">
-        <v>-418.9335609660675</v>
+        <v>-358.5623709660674</v>
       </c>
       <c r="O101">
-        <v>-104.7333902415169</v>
+        <v>-89.64059274151685</v>
       </c>
       <c r="P101">
-        <v>-314.2001707245506</v>
+        <v>-268.9217782245506</v>
       </c>
       <c r="Q101">
-        <v>-181.6001707245506</v>
+        <v>-136.3217782245505</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.235966064976307</v>
+        <v>3.199502492392394</v>
       </c>
       <c r="T101">
-        <v>62.15323472413836</v>
+        <v>61.47153156008999</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V101">
-        <v>0.1326429273590495</v>
+        <v>0.1422669791719586</v>
       </c>
       <c r="W101">
-        <v>0.1923248227257242</v>
+        <v>0.1773248227257242</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.5305717094361981</v>
+        <v>0.5690679166878344</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/belgium/belgium_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_construction_supplies.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08250699649463347</v>
+        <v>0.08237900362836591</v>
       </c>
       <c r="C2">
-        <v>4020.357562425989</v>
+        <v>3984.960346585092</v>
       </c>
       <c r="D2">
-        <v>3797.157562425989</v>
+        <v>3802.414346585092</v>
       </c>
       <c r="E2">
-        <v>-969.9</v>
+        <v>-929.246</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>40.654</v>
       </c>
       <c r="G2">
         <v>223.2</v>
@@ -1451,28 +1451,28 @@
         <v>473.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.286243413798661</v>
       </c>
       <c r="N2">
-        <v>473.5</v>
+        <v>471.2137565862013</v>
       </c>
       <c r="O2">
-        <v>118.375</v>
+        <v>117.8034391465503</v>
       </c>
       <c r="P2">
-        <v>355.125</v>
+        <v>353.410317439651</v>
       </c>
       <c r="Q2">
-        <v>487.725</v>
+        <v>486.010317439651</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08250699649463347</v>
+        <v>0.082785079801411</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7209080456223336</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>207.1083057657739</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08237900362836591</v>
+        <v>0.08225101076209833</v>
       </c>
       <c r="C3">
-        <v>3984.960346585092</v>
+        <v>3949.57770590389</v>
       </c>
       <c r="D3">
-        <v>3802.414346585092</v>
+        <v>3807.68570590389</v>
       </c>
       <c r="E3">
-        <v>-929.246</v>
+        <v>-888.592</v>
       </c>
       <c r="F3">
-        <v>40.654</v>
+        <v>81.30800000000001</v>
       </c>
       <c r="G3">
         <v>223.2</v>
@@ -1533,28 +1533,28 @@
         <v>473.5</v>
       </c>
       <c r="M3">
-        <v>2.286243413798661</v>
+        <v>4.572486827597323</v>
       </c>
       <c r="N3">
-        <v>471.2137565862013</v>
+        <v>468.9275131724027</v>
       </c>
       <c r="O3">
-        <v>117.8034391465503</v>
+        <v>117.2318782931007</v>
       </c>
       <c r="P3">
-        <v>353.410317439651</v>
+        <v>351.695634879302</v>
       </c>
       <c r="Q3">
-        <v>486.010317439651</v>
+        <v>484.295634879302</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.082785079801411</v>
+        <v>0.08306883827771461</v>
       </c>
       <c r="T3">
-        <v>0.7209080456223336</v>
+        <v>0.726439026484865</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>207.1083057657739</v>
+        <v>103.554152882887</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08225101076209833</v>
+        <v>0.08212301789583075</v>
       </c>
       <c r="C4">
-        <v>3949.57770590389</v>
+        <v>3914.209701083998</v>
       </c>
       <c r="D4">
-        <v>3807.68570590389</v>
+        <v>3812.971701083999</v>
       </c>
       <c r="E4">
-        <v>-888.592</v>
+        <v>-847.938</v>
       </c>
       <c r="F4">
-        <v>81.30800000000001</v>
+        <v>121.962</v>
       </c>
       <c r="G4">
         <v>223.2</v>
@@ -1615,28 +1615,28 @@
         <v>473.5</v>
       </c>
       <c r="M4">
-        <v>4.572486827597323</v>
+        <v>6.858730241395985</v>
       </c>
       <c r="N4">
-        <v>468.9275131724027</v>
+        <v>466.641269758604</v>
       </c>
       <c r="O4">
-        <v>117.2318782931007</v>
+        <v>116.660317439651</v>
       </c>
       <c r="P4">
-        <v>351.695634879302</v>
+        <v>349.980952318953</v>
       </c>
       <c r="Q4">
-        <v>484.295634879302</v>
+        <v>482.5809523189531</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08306883827771461</v>
+        <v>0.08335844744425126</v>
       </c>
       <c r="T4">
-        <v>0.726439026484865</v>
+        <v>0.7320840481899227</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>103.554152882887</v>
+        <v>69.03610192192464</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08212301789583075</v>
+        <v>0.08199502502956317</v>
       </c>
       <c r="C5">
-        <v>3914.209701083998</v>
+        <v>3878.856393164574</v>
       </c>
       <c r="D5">
-        <v>3812.971701083999</v>
+        <v>3818.272393164575</v>
       </c>
       <c r="E5">
-        <v>-847.938</v>
+        <v>-807.284</v>
       </c>
       <c r="F5">
-        <v>121.962</v>
+        <v>162.616</v>
       </c>
       <c r="G5">
         <v>223.2</v>
@@ -1697,28 +1697,28 @@
         <v>473.5</v>
       </c>
       <c r="M5">
-        <v>6.858730241395985</v>
+        <v>9.144973655194645</v>
       </c>
       <c r="N5">
-        <v>466.641269758604</v>
+        <v>464.3550263448054</v>
       </c>
       <c r="O5">
-        <v>116.660317439651</v>
+        <v>116.0887565862013</v>
       </c>
       <c r="P5">
-        <v>349.980952318953</v>
+        <v>348.266269758604</v>
       </c>
       <c r="Q5">
-        <v>482.5809523189531</v>
+        <v>480.8662697586041</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08335844744425126</v>
+        <v>0.08365409013509077</v>
       </c>
       <c r="T5">
-        <v>0.7320840481899227</v>
+        <v>0.7378466745138358</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.03610192192464</v>
+        <v>51.77707644144348</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08199502502956317</v>
+        <v>0.08186703216329559</v>
       </c>
       <c r="C6">
-        <v>3878.856393164574</v>
+        <v>3843.51784352467</v>
       </c>
       <c r="D6">
-        <v>3818.272393164575</v>
+        <v>3823.58784352467</v>
       </c>
       <c r="E6">
-        <v>-807.284</v>
+        <v>-766.63</v>
       </c>
       <c r="F6">
-        <v>162.616</v>
+        <v>203.27</v>
       </c>
       <c r="G6">
         <v>223.2</v>
@@ -1779,28 +1779,28 @@
         <v>473.5</v>
       </c>
       <c r="M6">
-        <v>9.144973655194645</v>
+        <v>11.43121706899331</v>
       </c>
       <c r="N6">
-        <v>464.3550263448054</v>
+        <v>462.0687829310067</v>
       </c>
       <c r="O6">
-        <v>116.0887565862013</v>
+        <v>115.5171957327517</v>
       </c>
       <c r="P6">
-        <v>348.266269758604</v>
+        <v>346.551587198255</v>
       </c>
       <c r="Q6">
-        <v>480.8662697586041</v>
+        <v>479.151587198255</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08365409013509077</v>
+        <v>0.08395595688257954</v>
       </c>
       <c r="T6">
-        <v>0.7378466745138358</v>
+        <v>0.7437306192866734</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.77707644144348</v>
+        <v>41.42166115315479</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08186703216329559</v>
+        <v>0.08173903929702801</v>
       </c>
       <c r="C7">
-        <v>3843.51784352467</v>
+        <v>3808.194113885596</v>
       </c>
       <c r="D7">
-        <v>3823.58784352467</v>
+        <v>3828.918113885596</v>
       </c>
       <c r="E7">
-        <v>-766.63</v>
+        <v>-725.9759999999999</v>
       </c>
       <c r="F7">
-        <v>203.27</v>
+        <v>243.924</v>
       </c>
       <c r="G7">
         <v>223.2</v>
@@ -1861,28 +1861,28 @@
         <v>473.5</v>
       </c>
       <c r="M7">
-        <v>11.43121706899331</v>
+        <v>13.71746048279197</v>
       </c>
       <c r="N7">
-        <v>462.0687829310067</v>
+        <v>459.782539517208</v>
       </c>
       <c r="O7">
-        <v>115.5171957327517</v>
+        <v>114.945634879302</v>
       </c>
       <c r="P7">
-        <v>346.551587198255</v>
+        <v>344.836904637906</v>
       </c>
       <c r="Q7">
-        <v>479.151587198255</v>
+        <v>477.436904637906</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08395595688257954</v>
+        <v>0.08426424632682337</v>
       </c>
       <c r="T7">
-        <v>0.7437306192866734</v>
+        <v>0.7497397543738267</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.42166115315479</v>
+        <v>34.51805096096232</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.081739039297028</v>
+        <v>0.08161104643076043</v>
       </c>
       <c r="C8">
-        <v>3808.194113885596</v>
+        <v>3772.885266313316</v>
       </c>
       <c r="D8">
-        <v>3828.918113885597</v>
+        <v>3834.263266313316</v>
       </c>
       <c r="E8">
-        <v>-725.976</v>
+        <v>-685.322</v>
       </c>
       <c r="F8">
-        <v>243.924</v>
+        <v>284.578</v>
       </c>
       <c r="G8">
         <v>223.2</v>
@@ -1943,28 +1943,28 @@
         <v>473.5</v>
       </c>
       <c r="M8">
-        <v>13.71746048279197</v>
+        <v>16.00370389659063</v>
       </c>
       <c r="N8">
-        <v>459.782539517208</v>
+        <v>457.4962961034093</v>
       </c>
       <c r="O8">
-        <v>114.945634879302</v>
+        <v>114.3740740258523</v>
       </c>
       <c r="P8">
-        <v>344.836904637906</v>
+        <v>343.122222077557</v>
       </c>
       <c r="Q8">
-        <v>477.436904637906</v>
+        <v>475.722222077557</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08426424632682337</v>
+        <v>0.0845791656515886</v>
       </c>
       <c r="T8">
-        <v>0.7497397543738267</v>
+        <v>0.7558781181725317</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.51805096096232</v>
+        <v>29.58690082368199</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08161104643076043</v>
+        <v>0.08148305356449284</v>
       </c>
       <c r="C9">
-        <v>3772.885266313316</v>
+        <v>3737.591363220854</v>
       </c>
       <c r="D9">
-        <v>3834.263266313316</v>
+        <v>3839.623363220854</v>
       </c>
       <c r="E9">
-        <v>-685.3219999999999</v>
+        <v>-644.6679999999999</v>
       </c>
       <c r="F9">
-        <v>284.578</v>
+        <v>325.232</v>
       </c>
       <c r="G9">
         <v>223.2</v>
@@ -2025,28 +2025,28 @@
         <v>473.5</v>
       </c>
       <c r="M9">
-        <v>16.00370389659063</v>
+        <v>18.28994731038929</v>
       </c>
       <c r="N9">
-        <v>457.4962961034093</v>
+        <v>455.2100526896107</v>
       </c>
       <c r="O9">
-        <v>114.3740740258523</v>
+        <v>113.8025131724027</v>
       </c>
       <c r="P9">
-        <v>343.122222077557</v>
+        <v>341.4075395172081</v>
       </c>
       <c r="Q9">
-        <v>475.722222077557</v>
+        <v>474.0075395172081</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0845791656515886</v>
+        <v>0.08490093104863131</v>
       </c>
       <c r="T9">
-        <v>0.7558781181725317</v>
+        <v>0.762149924662513</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.58690082368199</v>
+        <v>25.88853822072175</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08148305356449284</v>
+        <v>0.08135506069822528</v>
       </c>
       <c r="C10">
-        <v>3737.591363220854</v>
+        <v>3702.312467370719</v>
       </c>
       <c r="D10">
-        <v>3839.623363220854</v>
+        <v>3844.998467370719</v>
       </c>
       <c r="E10">
-        <v>-644.6679999999999</v>
+        <v>-604.014</v>
       </c>
       <c r="F10">
-        <v>325.232</v>
+        <v>365.886</v>
       </c>
       <c r="G10">
         <v>223.2</v>
@@ -2107,28 +2107,28 @@
         <v>473.5</v>
       </c>
       <c r="M10">
-        <v>18.28994731038929</v>
+        <v>20.57619072418795</v>
       </c>
       <c r="N10">
-        <v>455.2100526896107</v>
+        <v>452.9238092758121</v>
       </c>
       <c r="O10">
-        <v>113.8025131724027</v>
+        <v>113.230952318953</v>
       </c>
       <c r="P10">
-        <v>341.4075395172081</v>
+        <v>339.692856956859</v>
       </c>
       <c r="Q10">
-        <v>474.0075395172081</v>
+        <v>472.2928569568591</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08490093104863131</v>
+        <v>0.085229768212642</v>
       </c>
       <c r="T10">
-        <v>0.762149924662513</v>
+        <v>0.7685595730533727</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.88853822072175</v>
+        <v>23.01203397397489</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08135506069822528</v>
+        <v>0.08122706783195768</v>
       </c>
       <c r="C11">
-        <v>3702.312467370719</v>
+        <v>3667.048641877365</v>
       </c>
       <c r="D11">
-        <v>3844.998467370719</v>
+        <v>3850.388641877365</v>
       </c>
       <c r="E11">
-        <v>-604.014</v>
+        <v>-563.36</v>
       </c>
       <c r="F11">
-        <v>365.886</v>
+        <v>406.54</v>
       </c>
       <c r="G11">
         <v>223.2</v>
@@ -2189,28 +2189,28 @@
         <v>473.5</v>
       </c>
       <c r="M11">
-        <v>20.57619072418795</v>
+        <v>22.86243413798661</v>
       </c>
       <c r="N11">
-        <v>452.9238092758121</v>
+        <v>450.6375658620134</v>
       </c>
       <c r="O11">
-        <v>113.230952318953</v>
+        <v>112.6593914655033</v>
       </c>
       <c r="P11">
-        <v>339.692856956859</v>
+        <v>337.97817439651</v>
       </c>
       <c r="Q11">
-        <v>472.2928569568591</v>
+        <v>470.5781743965101</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.085229768212642</v>
+        <v>0.08556591286918626</v>
       </c>
       <c r="T11">
-        <v>0.7685595730533727</v>
+        <v>0.7751116580751406</v>
       </c>
       <c r="U11">
         <v>0.0562366166625341</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.01203397397489</v>
+        <v>20.7108305765774</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08122706783195768</v>
+        <v>0.08109907496569012</v>
       </c>
       <c r="C12">
-        <v>3667.048641877365</v>
+        <v>3631.799950209648</v>
       </c>
       <c r="D12">
-        <v>3850.388641877365</v>
+        <v>3855.793950209648</v>
       </c>
       <c r="E12">
-        <v>-563.3599999999999</v>
+        <v>-522.7059999999999</v>
       </c>
       <c r="F12">
-        <v>406.54</v>
+        <v>447.194</v>
       </c>
       <c r="G12">
         <v>223.2</v>
@@ -2271,28 +2271,28 @@
         <v>473.5</v>
       </c>
       <c r="M12">
-        <v>22.86243413798661</v>
+        <v>25.14867755178528</v>
       </c>
       <c r="N12">
-        <v>450.6375658620134</v>
+        <v>448.3513224482147</v>
       </c>
       <c r="O12">
-        <v>112.6593914655033</v>
+        <v>112.0878306120537</v>
       </c>
       <c r="P12">
-        <v>337.97817439651</v>
+        <v>336.2634918361611</v>
       </c>
       <c r="Q12">
-        <v>470.5781743965101</v>
+        <v>468.8634918361611</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08556591286918626</v>
+        <v>0.08590961133823714</v>
       </c>
       <c r="T12">
-        <v>0.7751116580751406</v>
+        <v>0.7818109809625663</v>
       </c>
       <c r="U12">
         <v>0.0562366166625341</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.71083057657739</v>
+        <v>18.82802779688854</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08109907496569012</v>
+        <v>0.08097108209942254</v>
       </c>
       <c r="C13">
-        <v>3631.799950209648</v>
+        <v>3596.566456193329</v>
       </c>
       <c r="D13">
-        <v>3855.793950209648</v>
+        <v>3861.214456193329</v>
       </c>
       <c r="E13">
-        <v>-522.7059999999999</v>
+        <v>-482.052</v>
       </c>
       <c r="F13">
-        <v>447.194</v>
+        <v>487.848</v>
       </c>
       <c r="G13">
         <v>223.2</v>
@@ -2353,28 +2353,28 @@
         <v>473.5</v>
       </c>
       <c r="M13">
-        <v>25.14867755178528</v>
+        <v>27.43492096558394</v>
       </c>
       <c r="N13">
-        <v>448.3513224482147</v>
+        <v>446.065079034416</v>
       </c>
       <c r="O13">
-        <v>112.0878306120537</v>
+        <v>111.516269758604</v>
       </c>
       <c r="P13">
-        <v>336.2634918361611</v>
+        <v>334.548809275812</v>
       </c>
       <c r="Q13">
-        <v>468.8634918361611</v>
+        <v>467.148809275812</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08590961133823714</v>
+        <v>0.08626112113613008</v>
       </c>
       <c r="T13">
-        <v>0.7818109809625663</v>
+        <v>0.7886625611883424</v>
       </c>
       <c r="U13">
         <v>0.0562366166625341</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.82802779688854</v>
+        <v>17.25902548048116</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08097108209942254</v>
+        <v>0.08084308923315496</v>
       </c>
       <c r="C14">
-        <v>3596.566456193329</v>
+        <v>3561.34822401358</v>
       </c>
       <c r="D14">
-        <v>3861.214456193329</v>
+        <v>3866.650224013581</v>
       </c>
       <c r="E14">
-        <v>-482.052</v>
+        <v>-441.3979999999999</v>
       </c>
       <c r="F14">
-        <v>487.848</v>
+        <v>528.5020000000001</v>
       </c>
       <c r="G14">
         <v>223.2</v>
@@ -2435,28 +2435,28 @@
         <v>473.5</v>
       </c>
       <c r="M14">
-        <v>27.43492096558394</v>
+        <v>29.7211643793826</v>
       </c>
       <c r="N14">
-        <v>446.065079034416</v>
+        <v>443.7788356206174</v>
       </c>
       <c r="O14">
-        <v>111.516269758604</v>
+        <v>110.9447089051544</v>
       </c>
       <c r="P14">
-        <v>334.548809275812</v>
+        <v>332.8341267154631</v>
       </c>
       <c r="Q14">
-        <v>467.148809275812</v>
+        <v>465.4341267154631</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08626112113613008</v>
+        <v>0.08662071161903205</v>
       </c>
       <c r="T14">
-        <v>0.7886625611883424</v>
+        <v>0.7956716490055157</v>
       </c>
       <c r="U14">
         <v>0.0562366166625341</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.25902548048116</v>
+        <v>15.93140813582876</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08084308923315496</v>
+        <v>0.08071509636688738</v>
       </c>
       <c r="C15">
-        <v>3561.34822401358</v>
+        <v>3526.145318217518</v>
       </c>
       <c r="D15">
-        <v>3866.650224013581</v>
+        <v>3872.101318217518</v>
       </c>
       <c r="E15">
-        <v>-441.3979999999999</v>
+        <v>-400.7439999999999</v>
       </c>
       <c r="F15">
-        <v>528.5020000000001</v>
+        <v>569.1560000000001</v>
       </c>
       <c r="G15">
         <v>223.2</v>
@@ -2517,28 +2517,28 @@
         <v>473.5</v>
       </c>
       <c r="M15">
-        <v>29.7211643793826</v>
+        <v>32.00740779318127</v>
       </c>
       <c r="N15">
-        <v>443.7788356206174</v>
+        <v>441.4925922068188</v>
       </c>
       <c r="O15">
-        <v>110.9447089051544</v>
+        <v>110.3731480517047</v>
       </c>
       <c r="P15">
-        <v>332.8341267154631</v>
+        <v>331.1194441551141</v>
       </c>
       <c r="Q15">
-        <v>465.4341267154631</v>
+        <v>463.7194441551141</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08662071161903205</v>
+        <v>0.08698866467130384</v>
       </c>
       <c r="T15">
-        <v>0.7956716490055157</v>
+        <v>0.8028437388649489</v>
       </c>
       <c r="U15">
         <v>0.0562366166625341</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.93140813582876</v>
+        <v>14.79345041184099</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08071509636688738</v>
+        <v>0.0805871035006198</v>
       </c>
       <c r="C16">
-        <v>3526.145318217518</v>
+        <v>3490.957803716763</v>
       </c>
       <c r="D16">
-        <v>3872.101318217518</v>
+        <v>3877.567803716763</v>
       </c>
       <c r="E16">
-        <v>-400.7439999999999</v>
+        <v>-360.0899999999999</v>
       </c>
       <c r="F16">
-        <v>569.1560000000001</v>
+        <v>609.8100000000001</v>
       </c>
       <c r="G16">
         <v>223.2</v>
@@ -2599,28 +2599,28 @@
         <v>473.5</v>
       </c>
       <c r="M16">
-        <v>32.00740779318127</v>
+        <v>34.29365120697992</v>
       </c>
       <c r="N16">
-        <v>441.4925922068188</v>
+        <v>439.2063487930201</v>
       </c>
       <c r="O16">
-        <v>110.3731480517047</v>
+        <v>109.801587198255</v>
       </c>
       <c r="P16">
-        <v>331.1194441551141</v>
+        <v>329.4047615947651</v>
       </c>
       <c r="Q16">
-        <v>463.7194441551141</v>
+        <v>462.0047615947651</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08698866467130384</v>
+        <v>0.08736527544245261</v>
       </c>
       <c r="T16">
-        <v>0.8028437388649489</v>
+        <v>0.8101845837798981</v>
       </c>
       <c r="U16">
         <v>0.0562366166625341</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.79345041184099</v>
+        <v>13.80722038438493</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0805871035006198</v>
+        <v>0.08045911063435222</v>
       </c>
       <c r="C17">
-        <v>3490.957803716763</v>
+        <v>3455.785745790007</v>
       </c>
       <c r="D17">
-        <v>3877.567803716763</v>
+        <v>3883.049745790007</v>
       </c>
       <c r="E17">
-        <v>-360.09</v>
+        <v>-319.4359999999999</v>
       </c>
       <c r="F17">
-        <v>609.8099999999999</v>
+        <v>650.4640000000001</v>
       </c>
       <c r="G17">
         <v>223.2</v>
@@ -2681,28 +2681,28 @@
         <v>473.5</v>
       </c>
       <c r="M17">
-        <v>34.29365120697992</v>
+        <v>36.57989462077858</v>
       </c>
       <c r="N17">
-        <v>439.2063487930201</v>
+        <v>436.9201053792214</v>
       </c>
       <c r="O17">
-        <v>109.801587198255</v>
+        <v>109.2300263448054</v>
       </c>
       <c r="P17">
-        <v>329.4047615947651</v>
+        <v>327.690079034416</v>
       </c>
       <c r="Q17">
-        <v>462.0047615947651</v>
+        <v>460.2900790344161</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08736527544245261</v>
+        <v>0.08775085313672397</v>
       </c>
       <c r="T17">
-        <v>0.8101845837798981</v>
+        <v>0.8177002107166318</v>
       </c>
       <c r="U17">
         <v>0.0562366166625341</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.80722038438493</v>
+        <v>12.94426911036087</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08045911063435222</v>
+        <v>0.08052236776808465</v>
       </c>
       <c r="C18">
-        <v>3455.785745790007</v>
+        <v>3412.42050306722</v>
       </c>
       <c r="D18">
-        <v>3883.049745790007</v>
+        <v>3880.338503067219</v>
       </c>
       <c r="E18">
-        <v>-319.4359999999999</v>
+        <v>-278.7819999999999</v>
       </c>
       <c r="F18">
-        <v>650.4640000000001</v>
+        <v>691.1180000000001</v>
       </c>
       <c r="G18">
         <v>223.2</v>
@@ -2763,45 +2763,45 @@
         <v>473.5</v>
       </c>
       <c r="M18">
-        <v>36.57989462077858</v>
+        <v>39.90281503457724</v>
       </c>
       <c r="N18">
-        <v>436.9201053792214</v>
+        <v>433.5971849654227</v>
       </c>
       <c r="O18">
-        <v>109.2300263448054</v>
+        <v>108.3992962413557</v>
       </c>
       <c r="P18">
-        <v>327.690079034416</v>
+        <v>325.1978887240671</v>
       </c>
       <c r="Q18">
-        <v>460.2900790344161</v>
+        <v>457.7978887240671</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08775085313672397</v>
+        <v>0.08814572185977296</v>
       </c>
       <c r="T18">
-        <v>0.8177002107166318</v>
+        <v>0.8253969370976244</v>
       </c>
       <c r="U18">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04217746249690058</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>12.94426911036087</v>
+        <v>11.86633072352652</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08052236776808465</v>
+        <v>0.08040562490181707</v>
       </c>
       <c r="C19">
-        <v>3412.42050306722</v>
+        <v>3376.773137603532</v>
       </c>
       <c r="D19">
-        <v>3880.338503067219</v>
+        <v>3885.345137603531</v>
       </c>
       <c r="E19">
-        <v>-278.7819999999999</v>
+        <v>-238.1279999999999</v>
       </c>
       <c r="F19">
-        <v>691.1180000000001</v>
+        <v>731.772</v>
       </c>
       <c r="G19">
         <v>223.2</v>
@@ -2845,28 +2845,28 @@
         <v>473.5</v>
       </c>
       <c r="M19">
-        <v>39.90281503457724</v>
+        <v>42.2500394483759</v>
       </c>
       <c r="N19">
-        <v>433.5971849654227</v>
+        <v>431.2499605516241</v>
       </c>
       <c r="O19">
-        <v>108.3992962413557</v>
+        <v>107.812490137906</v>
       </c>
       <c r="P19">
-        <v>325.1978887240671</v>
+        <v>323.4374704137181</v>
       </c>
       <c r="Q19">
-        <v>457.7978887240671</v>
+        <v>456.0374704137181</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08814572185977296</v>
+        <v>0.08855022152728655</v>
       </c>
       <c r="T19">
-        <v>0.8253969370976244</v>
+        <v>0.8332813885122994</v>
       </c>
       <c r="U19">
         <v>0.05773661666253409</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.86633072352652</v>
+        <v>11.20709012777505</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08040562490181707</v>
+        <v>0.08028888203554951</v>
       </c>
       <c r="C20">
-        <v>3376.773137603532</v>
+        <v>3341.13870852322</v>
       </c>
       <c r="D20">
-        <v>3885.345137603531</v>
+        <v>3890.36470852322</v>
       </c>
       <c r="E20">
-        <v>-238.128</v>
+        <v>-197.4739999999999</v>
       </c>
       <c r="F20">
-        <v>731.7719999999999</v>
+        <v>772.426</v>
       </c>
       <c r="G20">
         <v>223.2</v>
@@ -2927,28 +2927,28 @@
         <v>473.5</v>
       </c>
       <c r="M20">
-        <v>42.25003944837589</v>
+        <v>44.59726386217456</v>
       </c>
       <c r="N20">
-        <v>431.2499605516241</v>
+        <v>428.9027361378255</v>
       </c>
       <c r="O20">
-        <v>107.812490137906</v>
+        <v>107.2256840344564</v>
       </c>
       <c r="P20">
-        <v>323.4374704137181</v>
+        <v>321.6770521033691</v>
       </c>
       <c r="Q20">
-        <v>456.0374704137181</v>
+        <v>454.2770521033691</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08855022152728655</v>
+        <v>0.08896470884091159</v>
       </c>
       <c r="T20">
-        <v>0.8332813885122994</v>
+        <v>0.8413605177396827</v>
       </c>
       <c r="U20">
         <v>0.05773661666253409</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.20709012777505</v>
+        <v>10.61724327894478</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08028888203554951</v>
+        <v>0.08017213916928191</v>
       </c>
       <c r="C21">
-        <v>3341.13870852322</v>
+        <v>3305.51726602962</v>
       </c>
       <c r="D21">
-        <v>3890.36470852322</v>
+        <v>3895.39726602962</v>
       </c>
       <c r="E21">
-        <v>-197.4739999999999</v>
+        <v>-156.8199999999999</v>
       </c>
       <c r="F21">
-        <v>772.426</v>
+        <v>813.08</v>
       </c>
       <c r="G21">
         <v>223.2</v>
@@ -3009,28 +3009,28 @@
         <v>473.5</v>
       </c>
       <c r="M21">
-        <v>44.59726386217456</v>
+        <v>46.94448827597322</v>
       </c>
       <c r="N21">
-        <v>428.9027361378255</v>
+        <v>426.5555117240268</v>
       </c>
       <c r="O21">
-        <v>107.2256840344564</v>
+        <v>106.6388779310067</v>
       </c>
       <c r="P21">
-        <v>321.6770521033691</v>
+        <v>319.9166337930201</v>
       </c>
       <c r="Q21">
-        <v>454.2770521033691</v>
+        <v>452.5166337930201</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08896470884091159</v>
+        <v>0.08938955833737725</v>
       </c>
       <c r="T21">
-        <v>0.8413605177396827</v>
+        <v>0.8496416251977503</v>
       </c>
       <c r="U21">
         <v>0.05773661666253409</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.61724327894478</v>
+        <v>10.08638111499755</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08017213916928191</v>
+        <v>0.08032314630301435</v>
       </c>
       <c r="C22">
-        <v>3305.51726602962</v>
+        <v>3258.356110110852</v>
       </c>
       <c r="D22">
-        <v>3895.39726602962</v>
+        <v>3888.890110110852</v>
       </c>
       <c r="E22">
-        <v>-156.8199999999999</v>
+        <v>-116.1659999999998</v>
       </c>
       <c r="F22">
-        <v>813.08</v>
+        <v>853.7340000000002</v>
       </c>
       <c r="G22">
         <v>223.2</v>
@@ -3091,45 +3091,45 @@
         <v>473.5</v>
       </c>
       <c r="M22">
-        <v>46.94448827597322</v>
+        <v>50.74306048977189</v>
       </c>
       <c r="N22">
-        <v>426.5555117240268</v>
+        <v>422.7569395102281</v>
       </c>
       <c r="O22">
-        <v>106.6388779310067</v>
+        <v>105.689234877557</v>
       </c>
       <c r="P22">
-        <v>319.9166337930201</v>
+        <v>317.0677046326711</v>
       </c>
       <c r="Q22">
-        <v>452.5166337930201</v>
+        <v>449.6677046326711</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08938955833737725</v>
+        <v>0.08982516351729775</v>
       </c>
       <c r="T22">
-        <v>0.8496416251977503</v>
+        <v>0.8581323809458957</v>
       </c>
       <c r="U22">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04330246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.08638111499755</v>
+        <v>9.331325218261949</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08032314630301435</v>
+        <v>0.08021915343674677</v>
       </c>
       <c r="C23">
-        <v>3258.356110110852</v>
+        <v>3222.181007464746</v>
       </c>
       <c r="D23">
-        <v>3888.890110110852</v>
+        <v>3893.369007464747</v>
       </c>
       <c r="E23">
-        <v>-116.1659999999999</v>
+        <v>-75.51199999999994</v>
       </c>
       <c r="F23">
-        <v>853.734</v>
+        <v>894.388</v>
       </c>
       <c r="G23">
         <v>223.2</v>
@@ -3173,28 +3173,28 @@
         <v>473.5</v>
       </c>
       <c r="M23">
-        <v>50.74306048977189</v>
+        <v>53.15939670357054</v>
       </c>
       <c r="N23">
-        <v>422.7569395102281</v>
+        <v>420.3406032964294</v>
       </c>
       <c r="O23">
-        <v>105.689234877557</v>
+        <v>105.0851508241074</v>
       </c>
       <c r="P23">
-        <v>317.0677046326711</v>
+        <v>315.2554524723221</v>
       </c>
       <c r="Q23">
-        <v>449.6677046326711</v>
+        <v>447.8554524723221</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08982516351729775</v>
+        <v>0.09027193806080594</v>
       </c>
       <c r="T23">
-        <v>0.8581323809458957</v>
+        <v>0.8668408483798909</v>
       </c>
       <c r="U23">
         <v>0.05943661666253409</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.33132521826195</v>
+        <v>8.907174071977316</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08021915343674677</v>
+        <v>0.08011516057047917</v>
       </c>
       <c r="C24">
-        <v>3222.181007464746</v>
+        <v>3186.016233550801</v>
       </c>
       <c r="D24">
-        <v>3893.369007464747</v>
+        <v>3897.8582335508</v>
       </c>
       <c r="E24">
-        <v>-75.51199999999994</v>
+        <v>-34.85799999999995</v>
       </c>
       <c r="F24">
-        <v>894.388</v>
+        <v>935.042</v>
       </c>
       <c r="G24">
         <v>223.2</v>
@@ -3255,28 +3255,28 @@
         <v>473.5</v>
       </c>
       <c r="M24">
-        <v>53.15939670357054</v>
+        <v>55.57573291736921</v>
       </c>
       <c r="N24">
-        <v>420.3406032964294</v>
+        <v>417.9242670826308</v>
       </c>
       <c r="O24">
-        <v>105.0851508241074</v>
+        <v>104.4810667706577</v>
       </c>
       <c r="P24">
-        <v>315.2554524723221</v>
+        <v>313.4432003119731</v>
       </c>
       <c r="Q24">
-        <v>447.8554524723221</v>
+        <v>446.0432003119731</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09027193806080594</v>
+        <v>0.09073031713791174</v>
       </c>
       <c r="T24">
-        <v>0.8668408483798909</v>
+        <v>0.8757755097732108</v>
       </c>
       <c r="U24">
         <v>0.05943661666253409</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.907174071977316</v>
+        <v>8.519905634065259</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08011516057047917</v>
+        <v>0.08001116770421161</v>
       </c>
       <c r="C25">
-        <v>3186.016233550801</v>
+        <v>3149.861824138707</v>
       </c>
       <c r="D25">
-        <v>3897.8582335508</v>
+        <v>3902.357824138707</v>
       </c>
       <c r="E25">
-        <v>-34.85799999999995</v>
+        <v>5.796000000000163</v>
       </c>
       <c r="F25">
-        <v>935.042</v>
+        <v>975.6960000000001</v>
       </c>
       <c r="G25">
         <v>223.2</v>
@@ -3337,28 +3337,28 @@
         <v>473.5</v>
       </c>
       <c r="M25">
-        <v>55.57573291736921</v>
+        <v>57.99206913116787</v>
       </c>
       <c r="N25">
-        <v>417.9242670826308</v>
+        <v>415.5079308688321</v>
       </c>
       <c r="O25">
-        <v>104.4810667706577</v>
+        <v>103.876982717208</v>
       </c>
       <c r="P25">
-        <v>313.4432003119731</v>
+        <v>311.6309481516241</v>
       </c>
       <c r="Q25">
-        <v>446.0432003119731</v>
+        <v>444.2309481516241</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09073031713791174</v>
+        <v>0.09120075882230982</v>
       </c>
       <c r="T25">
-        <v>0.8757755097732108</v>
+        <v>0.884945293834776</v>
       </c>
       <c r="U25">
         <v>0.05943661666253409</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.519905634065259</v>
+        <v>8.164909565979206</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0800111677042116</v>
+        <v>0.07990717483794403</v>
       </c>
       <c r="C26">
-        <v>3149.861824138708</v>
+        <v>3113.71781516352</v>
       </c>
       <c r="D26">
-        <v>3902.357824138708</v>
+        <v>3906.86781516352</v>
       </c>
       <c r="E26">
-        <v>5.796000000000049</v>
+        <v>46.45000000000005</v>
       </c>
       <c r="F26">
-        <v>975.696</v>
+        <v>1016.35</v>
       </c>
       <c r="G26">
         <v>223.2</v>
@@ -3419,28 +3419,28 @@
         <v>473.5</v>
       </c>
       <c r="M26">
-        <v>57.99206913116787</v>
+        <v>60.40840534496653</v>
       </c>
       <c r="N26">
-        <v>415.5079308688321</v>
+        <v>413.0915946550335</v>
       </c>
       <c r="O26">
-        <v>103.876982717208</v>
+        <v>103.2728986637584</v>
       </c>
       <c r="P26">
-        <v>311.6309481516241</v>
+        <v>309.8186959912751</v>
       </c>
       <c r="Q26">
-        <v>444.2309481516241</v>
+        <v>442.4186959912751</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09120075882230982</v>
+        <v>0.09168374561829185</v>
       </c>
       <c r="T26">
-        <v>0.884945293834776</v>
+        <v>0.8943596054713161</v>
       </c>
       <c r="U26">
         <v>0.05943661666253409</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.164909565979208</v>
+        <v>7.838313183340039</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07990717483794403</v>
+        <v>0.07995918197167645</v>
       </c>
       <c r="C27">
-        <v>3113.71781516352</v>
+        <v>3070.8070532778</v>
       </c>
       <c r="D27">
-        <v>3906.86781516352</v>
+        <v>3904.6110532778</v>
       </c>
       <c r="E27">
-        <v>46.45000000000005</v>
+        <v>87.10400000000016</v>
       </c>
       <c r="F27">
-        <v>1016.35</v>
+        <v>1057.004</v>
       </c>
       <c r="G27">
         <v>223.2</v>
@@ -3501,45 +3501,45 @@
         <v>473.5</v>
       </c>
       <c r="M27">
-        <v>60.40840534496653</v>
+        <v>63.6703447587652</v>
       </c>
       <c r="N27">
-        <v>413.0915946550335</v>
+        <v>409.8296552412348</v>
       </c>
       <c r="O27">
-        <v>103.2728986637584</v>
+        <v>102.4574138103087</v>
       </c>
       <c r="P27">
-        <v>309.8186959912751</v>
+        <v>307.3722414309261</v>
       </c>
       <c r="Q27">
-        <v>442.4186959912751</v>
+        <v>439.9722414309261</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09168374561829185</v>
+        <v>0.09217978611146257</v>
       </c>
       <c r="T27">
-        <v>0.8943596054713161</v>
+        <v>0.9040283579628979</v>
       </c>
       <c r="U27">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04457746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.838313183340039</v>
+        <v>7.436743146185266</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07995918197167645</v>
+        <v>0.07986118910540888</v>
       </c>
       <c r="C28">
-        <v>3070.8070532778</v>
+        <v>3034.407462735966</v>
       </c>
       <c r="D28">
-        <v>3904.6110532778</v>
+        <v>3908.865462735967</v>
       </c>
       <c r="E28">
-        <v>87.10400000000016</v>
+        <v>127.7580000000002</v>
       </c>
       <c r="F28">
-        <v>1057.004</v>
+        <v>1097.658</v>
       </c>
       <c r="G28">
         <v>223.2</v>
@@ -3583,28 +3583,28 @@
         <v>473.5</v>
       </c>
       <c r="M28">
-        <v>63.6703447587652</v>
+        <v>66.11920417256385</v>
       </c>
       <c r="N28">
-        <v>409.8296552412348</v>
+        <v>407.3807958274361</v>
       </c>
       <c r="O28">
-        <v>102.4574138103087</v>
+        <v>101.845198956859</v>
       </c>
       <c r="P28">
-        <v>307.3722414309261</v>
+        <v>305.5355968705771</v>
       </c>
       <c r="Q28">
-        <v>439.9722414309261</v>
+        <v>438.1355968705772</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09217978611146257</v>
+        <v>0.09268941675513112</v>
       </c>
       <c r="T28">
-        <v>0.9040283579628979</v>
+        <v>0.9139620077830163</v>
       </c>
       <c r="U28">
         <v>0.0602366166625341</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.436743146185266</v>
+        <v>7.161308214845071</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07986118910540888</v>
+        <v>0.0797631962391413</v>
       </c>
       <c r="C29">
-        <v>3034.407462735966</v>
+        <v>2998.017153396592</v>
       </c>
       <c r="D29">
-        <v>3908.865462735967</v>
+        <v>3913.129153396592</v>
       </c>
       <c r="E29">
-        <v>127.7580000000002</v>
+        <v>168.4120000000001</v>
       </c>
       <c r="F29">
-        <v>1097.658</v>
+        <v>1138.312</v>
       </c>
       <c r="G29">
         <v>223.2</v>
@@ -3665,28 +3665,28 @@
         <v>473.5</v>
       </c>
       <c r="M29">
-        <v>66.11920417256385</v>
+        <v>68.56806358636253</v>
       </c>
       <c r="N29">
-        <v>407.3807958274361</v>
+        <v>404.9319364136375</v>
       </c>
       <c r="O29">
-        <v>101.845198956859</v>
+        <v>101.2329841034094</v>
       </c>
       <c r="P29">
-        <v>305.5355968705771</v>
+        <v>303.6989523102281</v>
       </c>
       <c r="Q29">
-        <v>438.1355968705772</v>
+        <v>436.2989523102281</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09268941675513112</v>
+        <v>0.09321320380556825</v>
       </c>
       <c r="T29">
-        <v>0.9139620077830163</v>
+        <v>0.9241715923203601</v>
       </c>
       <c r="U29">
         <v>0.0602366166625341</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.161308214845071</v>
+        <v>6.905547207172031</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0797631962391413</v>
+        <v>0.07966520337287371</v>
       </c>
       <c r="C30">
-        <v>2998.017153396592</v>
+        <v>2961.636155663939</v>
       </c>
       <c r="D30">
-        <v>3913.129153396592</v>
+        <v>3917.402155663939</v>
       </c>
       <c r="E30">
-        <v>168.4120000000001</v>
+        <v>209.0660000000001</v>
       </c>
       <c r="F30">
-        <v>1138.312</v>
+        <v>1178.966</v>
       </c>
       <c r="G30">
         <v>223.2</v>
@@ -3747,28 +3747,28 @@
         <v>473.5</v>
       </c>
       <c r="M30">
-        <v>68.56806358636253</v>
+        <v>71.01692300016119</v>
       </c>
       <c r="N30">
-        <v>404.9319364136375</v>
+        <v>402.4830769998388</v>
       </c>
       <c r="O30">
-        <v>101.2329841034094</v>
+        <v>100.6207692499597</v>
       </c>
       <c r="P30">
-        <v>303.6989523102281</v>
+        <v>301.8623077498791</v>
       </c>
       <c r="Q30">
-        <v>436.2989523102281</v>
+        <v>434.4623077498791</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09321320380556825</v>
+        <v>0.0937517454208064</v>
       </c>
       <c r="T30">
-        <v>0.9241715923203601</v>
+        <v>0.9346687707883331</v>
       </c>
       <c r="U30">
         <v>0.0602366166625341</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.905547207172031</v>
+        <v>6.667424889683341</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07966520337287371</v>
+        <v>0.07956721050660613</v>
       </c>
       <c r="C31">
-        <v>2961.636155663939</v>
+        <v>2925.264500075211</v>
       </c>
       <c r="D31">
-        <v>3917.402155663939</v>
+        <v>3921.684500075211</v>
       </c>
       <c r="E31">
-        <v>209.0659999999999</v>
+        <v>249.7199999999999</v>
       </c>
       <c r="F31">
-        <v>1178.966</v>
+        <v>1219.62</v>
       </c>
       <c r="G31">
         <v>223.2</v>
@@ -3829,28 +3829,28 @@
         <v>473.5</v>
       </c>
       <c r="M31">
-        <v>71.01692300016117</v>
+        <v>73.46578241395983</v>
       </c>
       <c r="N31">
-        <v>402.4830769998388</v>
+        <v>400.0342175860402</v>
       </c>
       <c r="O31">
-        <v>100.6207692499597</v>
+        <v>100.00855439651</v>
       </c>
       <c r="P31">
-        <v>301.8623077498791</v>
+        <v>300.0256631895302</v>
       </c>
       <c r="Q31">
-        <v>434.4623077498791</v>
+        <v>432.6256631895302</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0937517454208064</v>
+        <v>0.09430567393933709</v>
       </c>
       <c r="T31">
-        <v>0.9346687707883331</v>
+        <v>0.9454658686411056</v>
       </c>
       <c r="U31">
         <v>0.0602366166625341</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.667424889683343</v>
+        <v>6.445177393360565</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07956721050660613</v>
+        <v>0.07946921764033854</v>
       </c>
       <c r="C32">
-        <v>2925.264500075211</v>
+        <v>2888.902217301292</v>
       </c>
       <c r="D32">
-        <v>3921.684500075211</v>
+        <v>3925.976217301292</v>
       </c>
       <c r="E32">
-        <v>249.7199999999999</v>
+        <v>290.3740000000001</v>
       </c>
       <c r="F32">
-        <v>1219.62</v>
+        <v>1260.274</v>
       </c>
       <c r="G32">
         <v>223.2</v>
@@ -3911,28 +3911,28 @@
         <v>473.5</v>
       </c>
       <c r="M32">
-        <v>73.46578241395983</v>
+        <v>75.9146418277585</v>
       </c>
       <c r="N32">
-        <v>400.0342175860402</v>
+        <v>397.5853581722415</v>
       </c>
       <c r="O32">
-        <v>100.00855439651</v>
+        <v>99.39633954306038</v>
       </c>
       <c r="P32">
-        <v>300.0256631895302</v>
+        <v>298.1890186291811</v>
       </c>
       <c r="Q32">
-        <v>432.6256631895302</v>
+        <v>430.7890186291812</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09430567393933709</v>
+        <v>0.09487565835695562</v>
       </c>
       <c r="T32">
-        <v>0.9454658686411056</v>
+        <v>0.9565759258519294</v>
       </c>
       <c r="U32">
         <v>0.0602366166625341</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.445177393360565</v>
+        <v>6.237268445187643</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07946921764033854</v>
+        <v>0.07961122477407097</v>
       </c>
       <c r="C33">
-        <v>2888.902217301292</v>
+        <v>2842.031893712426</v>
       </c>
       <c r="D33">
-        <v>3925.976217301292</v>
+        <v>3919.759893712425</v>
       </c>
       <c r="E33">
-        <v>290.3740000000001</v>
+        <v>331.0280000000001</v>
       </c>
       <c r="F33">
-        <v>1260.274</v>
+        <v>1300.928</v>
       </c>
       <c r="G33">
         <v>223.2</v>
@@ -3993,45 +3993,45 @@
         <v>473.5</v>
       </c>
       <c r="M33">
-        <v>75.9146418277585</v>
+        <v>79.66442924155716</v>
       </c>
       <c r="N33">
-        <v>397.5853581722415</v>
+        <v>393.8355707584428</v>
       </c>
       <c r="O33">
-        <v>99.39633954306038</v>
+        <v>98.45889268961071</v>
       </c>
       <c r="P33">
-        <v>298.1890186291811</v>
+        <v>295.3766780688321</v>
       </c>
       <c r="Q33">
-        <v>430.7890186291812</v>
+        <v>427.9766780688321</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09487565835695562</v>
+        <v>0.09546240702215117</v>
       </c>
       <c r="T33">
-        <v>0.9565759258519294</v>
+        <v>0.9680127494513069</v>
       </c>
       <c r="U33">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04517746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.237268445187643</v>
+        <v>5.943681571661816</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07961122477407097</v>
+        <v>0.0795207319078034</v>
       </c>
       <c r="C34">
-        <v>2842.031893712426</v>
+        <v>2805.336916667322</v>
       </c>
       <c r="D34">
-        <v>3919.759893712425</v>
+        <v>3923.718916667322</v>
       </c>
       <c r="E34">
-        <v>331.0280000000001</v>
+        <v>371.6820000000001</v>
       </c>
       <c r="F34">
-        <v>1300.928</v>
+        <v>1341.582</v>
       </c>
       <c r="G34">
         <v>223.2</v>
@@ -4075,28 +4075,28 @@
         <v>473.5</v>
       </c>
       <c r="M34">
-        <v>79.66442924155716</v>
+        <v>82.15394265535582</v>
       </c>
       <c r="N34">
-        <v>393.8355707584428</v>
+        <v>391.3460573446442</v>
       </c>
       <c r="O34">
-        <v>98.45889268961071</v>
+        <v>97.83651433616104</v>
       </c>
       <c r="P34">
-        <v>295.3766780688321</v>
+        <v>293.5095430084831</v>
       </c>
       <c r="Q34">
-        <v>427.9766780688321</v>
+        <v>426.1095430084832</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09546240702215117</v>
+        <v>0.09606667057287495</v>
       </c>
       <c r="T34">
-        <v>0.9680127494513069</v>
+        <v>0.9797909707700688</v>
       </c>
       <c r="U34">
         <v>0.0612366166625341</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.943681571661816</v>
+        <v>5.763570008884185</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0795207319078034</v>
+        <v>0.07943023904153582</v>
       </c>
       <c r="C35">
-        <v>2805.336916667322</v>
+        <v>2768.649945066455</v>
       </c>
       <c r="D35">
-        <v>3923.718916667322</v>
+        <v>3927.685945066455</v>
       </c>
       <c r="E35">
-        <v>371.6820000000001</v>
+        <v>412.3360000000001</v>
       </c>
       <c r="F35">
-        <v>1341.582</v>
+        <v>1382.236</v>
       </c>
       <c r="G35">
         <v>223.2</v>
@@ -4157,28 +4157,28 @@
         <v>473.5</v>
       </c>
       <c r="M35">
-        <v>82.15394265535582</v>
+        <v>84.64345606915448</v>
       </c>
       <c r="N35">
-        <v>391.3460573446442</v>
+        <v>388.8565439308455</v>
       </c>
       <c r="O35">
-        <v>97.83651433616104</v>
+        <v>97.21413598271138</v>
       </c>
       <c r="P35">
-        <v>293.5095430084831</v>
+        <v>291.6424079481342</v>
       </c>
       <c r="Q35">
-        <v>426.1095430084832</v>
+        <v>424.2424079481342</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09606667057287495</v>
+        <v>0.09668924514028732</v>
       </c>
       <c r="T35">
-        <v>0.9797909707700688</v>
+        <v>0.9919261078863688</v>
       </c>
       <c r="U35">
         <v>0.0612366166625341</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.763570008884185</v>
+        <v>5.594053243917004</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07943023904153582</v>
+        <v>0.07933974617526825</v>
       </c>
       <c r="C36">
-        <v>2768.649945066455</v>
+        <v>2731.971003215822</v>
       </c>
       <c r="D36">
-        <v>3927.685945066455</v>
+        <v>3931.661003215822</v>
       </c>
       <c r="E36">
-        <v>412.3360000000001</v>
+        <v>452.9900000000001</v>
       </c>
       <c r="F36">
-        <v>1382.236</v>
+        <v>1422.89</v>
       </c>
       <c r="G36">
         <v>223.2</v>
@@ -4239,28 +4239,28 @@
         <v>473.5</v>
       </c>
       <c r="M36">
-        <v>84.64345606915448</v>
+        <v>87.13296948295314</v>
       </c>
       <c r="N36">
-        <v>388.8565439308455</v>
+        <v>386.3670305170468</v>
       </c>
       <c r="O36">
-        <v>97.21413598271138</v>
+        <v>96.59175762926171</v>
       </c>
       <c r="P36">
-        <v>291.6424079481342</v>
+        <v>289.7752728877851</v>
       </c>
       <c r="Q36">
-        <v>424.2424079481342</v>
+        <v>422.3752728877852</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09668924514028732</v>
+        <v>0.09733097584823547</v>
       </c>
       <c r="T36">
-        <v>0.9919261078863688</v>
+        <v>1.004434633837017</v>
       </c>
       <c r="U36">
         <v>0.0612366166625341</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.594053243917004</v>
+        <v>5.434223151233661</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07933974617526825</v>
+        <v>0.07924925330900066</v>
       </c>
       <c r="C37">
-        <v>2731.971003215822</v>
+        <v>2695.300115519914</v>
       </c>
       <c r="D37">
-        <v>3931.661003215822</v>
+        <v>3935.644115519915</v>
       </c>
       <c r="E37">
-        <v>452.9900000000001</v>
+        <v>493.6440000000001</v>
       </c>
       <c r="F37">
-        <v>1422.89</v>
+        <v>1463.544</v>
       </c>
       <c r="G37">
         <v>223.2</v>
@@ -4321,28 +4321,28 @@
         <v>473.5</v>
       </c>
       <c r="M37">
-        <v>87.13296948295314</v>
+        <v>89.62248289675181</v>
       </c>
       <c r="N37">
-        <v>386.3670305170468</v>
+        <v>383.8775171032482</v>
       </c>
       <c r="O37">
-        <v>96.59175762926171</v>
+        <v>95.96937927581205</v>
       </c>
       <c r="P37">
-        <v>289.7752728877851</v>
+        <v>287.9081378274361</v>
       </c>
       <c r="Q37">
-        <v>422.3752728877852</v>
+        <v>420.5081378274361</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09733097584823547</v>
+        <v>0.09799276064080698</v>
       </c>
       <c r="T37">
-        <v>1.004434633837017</v>
+        <v>1.017334051223622</v>
       </c>
       <c r="U37">
         <v>0.0612366166625341</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.434223151233661</v>
+        <v>5.283272508143837</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07924925330900068</v>
+        <v>0.07915876044273309</v>
       </c>
       <c r="C38">
-        <v>2695.300115519914</v>
+        <v>2658.63730648222</v>
       </c>
       <c r="D38">
-        <v>3935.644115519914</v>
+        <v>3939.63530648222</v>
       </c>
       <c r="E38">
-        <v>493.6439999999999</v>
+        <v>534.2980000000001</v>
       </c>
       <c r="F38">
-        <v>1463.544</v>
+        <v>1504.198</v>
       </c>
       <c r="G38">
         <v>223.2</v>
@@ -4403,28 +4403,28 @@
         <v>473.5</v>
       </c>
       <c r="M38">
-        <v>89.62248289675179</v>
+        <v>92.11199631055047</v>
       </c>
       <c r="N38">
-        <v>383.8775171032482</v>
+        <v>381.3880036894495</v>
       </c>
       <c r="O38">
-        <v>95.96937927581206</v>
+        <v>95.34700092236238</v>
       </c>
       <c r="P38">
-        <v>287.9081378274362</v>
+        <v>286.0410027670872</v>
       </c>
       <c r="Q38">
-        <v>420.5081378274362</v>
+        <v>418.6410027670872</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09799276064080698</v>
+        <v>0.09867555447441251</v>
       </c>
       <c r="T38">
-        <v>1.017334051223622</v>
+        <v>1.030642973924088</v>
       </c>
       <c r="U38">
         <v>0.0612366166625341</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.283272508143837</v>
+        <v>5.140481359275084</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07915876044273309</v>
+        <v>0.07906826757646551</v>
       </c>
       <c r="C39">
-        <v>2658.63730648222</v>
+        <v>2621.982600705727</v>
       </c>
       <c r="D39">
-        <v>3939.63530648222</v>
+        <v>3943.634600705727</v>
       </c>
       <c r="E39">
-        <v>534.2980000000001</v>
+        <v>574.9520000000001</v>
       </c>
       <c r="F39">
-        <v>1504.198</v>
+        <v>1544.852</v>
       </c>
       <c r="G39">
         <v>223.2</v>
@@ -4485,28 +4485,28 @@
         <v>473.5</v>
       </c>
       <c r="M39">
-        <v>92.11199631055047</v>
+        <v>94.60150972434913</v>
       </c>
       <c r="N39">
-        <v>381.3880036894495</v>
+        <v>378.8984902756509</v>
       </c>
       <c r="O39">
-        <v>95.34700092236238</v>
+        <v>94.72462256891272</v>
       </c>
       <c r="P39">
-        <v>286.0410027670872</v>
+        <v>284.1738677067382</v>
       </c>
       <c r="Q39">
-        <v>418.6410027670872</v>
+        <v>416.7738677067382</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09867555447441251</v>
+        <v>0.09938037391555371</v>
       </c>
       <c r="T39">
-        <v>1.030642973924088</v>
+        <v>1.044381216711666</v>
       </c>
       <c r="U39">
         <v>0.0612366166625341</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.140481359275084</v>
+        <v>5.005205534031004</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07906826757646551</v>
+        <v>0.07897777471019793</v>
       </c>
       <c r="C40">
-        <v>2621.982600705727</v>
+        <v>2585.336022893423</v>
       </c>
       <c r="D40">
-        <v>3943.634600705727</v>
+        <v>3947.642022893423</v>
       </c>
       <c r="E40">
-        <v>574.9520000000001</v>
+        <v>615.6060000000001</v>
       </c>
       <c r="F40">
-        <v>1544.852</v>
+        <v>1585.506</v>
       </c>
       <c r="G40">
         <v>223.2</v>
@@ -4567,28 +4567,28 @@
         <v>473.5</v>
       </c>
       <c r="M40">
-        <v>94.60150972434913</v>
+        <v>97.09102313814779</v>
       </c>
       <c r="N40">
-        <v>378.8984902756509</v>
+        <v>376.4089768618522</v>
       </c>
       <c r="O40">
-        <v>94.72462256891272</v>
+        <v>94.10224421546306</v>
       </c>
       <c r="P40">
-        <v>284.1738677067382</v>
+        <v>282.3067326463892</v>
       </c>
       <c r="Q40">
-        <v>416.7738677067382</v>
+        <v>414.9067326463892</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09938037391555371</v>
+        <v>0.1001083021908307</v>
       </c>
       <c r="T40">
-        <v>1.044381216711666</v>
+        <v>1.058569893689</v>
       </c>
       <c r="U40">
         <v>0.0612366166625341</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.005205534031004</v>
+        <v>4.876866930594311</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07897777471019793</v>
+        <v>0.07888728184393036</v>
       </c>
       <c r="C41">
-        <v>2585.336022893423</v>
+        <v>2548.697597848811</v>
       </c>
       <c r="D41">
-        <v>3947.642022893423</v>
+        <v>3951.657597848811</v>
       </c>
       <c r="E41">
-        <v>615.6060000000001</v>
+        <v>656.2600000000001</v>
       </c>
       <c r="F41">
-        <v>1585.506</v>
+        <v>1626.16</v>
       </c>
       <c r="G41">
         <v>223.2</v>
@@ -4649,28 +4649,28 @@
         <v>473.5</v>
       </c>
       <c r="M41">
-        <v>97.09102313814779</v>
+        <v>99.58053655194645</v>
       </c>
       <c r="N41">
-        <v>376.4089768618522</v>
+        <v>373.9194634480535</v>
       </c>
       <c r="O41">
-        <v>94.10224421546306</v>
+        <v>93.47986586201338</v>
       </c>
       <c r="P41">
-        <v>282.3067326463892</v>
+        <v>280.4395975860401</v>
       </c>
       <c r="Q41">
-        <v>414.9067326463892</v>
+        <v>413.0395975860401</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1001083021908307</v>
+        <v>0.1008604947419502</v>
       </c>
       <c r="T41">
-        <v>1.058569893689</v>
+        <v>1.073231526565579</v>
       </c>
       <c r="U41">
         <v>0.0612366166625341</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.876866930594311</v>
+        <v>4.754945257329453</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07888728184393036</v>
+        <v>0.07879678897766279</v>
       </c>
       <c r="C42">
-        <v>2548.697597848811</v>
+        <v>2512.067350476417</v>
       </c>
       <c r="D42">
-        <v>3951.657597848811</v>
+        <v>3955.681350476417</v>
       </c>
       <c r="E42">
-        <v>656.2600000000001</v>
+        <v>696.9140000000001</v>
       </c>
       <c r="F42">
-        <v>1626.16</v>
+        <v>1666.814</v>
       </c>
       <c r="G42">
         <v>223.2</v>
@@ -4731,28 +4731,28 @@
         <v>473.5</v>
       </c>
       <c r="M42">
-        <v>99.58053655194645</v>
+        <v>102.0700499657451</v>
       </c>
       <c r="N42">
-        <v>373.9194634480535</v>
+        <v>371.4299500342549</v>
       </c>
       <c r="O42">
-        <v>93.47986586201338</v>
+        <v>92.85748750856372</v>
       </c>
       <c r="P42">
-        <v>280.4395975860401</v>
+        <v>278.5724625256912</v>
       </c>
       <c r="Q42">
-        <v>413.0395975860401</v>
+        <v>411.1724625256912</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1008604947419502</v>
+        <v>0.1016381853456501</v>
       </c>
       <c r="T42">
-        <v>1.073231526565579</v>
+        <v>1.088390163946449</v>
       </c>
       <c r="U42">
         <v>0.0612366166625341</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.754945257329453</v>
+        <v>4.638970982760442</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07879678897766279</v>
+        <v>0.07870629611139519</v>
       </c>
       <c r="C43">
-        <v>2512.067350476417</v>
+        <v>2475.44530578231</v>
       </c>
       <c r="D43">
-        <v>3955.681350476417</v>
+        <v>3959.71330578231</v>
       </c>
       <c r="E43">
-        <v>696.9140000000001</v>
+        <v>737.5680000000003</v>
       </c>
       <c r="F43">
-        <v>1666.814</v>
+        <v>1707.468</v>
       </c>
       <c r="G43">
         <v>223.2</v>
@@ -4813,28 +4813,28 @@
         <v>473.5</v>
       </c>
       <c r="M43">
-        <v>102.0700499657451</v>
+        <v>104.5595633795438</v>
       </c>
       <c r="N43">
-        <v>371.4299500342549</v>
+        <v>368.9404366204562</v>
       </c>
       <c r="O43">
-        <v>92.85748750856372</v>
+        <v>92.23510915511406</v>
       </c>
       <c r="P43">
-        <v>278.5724625256912</v>
+        <v>276.7053274653422</v>
       </c>
       <c r="Q43">
-        <v>411.1724625256912</v>
+        <v>409.3053274653422</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1016381853456501</v>
+        <v>0.1024426928667189</v>
       </c>
       <c r="T43">
-        <v>1.088390163946449</v>
+        <v>1.104071512961142</v>
       </c>
       <c r="U43">
         <v>0.0612366166625341</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.638970982760442</v>
+        <v>4.528519292694717</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07870629611139521</v>
+        <v>0.07942205324512763</v>
       </c>
       <c r="C44">
-        <v>2475.445305782309</v>
+        <v>2403.123189867158</v>
       </c>
       <c r="D44">
-        <v>3959.713305782309</v>
+        <v>3928.045189867158</v>
       </c>
       <c r="E44">
-        <v>737.5680000000001</v>
+        <v>778.2220000000001</v>
       </c>
       <c r="F44">
-        <v>1707.468</v>
+        <v>1748.122</v>
       </c>
       <c r="G44">
         <v>223.2</v>
@@ -4895,45 +4895,45 @@
         <v>473.5</v>
       </c>
       <c r="M44">
-        <v>104.5595633795438</v>
+        <v>111.4193817933424</v>
       </c>
       <c r="N44">
-        <v>368.9404366204562</v>
+        <v>362.0806182066576</v>
       </c>
       <c r="O44">
-        <v>92.23510915511406</v>
+        <v>90.52015455166439</v>
       </c>
       <c r="P44">
-        <v>276.7053274653422</v>
+        <v>271.5604636549932</v>
       </c>
       <c r="Q44">
-        <v>409.3053274653422</v>
+        <v>404.1604636549932</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1024426928667189</v>
+        <v>0.1032754287218603</v>
       </c>
       <c r="T44">
-        <v>1.104071512961142</v>
+        <v>1.12030308474828</v>
       </c>
       <c r="U44">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04592746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.528519292694718</v>
+        <v>4.249709452510109</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07942205324512763</v>
+        <v>0.07935031037886005</v>
       </c>
       <c r="C45">
-        <v>2403.123189867158</v>
+        <v>2365.620537239349</v>
       </c>
       <c r="D45">
-        <v>3928.045189867158</v>
+        <v>3931.196537239349</v>
       </c>
       <c r="E45">
-        <v>778.2220000000001</v>
+        <v>818.8760000000001</v>
       </c>
       <c r="F45">
-        <v>1748.122</v>
+        <v>1788.776</v>
       </c>
       <c r="G45">
         <v>223.2</v>
@@ -4977,28 +4977,28 @@
         <v>473.5</v>
       </c>
       <c r="M45">
-        <v>111.4193817933424</v>
+        <v>114.0105302071411</v>
       </c>
       <c r="N45">
-        <v>362.0806182066576</v>
+        <v>359.4894697928589</v>
       </c>
       <c r="O45">
-        <v>90.52015455166439</v>
+        <v>89.87236744821473</v>
       </c>
       <c r="P45">
-        <v>271.5604636549932</v>
+        <v>269.6171023446442</v>
       </c>
       <c r="Q45">
-        <v>404.1604636549932</v>
+        <v>402.2171023446442</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1032754287218603</v>
+        <v>0.1041379051432568</v>
       </c>
       <c r="T45">
-        <v>1.12030308474828</v>
+        <v>1.137114355527816</v>
       </c>
       <c r="U45">
         <v>0.06373661666253409</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.249709452510109</v>
+        <v>4.153125146771242</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07935031037886005</v>
+        <v>0.07927856751259246</v>
       </c>
       <c r="C46">
-        <v>2365.620537239349</v>
+        <v>2328.12294512561</v>
       </c>
       <c r="D46">
-        <v>3931.196537239349</v>
+        <v>3934.352945125611</v>
       </c>
       <c r="E46">
-        <v>818.8760000000001</v>
+        <v>859.5300000000001</v>
       </c>
       <c r="F46">
-        <v>1788.776</v>
+        <v>1829.43</v>
       </c>
       <c r="G46">
         <v>223.2</v>
@@ -5059,28 +5059,28 @@
         <v>473.5</v>
       </c>
       <c r="M46">
-        <v>114.0105302071411</v>
+        <v>116.6016786209398</v>
       </c>
       <c r="N46">
-        <v>359.4894697928589</v>
+        <v>356.8983213790602</v>
       </c>
       <c r="O46">
-        <v>89.87236744821473</v>
+        <v>89.22458034476506</v>
       </c>
       <c r="P46">
-        <v>269.6171023446442</v>
+        <v>267.6737410342952</v>
       </c>
       <c r="Q46">
-        <v>402.2171023446442</v>
+        <v>400.2737410342952</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1041379051432568</v>
+        <v>0.1050317443436131</v>
       </c>
       <c r="T46">
-        <v>1.137114355527816</v>
+        <v>1.15453694524479</v>
       </c>
       <c r="U46">
         <v>0.06373661666253409</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.153125146771242</v>
+        <v>4.060833476842992</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07927856751259246</v>
+        <v>0.08041432464632489</v>
       </c>
       <c r="C47">
-        <v>2328.12294512561</v>
+        <v>2238.087594887545</v>
       </c>
       <c r="D47">
-        <v>3934.352945125611</v>
+        <v>3884.971594887545</v>
       </c>
       <c r="E47">
-        <v>859.5300000000001</v>
+        <v>900.1840000000001</v>
       </c>
       <c r="F47">
-        <v>1829.43</v>
+        <v>1870.084</v>
       </c>
       <c r="G47">
         <v>223.2</v>
@@ -5141,45 +5141,45 @@
         <v>473.5</v>
       </c>
       <c r="M47">
-        <v>116.6016786209398</v>
+        <v>125.7381210347384</v>
       </c>
       <c r="N47">
-        <v>356.8983213790602</v>
+        <v>347.7618789652616</v>
       </c>
       <c r="O47">
-        <v>89.22458034476506</v>
+        <v>86.9404697413154</v>
       </c>
       <c r="P47">
-        <v>267.6737410342952</v>
+        <v>260.8214092239462</v>
       </c>
       <c r="Q47">
-        <v>400.2737410342952</v>
+        <v>393.4214092239462</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1050317443436131</v>
+        <v>0.1059586886995382</v>
       </c>
       <c r="T47">
-        <v>1.15453694524479</v>
+        <v>1.172604816062392</v>
       </c>
       <c r="U47">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04780246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.060833476842992</v>
+        <v>3.7657632872467</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08041432464632489</v>
+        <v>0.08036883178005731</v>
       </c>
       <c r="C48">
-        <v>2238.087594887545</v>
+        <v>2199.38772605856</v>
       </c>
       <c r="D48">
-        <v>3884.971594887545</v>
+        <v>3886.92572605856</v>
       </c>
       <c r="E48">
-        <v>900.1840000000001</v>
+        <v>940.8380000000001</v>
       </c>
       <c r="F48">
-        <v>1870.084</v>
+        <v>1910.738</v>
       </c>
       <c r="G48">
         <v>223.2</v>
@@ -5223,28 +5223,28 @@
         <v>473.5</v>
       </c>
       <c r="M48">
-        <v>125.7381210347384</v>
+        <v>128.4715584485371</v>
       </c>
       <c r="N48">
-        <v>347.7618789652616</v>
+        <v>345.0284415514629</v>
       </c>
       <c r="O48">
-        <v>86.9404697413154</v>
+        <v>86.25711038786574</v>
       </c>
       <c r="P48">
-        <v>260.8214092239462</v>
+        <v>258.7713311635972</v>
       </c>
       <c r="Q48">
-        <v>393.4214092239462</v>
+        <v>391.3713311635972</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1059586886995382</v>
+        <v>0.1069206120877624</v>
       </c>
       <c r="T48">
-        <v>1.172604816062392</v>
+        <v>1.191354493325942</v>
       </c>
       <c r="U48">
         <v>0.0672366166625341</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.7657632872467</v>
+        <v>3.685640664113792</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08036883178005731</v>
+        <v>0.08032333891378973</v>
       </c>
       <c r="C49">
-        <v>2199.38772605856</v>
+        <v>2160.689824065249</v>
       </c>
       <c r="D49">
-        <v>3886.92572605856</v>
+        <v>3888.881824065249</v>
       </c>
       <c r="E49">
-        <v>940.8380000000001</v>
+        <v>981.4920000000003</v>
       </c>
       <c r="F49">
-        <v>1910.738</v>
+        <v>1951.392</v>
       </c>
       <c r="G49">
         <v>223.2</v>
@@ -5305,28 +5305,28 @@
         <v>473.5</v>
       </c>
       <c r="M49">
-        <v>128.4715584485371</v>
+        <v>131.2049958623357</v>
       </c>
       <c r="N49">
-        <v>345.0284415514629</v>
+        <v>342.2950041376643</v>
       </c>
       <c r="O49">
-        <v>86.25711038786574</v>
+        <v>85.57375103441606</v>
       </c>
       <c r="P49">
-        <v>258.7713311635972</v>
+        <v>256.7212531032482</v>
       </c>
       <c r="Q49">
-        <v>391.3713311635972</v>
+        <v>389.3212531032482</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1069206120877624</v>
+        <v>0.1079195325293797</v>
       </c>
       <c r="T49">
-        <v>1.191354493325942</v>
+        <v>1.210825312022705</v>
       </c>
       <c r="U49">
         <v>0.0672366166625341</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.685640664113792</v>
+        <v>3.608856483611421</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08032333891378973</v>
+        <v>0.08027784604752214</v>
       </c>
       <c r="C50">
-        <v>2160.68982406525</v>
+        <v>2121.993891878541</v>
       </c>
       <c r="D50">
-        <v>3888.881824065249</v>
+        <v>3890.839891878541</v>
       </c>
       <c r="E50">
-        <v>981.4920000000001</v>
+        <v>1022.146</v>
       </c>
       <c r="F50">
-        <v>1951.392</v>
+        <v>1992.046</v>
       </c>
       <c r="G50">
         <v>223.2</v>
@@ -5387,28 +5387,28 @@
         <v>473.5</v>
       </c>
       <c r="M50">
-        <v>131.2049958623357</v>
+        <v>133.9384332761344</v>
       </c>
       <c r="N50">
-        <v>342.2950041376643</v>
+        <v>339.5615667238656</v>
       </c>
       <c r="O50">
-        <v>85.57375103441606</v>
+        <v>84.8903916809664</v>
       </c>
       <c r="P50">
-        <v>256.7212531032482</v>
+        <v>254.6711750428992</v>
       </c>
       <c r="Q50">
-        <v>389.3212531032482</v>
+        <v>387.2711750428992</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1079195325293797</v>
+        <v>0.1089576263216488</v>
       </c>
       <c r="T50">
-        <v>1.210825312022705</v>
+        <v>1.231059692236988</v>
       </c>
       <c r="U50">
         <v>0.0672366166625341</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.608856483611421</v>
+        <v>3.535206351292821</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08027784604752214</v>
+        <v>0.08128235318125457</v>
       </c>
       <c r="C51">
-        <v>2121.993891878541</v>
+        <v>2038.558552288423</v>
       </c>
       <c r="D51">
-        <v>3890.839891878541</v>
+        <v>3848.058552288423</v>
       </c>
       <c r="E51">
-        <v>1022.146</v>
+        <v>1062.8</v>
       </c>
       <c r="F51">
-        <v>1992.046</v>
+        <v>2032.7</v>
       </c>
       <c r="G51">
         <v>223.2</v>
@@ -5469,45 +5469,45 @@
         <v>473.5</v>
       </c>
       <c r="M51">
-        <v>133.9384332761344</v>
+        <v>142.3634306899331</v>
       </c>
       <c r="N51">
-        <v>339.5615667238656</v>
+        <v>331.1365693100669</v>
       </c>
       <c r="O51">
-        <v>84.8903916809664</v>
+        <v>82.78414232751673</v>
       </c>
       <c r="P51">
-        <v>254.6711750428992</v>
+        <v>248.3524269825502</v>
       </c>
       <c r="Q51">
-        <v>387.2711750428992</v>
+        <v>380.9524269825502</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1089576263216488</v>
+        <v>0.1100372438656086</v>
       </c>
       <c r="T51">
-        <v>1.231059692236988</v>
+        <v>1.252103447659842</v>
       </c>
       <c r="U51">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.05042746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.535206351292821</v>
+        <v>3.325994587973093</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08128235318125457</v>
+        <v>0.081257860314987</v>
       </c>
       <c r="C52">
-        <v>2038.558552288423</v>
+        <v>1998.93649533035</v>
       </c>
       <c r="D52">
-        <v>3848.058552288423</v>
+        <v>3849.090495330351</v>
       </c>
       <c r="E52">
-        <v>1062.8</v>
+        <v>1103.454</v>
       </c>
       <c r="F52">
-        <v>2032.7</v>
+        <v>2073.354</v>
       </c>
       <c r="G52">
         <v>223.2</v>
@@ -5551,28 +5551,28 @@
         <v>473.5</v>
       </c>
       <c r="M52">
-        <v>142.3634306899331</v>
+        <v>145.2106993037317</v>
       </c>
       <c r="N52">
-        <v>331.1365693100669</v>
+        <v>328.2893006962682</v>
       </c>
       <c r="O52">
-        <v>82.78414232751673</v>
+        <v>82.07232517406706</v>
       </c>
       <c r="P52">
-        <v>248.3524269825502</v>
+        <v>246.2169755222012</v>
       </c>
       <c r="Q52">
-        <v>380.9524269825502</v>
+        <v>378.8169755222012</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1100372438656086</v>
+        <v>0.1111609274317708</v>
       </c>
       <c r="T52">
-        <v>1.252103447659842</v>
+        <v>1.274006131875467</v>
       </c>
       <c r="U52">
         <v>0.07003661666253409</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.325994587973093</v>
+        <v>3.260779007816758</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.081257860314987</v>
+        <v>0.08123336744871942</v>
       </c>
       <c r="C53">
-        <v>1998.93649533035</v>
+        <v>1959.314991998</v>
       </c>
       <c r="D53">
-        <v>3849.090495330351</v>
+        <v>3850.122991998</v>
       </c>
       <c r="E53">
-        <v>1103.454</v>
+        <v>1144.108</v>
       </c>
       <c r="F53">
-        <v>2073.354</v>
+        <v>2114.008</v>
       </c>
       <c r="G53">
         <v>223.2</v>
@@ -5633,28 +5633,28 @@
         <v>473.5</v>
       </c>
       <c r="M53">
-        <v>145.2106993037317</v>
+        <v>148.0579679175304</v>
       </c>
       <c r="N53">
-        <v>328.2893006962682</v>
+        <v>325.4420320824696</v>
       </c>
       <c r="O53">
-        <v>82.07232517406706</v>
+        <v>81.3605080206174</v>
       </c>
       <c r="P53">
-        <v>246.2169755222012</v>
+        <v>244.0815240618522</v>
       </c>
       <c r="Q53">
-        <v>378.8169755222012</v>
+        <v>376.6815240618522</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1111609274317708</v>
+        <v>0.1123314311465232</v>
       </c>
       <c r="T53">
-        <v>1.274006131875467</v>
+        <v>1.296821427933408</v>
       </c>
       <c r="U53">
         <v>0.07003661666253409</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.260779007816758</v>
+        <v>3.198071719204898</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08123336744871942</v>
+        <v>0.08120887458245185</v>
       </c>
       <c r="C54">
-        <v>1959.314991998</v>
+        <v>1919.69404273701</v>
       </c>
       <c r="D54">
-        <v>3850.122991998</v>
+        <v>3851.156042737011</v>
       </c>
       <c r="E54">
-        <v>1144.108</v>
+        <v>1184.762</v>
       </c>
       <c r="F54">
-        <v>2114.008</v>
+        <v>2154.662</v>
       </c>
       <c r="G54">
         <v>223.2</v>
@@ -5715,28 +5715,28 @@
         <v>473.5</v>
       </c>
       <c r="M54">
-        <v>148.0579679175304</v>
+        <v>150.9052365313291</v>
       </c>
       <c r="N54">
-        <v>325.4420320824696</v>
+        <v>322.594763468671</v>
       </c>
       <c r="O54">
-        <v>81.3605080206174</v>
+        <v>80.64869086716774</v>
       </c>
       <c r="P54">
-        <v>244.0815240618522</v>
+        <v>241.9460726015032</v>
       </c>
       <c r="Q54">
-        <v>376.6815240618522</v>
+        <v>374.5460726015033</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1123314311465232</v>
+        <v>0.1135517435299884</v>
       </c>
       <c r="T54">
-        <v>1.296821427933408</v>
+        <v>1.32060758765339</v>
       </c>
       <c r="U54">
         <v>0.07003661666253409</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.198071719204898</v>
+        <v>3.137730743370843</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08120887458245185</v>
+        <v>0.08118438171618426</v>
       </c>
       <c r="C55">
-        <v>1919.69404273701</v>
+        <v>1880.073647993504</v>
       </c>
       <c r="D55">
-        <v>3851.156042737011</v>
+        <v>3852.189647993504</v>
       </c>
       <c r="E55">
-        <v>1184.762</v>
+        <v>1225.416</v>
       </c>
       <c r="F55">
-        <v>2154.662</v>
+        <v>2195.316</v>
       </c>
       <c r="G55">
         <v>223.2</v>
@@ -5797,28 +5797,28 @@
         <v>473.5</v>
       </c>
       <c r="M55">
-        <v>150.9052365313291</v>
+        <v>153.7525051451277</v>
       </c>
       <c r="N55">
-        <v>322.594763468671</v>
+        <v>319.7474948548723</v>
       </c>
       <c r="O55">
-        <v>80.64869086716774</v>
+        <v>79.93687371371807</v>
       </c>
       <c r="P55">
-        <v>241.9460726015032</v>
+        <v>239.8106211411542</v>
       </c>
       <c r="Q55">
-        <v>374.5460726015033</v>
+        <v>372.4106211411543</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1135517435299884</v>
+        <v>0.1148251129736043</v>
       </c>
       <c r="T55">
-        <v>1.32060758765339</v>
+        <v>1.345427928230763</v>
       </c>
       <c r="U55">
         <v>0.07003661666253409</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.137730743370843</v>
+        <v>3.079624618493605</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08118438171618426</v>
+        <v>0.08115988884991668</v>
       </c>
       <c r="C56">
-        <v>1880.073647993504</v>
+        <v>1840.453808214076</v>
       </c>
       <c r="D56">
-        <v>3852.189647993504</v>
+        <v>3853.223808214077</v>
       </c>
       <c r="E56">
-        <v>1225.416</v>
+        <v>1266.07</v>
       </c>
       <c r="F56">
-        <v>2195.316</v>
+        <v>2235.97</v>
       </c>
       <c r="G56">
         <v>223.2</v>
@@ -5879,28 +5879,28 @@
         <v>473.5</v>
       </c>
       <c r="M56">
-        <v>153.7525051451277</v>
+        <v>156.5997737589264</v>
       </c>
       <c r="N56">
-        <v>319.7474948548723</v>
+        <v>316.9002262410736</v>
       </c>
       <c r="O56">
-        <v>79.93687371371807</v>
+        <v>79.2250565602684</v>
       </c>
       <c r="P56">
-        <v>239.8106211411542</v>
+        <v>237.6751696808052</v>
       </c>
       <c r="Q56">
-        <v>372.4106211411543</v>
+        <v>370.2751696808052</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1148251129736043</v>
+        <v>0.1161550766147142</v>
       </c>
       <c r="T56">
-        <v>1.345427928230763</v>
+        <v>1.371351395056018</v>
       </c>
       <c r="U56">
         <v>0.07003661666253409</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.079624618493605</v>
+        <v>3.023631443611903</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08115988884991668</v>
+        <v>0.08441139598364911</v>
       </c>
       <c r="C57">
-        <v>1840.453808214076</v>
+        <v>1667.200543699896</v>
       </c>
       <c r="D57">
-        <v>3853.223808214077</v>
+        <v>3720.624543699897</v>
       </c>
       <c r="E57">
-        <v>1266.07</v>
+        <v>1306.724</v>
       </c>
       <c r="F57">
-        <v>2235.97</v>
+        <v>2276.624</v>
       </c>
       <c r="G57">
         <v>223.2</v>
@@ -5961,45 +5961,45 @@
         <v>473.5</v>
       </c>
       <c r="M57">
-        <v>156.5997737589264</v>
+        <v>177.2047095727251</v>
       </c>
       <c r="N57">
-        <v>316.9002262410736</v>
+        <v>296.2952904272749</v>
       </c>
       <c r="O57">
-        <v>79.2250565602684</v>
+        <v>74.07382260681874</v>
       </c>
       <c r="P57">
-        <v>237.6751696808052</v>
+        <v>222.2214678204562</v>
       </c>
       <c r="Q57">
-        <v>370.2751696808052</v>
+        <v>354.8214678204562</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1161550766147142</v>
+        <v>0.1175454931486018</v>
       </c>
       <c r="T57">
-        <v>1.371351395056018</v>
+        <v>1.398453201282422</v>
       </c>
       <c r="U57">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.05252746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.023631443611903</v>
+        <v>2.672050879131262</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08441139598364911</v>
+        <v>0.08444540311738154</v>
       </c>
       <c r="C58">
-        <v>1667.200543699896</v>
+        <v>1625.207909972298</v>
       </c>
       <c r="D58">
-        <v>3720.624543699897</v>
+        <v>3719.285909972299</v>
       </c>
       <c r="E58">
-        <v>1306.724</v>
+        <v>1347.378</v>
       </c>
       <c r="F58">
-        <v>2276.624</v>
+        <v>2317.278</v>
       </c>
       <c r="G58">
         <v>223.2</v>
@@ -6043,28 +6043,28 @@
         <v>473.5</v>
       </c>
       <c r="M58">
-        <v>177.2047095727251</v>
+        <v>180.3690793865237</v>
       </c>
       <c r="N58">
-        <v>296.2952904272749</v>
+        <v>293.1309206134763</v>
       </c>
       <c r="O58">
-        <v>74.07382260681874</v>
+        <v>73.28273015336907</v>
       </c>
       <c r="P58">
-        <v>222.2214678204562</v>
+        <v>219.8481904601072</v>
       </c>
       <c r="Q58">
-        <v>354.8214678204562</v>
+        <v>352.4481904601072</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1175454931486018</v>
+        <v>0.1190005802189493</v>
       </c>
       <c r="T58">
-        <v>1.398453201282422</v>
+        <v>1.426815556635635</v>
       </c>
       <c r="U58">
         <v>0.07783661666253411</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.672050879131262</v>
+        <v>2.625172793532468</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08444540311738154</v>
+        <v>0.08447941025111397</v>
       </c>
       <c r="C59">
-        <v>1625.207909972298</v>
+        <v>1583.216239145284</v>
       </c>
       <c r="D59">
-        <v>3719.285909972299</v>
+        <v>3717.948239145284</v>
       </c>
       <c r="E59">
-        <v>1347.378</v>
+        <v>1388.032</v>
       </c>
       <c r="F59">
-        <v>2317.278</v>
+        <v>2357.932</v>
       </c>
       <c r="G59">
         <v>223.2</v>
@@ -6125,28 +6125,28 @@
         <v>473.5</v>
       </c>
       <c r="M59">
-        <v>180.3690793865237</v>
+        <v>183.5334492003224</v>
       </c>
       <c r="N59">
-        <v>293.1309206134763</v>
+        <v>289.9665507996776</v>
       </c>
       <c r="O59">
-        <v>73.28273015336907</v>
+        <v>72.49163769991941</v>
       </c>
       <c r="P59">
-        <v>219.8481904601072</v>
+        <v>217.4749130997582</v>
       </c>
       <c r="Q59">
-        <v>352.4481904601072</v>
+        <v>350.0749130997582</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1190005802189493</v>
+        <v>0.1205249571497896</v>
       </c>
       <c r="T59">
-        <v>1.426815556635635</v>
+        <v>1.456528500339001</v>
       </c>
       <c r="U59">
         <v>0.07783661666253411</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.625172793532468</v>
+        <v>2.579911193643977</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08447941025111395</v>
+        <v>0.08451341738484638</v>
       </c>
       <c r="C60">
-        <v>1583.216239145285</v>
+        <v>1541.225530180282</v>
       </c>
       <c r="D60">
-        <v>3717.948239145285</v>
+        <v>3716.611530180282</v>
       </c>
       <c r="E60">
-        <v>1388.032</v>
+        <v>1428.686</v>
       </c>
       <c r="F60">
-        <v>2357.932</v>
+        <v>2398.586</v>
       </c>
       <c r="G60">
         <v>223.2</v>
@@ -6207,28 +6207,28 @@
         <v>473.5</v>
       </c>
       <c r="M60">
-        <v>183.5334492003224</v>
+        <v>186.697819014121</v>
       </c>
       <c r="N60">
-        <v>289.9665507996776</v>
+        <v>286.802180985879</v>
       </c>
       <c r="O60">
-        <v>72.49163769991941</v>
+        <v>71.70054524646974</v>
       </c>
       <c r="P60">
-        <v>217.4749130997582</v>
+        <v>215.1016357394092</v>
       </c>
       <c r="Q60">
-        <v>350.0749130997582</v>
+        <v>347.7016357394093</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1205249571497896</v>
+        <v>0.1221236939309147</v>
       </c>
       <c r="T60">
-        <v>1.456528500339</v>
+        <v>1.487690855930335</v>
       </c>
       <c r="U60">
         <v>0.07783661666253411</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.579911193643977</v>
+        <v>2.536183885277131</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08451341738484638</v>
+        <v>0.08630242451857881</v>
       </c>
       <c r="C61">
-        <v>1541.225530180282</v>
+        <v>1431.581656449361</v>
       </c>
       <c r="D61">
-        <v>3716.611530180282</v>
+        <v>3647.621656449361</v>
       </c>
       <c r="E61">
-        <v>1428.686</v>
+        <v>1469.34</v>
       </c>
       <c r="F61">
-        <v>2398.586</v>
+        <v>2439.24</v>
       </c>
       <c r="G61">
         <v>223.2</v>
@@ -6289,45 +6289,45 @@
         <v>473.5</v>
       </c>
       <c r="M61">
-        <v>186.697819014121</v>
+        <v>199.3752248279197</v>
       </c>
       <c r="N61">
-        <v>286.802180985879</v>
+        <v>274.1247751720804</v>
       </c>
       <c r="O61">
-        <v>71.70054524646974</v>
+        <v>68.53119379302009</v>
       </c>
       <c r="P61">
-        <v>215.1016357394092</v>
+        <v>205.5935813790603</v>
       </c>
       <c r="Q61">
-        <v>347.7016357394093</v>
+        <v>338.1935813790603</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1221236939309147</v>
+        <v>0.1238023675510961</v>
       </c>
       <c r="T61">
-        <v>1.487690855930335</v>
+        <v>1.520411329301237</v>
       </c>
       <c r="U61">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.05837746249690058</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.536183885277131</v>
+        <v>2.374918951984515</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08630242451857881</v>
+        <v>0.08636568165231123</v>
       </c>
       <c r="C62">
-        <v>1431.581656449361</v>
+        <v>1388.535109619098</v>
       </c>
       <c r="D62">
-        <v>3647.621656449361</v>
+        <v>3645.229109619098</v>
       </c>
       <c r="E62">
-        <v>1469.34</v>
+        <v>1509.994</v>
       </c>
       <c r="F62">
-        <v>2439.24</v>
+        <v>2479.894</v>
       </c>
       <c r="G62">
         <v>223.2</v>
@@ -6371,28 +6371,28 @@
         <v>473.5</v>
       </c>
       <c r="M62">
-        <v>199.3752248279197</v>
+        <v>202.6981452417183</v>
       </c>
       <c r="N62">
-        <v>274.1247751720804</v>
+        <v>270.8018547582817</v>
       </c>
       <c r="O62">
-        <v>68.53119379302009</v>
+        <v>67.70046368957043</v>
       </c>
       <c r="P62">
-        <v>205.5935813790603</v>
+        <v>203.1013910687113</v>
       </c>
       <c r="Q62">
-        <v>338.1935813790603</v>
+        <v>335.7013910687113</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1238023675510961</v>
+        <v>0.1255671269979535</v>
       </c>
       <c r="T62">
-        <v>1.520411329301237</v>
+        <v>1.554809775665519</v>
       </c>
       <c r="U62">
         <v>0.0817366166625341</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.374918951984515</v>
+        <v>2.335985854410998</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08636568165231123</v>
+        <v>0.08642893878604366</v>
       </c>
       <c r="C63">
-        <v>1388.535109619098</v>
+        <v>1345.491699368595</v>
       </c>
       <c r="D63">
-        <v>3645.229109619098</v>
+        <v>3642.839699368596</v>
       </c>
       <c r="E63">
-        <v>1509.994</v>
+        <v>1550.648</v>
       </c>
       <c r="F63">
-        <v>2479.894</v>
+        <v>2520.548</v>
       </c>
       <c r="G63">
         <v>223.2</v>
@@ -6453,28 +6453,28 @@
         <v>473.5</v>
       </c>
       <c r="M63">
-        <v>202.6981452417183</v>
+        <v>206.021065655517</v>
       </c>
       <c r="N63">
-        <v>270.8018547582817</v>
+        <v>267.478934344483</v>
       </c>
       <c r="O63">
-        <v>67.70046368957043</v>
+        <v>66.86973358612074</v>
       </c>
       <c r="P63">
-        <v>203.1013910687113</v>
+        <v>200.6092007583622</v>
       </c>
       <c r="Q63">
-        <v>335.7013910687113</v>
+        <v>333.2092007583623</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1255671269979535</v>
+        <v>0.1274247685209613</v>
       </c>
       <c r="T63">
-        <v>1.554809775665519</v>
+        <v>1.591018666575289</v>
       </c>
       <c r="U63">
         <v>0.0817366166625341</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.335985854410998</v>
+        <v>2.298308663210821</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08642893878604366</v>
+        <v>0.08649219591977605</v>
       </c>
       <c r="C64">
-        <v>1345.491699368595</v>
+        <v>1302.451419533905</v>
       </c>
       <c r="D64">
-        <v>3642.839699368596</v>
+        <v>3640.453419533905</v>
       </c>
       <c r="E64">
-        <v>1550.648</v>
+        <v>1591.302</v>
       </c>
       <c r="F64">
-        <v>2520.548</v>
+        <v>2561.202</v>
       </c>
       <c r="G64">
         <v>223.2</v>
@@ -6535,28 +6535,28 @@
         <v>473.5</v>
       </c>
       <c r="M64">
-        <v>206.021065655517</v>
+        <v>209.3439860693157</v>
       </c>
       <c r="N64">
-        <v>267.478934344483</v>
+        <v>264.1560139306844</v>
       </c>
       <c r="O64">
-        <v>66.86973358612074</v>
+        <v>66.03900348267109</v>
       </c>
       <c r="P64">
-        <v>200.6092007583622</v>
+        <v>198.1170104480133</v>
       </c>
       <c r="Q64">
-        <v>333.2092007583623</v>
+        <v>330.7170104480133</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1274247685209613</v>
+        <v>0.1293828230992668</v>
       </c>
       <c r="T64">
-        <v>1.591018666575289</v>
+        <v>1.629184794831533</v>
       </c>
       <c r="U64">
         <v>0.0817366166625341</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.298308663210821</v>
+        <v>2.261827573318586</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08649219591977605</v>
+        <v>0.08655545305350848</v>
       </c>
       <c r="C65">
-        <v>1302.451419533905</v>
+        <v>1259.414263967219</v>
       </c>
       <c r="D65">
-        <v>3640.453419533905</v>
+        <v>3638.070263967219</v>
       </c>
       <c r="E65">
-        <v>1591.302</v>
+        <v>1631.956</v>
       </c>
       <c r="F65">
-        <v>2561.202</v>
+        <v>2601.856</v>
       </c>
       <c r="G65">
         <v>223.2</v>
@@ -6617,28 +6617,28 @@
         <v>473.5</v>
       </c>
       <c r="M65">
-        <v>209.3439860693157</v>
+        <v>212.6669064831143</v>
       </c>
       <c r="N65">
-        <v>264.1560139306844</v>
+        <v>260.8330935168857</v>
       </c>
       <c r="O65">
-        <v>66.03900348267109</v>
+        <v>65.20827337922142</v>
       </c>
       <c r="P65">
-        <v>198.1170104480133</v>
+        <v>195.6248201376643</v>
       </c>
       <c r="Q65">
-        <v>330.7170104480133</v>
+        <v>328.2248201376643</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1293828230992668</v>
+        <v>0.1314496584874781</v>
       </c>
       <c r="T65">
-        <v>1.629184794831533</v>
+        <v>1.669471263546457</v>
       </c>
       <c r="U65">
         <v>0.0817366166625341</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.261827573318586</v>
+        <v>2.226486517485482</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08655545305350848</v>
+        <v>0.0866187101872409</v>
       </c>
       <c r="C66">
-        <v>1259.414263967219</v>
+        <v>1216.380226536819</v>
       </c>
       <c r="D66">
-        <v>3638.070263967219</v>
+        <v>3635.69022653682</v>
       </c>
       <c r="E66">
-        <v>1631.956</v>
+        <v>1672.61</v>
       </c>
       <c r="F66">
-        <v>2601.856</v>
+        <v>2642.51</v>
       </c>
       <c r="G66">
         <v>223.2</v>
@@ -6699,28 +6699,28 @@
         <v>473.5</v>
       </c>
       <c r="M66">
-        <v>212.6669064831143</v>
+        <v>215.989826896913</v>
       </c>
       <c r="N66">
-        <v>260.8330935168857</v>
+        <v>257.510173103087</v>
       </c>
       <c r="O66">
-        <v>65.20827337922142</v>
+        <v>64.37754327577176</v>
       </c>
       <c r="P66">
-        <v>195.6248201376643</v>
+        <v>193.1326298273153</v>
       </c>
       <c r="Q66">
-        <v>328.2248201376643</v>
+        <v>325.7326298273153</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1314496584874781</v>
+        <v>0.1336345987550158</v>
       </c>
       <c r="T66">
-        <v>1.669471263546457</v>
+        <v>1.712059816187948</v>
       </c>
       <c r="U66">
         <v>0.0817366166625341</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.226486517485482</v>
+        <v>2.192232878754937</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0866187101872409</v>
+        <v>0.08668196732097333</v>
       </c>
       <c r="C67">
-        <v>1216.380226536819</v>
+        <v>1173.349301127022</v>
       </c>
       <c r="D67">
-        <v>3635.69022653682</v>
+        <v>3633.313301127022</v>
       </c>
       <c r="E67">
-        <v>1672.61</v>
+        <v>1713.264</v>
       </c>
       <c r="F67">
-        <v>2642.51</v>
+        <v>2683.164</v>
       </c>
       <c r="G67">
         <v>223.2</v>
@@ -6781,28 +6781,28 @@
         <v>473.5</v>
       </c>
       <c r="M67">
-        <v>215.989826896913</v>
+        <v>219.3127473107116</v>
       </c>
       <c r="N67">
-        <v>257.510173103087</v>
+        <v>254.1872526892884</v>
       </c>
       <c r="O67">
-        <v>64.37754327577176</v>
+        <v>63.54681317232209</v>
       </c>
       <c r="P67">
-        <v>193.1326298273153</v>
+        <v>190.6404395169663</v>
       </c>
       <c r="Q67">
-        <v>325.7326298273153</v>
+        <v>323.2404395169663</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1336345987550158</v>
+        <v>0.135948064920644</v>
       </c>
       <c r="T67">
-        <v>1.712059816187948</v>
+        <v>1.757153577808351</v>
       </c>
       <c r="U67">
         <v>0.0817366166625341</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.192232878754937</v>
+        <v>2.159017229076832</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08668196732097333</v>
+        <v>0.08674522445470575</v>
       </c>
       <c r="C68">
-        <v>1173.349301127022</v>
+        <v>1130.321481638126</v>
       </c>
       <c r="D68">
-        <v>3633.313301127022</v>
+        <v>3630.939481638127</v>
       </c>
       <c r="E68">
-        <v>1713.264</v>
+        <v>1753.918</v>
       </c>
       <c r="F68">
-        <v>2683.164</v>
+        <v>2723.818</v>
       </c>
       <c r="G68">
         <v>223.2</v>
@@ -6863,28 +6863,28 @@
         <v>473.5</v>
       </c>
       <c r="M68">
-        <v>219.3127473107116</v>
+        <v>222.6356677245103</v>
       </c>
       <c r="N68">
-        <v>254.1872526892884</v>
+        <v>250.8643322754897</v>
       </c>
       <c r="O68">
-        <v>63.54681317232209</v>
+        <v>62.71608306887242</v>
       </c>
       <c r="P68">
-        <v>190.6404395169663</v>
+        <v>188.1482492066173</v>
       </c>
       <c r="Q68">
-        <v>323.2404395169663</v>
+        <v>320.7482492066173</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.135948064920644</v>
+        <v>0.1384017411569163</v>
       </c>
       <c r="T68">
-        <v>1.757153577808351</v>
+        <v>1.804980294678475</v>
       </c>
       <c r="U68">
         <v>0.0817366166625341</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.159017229076832</v>
+        <v>2.126793091329416</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08674522445470575</v>
+        <v>0.08680848158843818</v>
       </c>
       <c r="C69">
-        <v>1130.321481638126</v>
+        <v>1087.296761986361</v>
       </c>
       <c r="D69">
-        <v>3630.939481638127</v>
+        <v>3628.568761986362</v>
       </c>
       <c r="E69">
-        <v>1753.918</v>
+        <v>1794.572</v>
       </c>
       <c r="F69">
-        <v>2723.818</v>
+        <v>2764.472</v>
       </c>
       <c r="G69">
         <v>223.2</v>
@@ -6945,28 +6945,28 @@
         <v>473.5</v>
       </c>
       <c r="M69">
-        <v>222.6356677245103</v>
+        <v>225.958588138309</v>
       </c>
       <c r="N69">
-        <v>250.8643322754897</v>
+        <v>247.541411861691</v>
       </c>
       <c r="O69">
-        <v>62.71608306887242</v>
+        <v>61.88535296542275</v>
       </c>
       <c r="P69">
-        <v>188.1482492066173</v>
+        <v>185.6560588962683</v>
       </c>
       <c r="Q69">
-        <v>320.7482492066173</v>
+        <v>318.2560588962683</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1384017411569163</v>
+        <v>0.1410087721579556</v>
       </c>
       <c r="T69">
-        <v>1.804980294678475</v>
+        <v>1.855796181352981</v>
       </c>
       <c r="U69">
         <v>0.0817366166625341</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.126793091329416</v>
+        <v>2.095516722339278</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08680848158843818</v>
+        <v>0.08687173872217059</v>
       </c>
       <c r="C70">
-        <v>1087.296761986361</v>
+        <v>1044.275136103835</v>
       </c>
       <c r="D70">
-        <v>3628.568761986362</v>
+        <v>3626.201136103835</v>
       </c>
       <c r="E70">
-        <v>1794.572</v>
+        <v>1835.226</v>
       </c>
       <c r="F70">
-        <v>2764.472</v>
+        <v>2805.126</v>
       </c>
       <c r="G70">
         <v>223.2</v>
@@ -7027,28 +7027,28 @@
         <v>473.5</v>
       </c>
       <c r="M70">
-        <v>225.958588138309</v>
+        <v>229.2815085521076</v>
       </c>
       <c r="N70">
-        <v>247.541411861691</v>
+        <v>244.2184914478924</v>
       </c>
       <c r="O70">
-        <v>61.88535296542275</v>
+        <v>61.05462286197309</v>
       </c>
       <c r="P70">
-        <v>185.6560588962683</v>
+        <v>183.1638685859193</v>
       </c>
       <c r="Q70">
-        <v>318.2560588962683</v>
+        <v>315.7638685859193</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1410087721579556</v>
+        <v>0.143783998707449</v>
       </c>
       <c r="T70">
-        <v>1.855796181352981</v>
+        <v>1.909890512329069</v>
       </c>
       <c r="U70">
         <v>0.0817366166625341</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.095516722339278</v>
+        <v>2.065146914769143</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08687173872217059</v>
+        <v>0.086934995855903</v>
       </c>
       <c r="C71">
-        <v>1044.275136103835</v>
+        <v>1001.256597938482</v>
       </c>
       <c r="D71">
-        <v>3626.201136103835</v>
+        <v>3623.836597938482</v>
       </c>
       <c r="E71">
-        <v>1835.226</v>
+        <v>1875.88</v>
       </c>
       <c r="F71">
-        <v>2805.126</v>
+        <v>2845.78</v>
       </c>
       <c r="G71">
         <v>223.2</v>
@@ -7109,28 +7109,28 @@
         <v>473.5</v>
       </c>
       <c r="M71">
-        <v>229.2815085521076</v>
+        <v>232.6044289659063</v>
       </c>
       <c r="N71">
-        <v>244.2184914478924</v>
+        <v>240.8955710340937</v>
       </c>
       <c r="O71">
-        <v>61.05462286197309</v>
+        <v>60.22389275852343</v>
       </c>
       <c r="P71">
-        <v>183.1638685859193</v>
+        <v>180.6716782755703</v>
       </c>
       <c r="Q71">
-        <v>315.7638685859193</v>
+        <v>313.2716782755703</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.143783998707449</v>
+        <v>0.1467442403602421</v>
       </c>
       <c r="T71">
-        <v>1.909890512329069</v>
+        <v>1.967591132036896</v>
       </c>
       <c r="U71">
         <v>0.0817366166625341</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.065146914769143</v>
+        <v>2.035644815986727</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.086934995855903</v>
+        <v>0.08699825298963544</v>
       </c>
       <c r="C72">
-        <v>1001.256597938482</v>
+        <v>958.2411414540102</v>
       </c>
       <c r="D72">
-        <v>3623.836597938482</v>
+        <v>3621.475141454011</v>
       </c>
       <c r="E72">
-        <v>1875.88</v>
+        <v>1916.534</v>
       </c>
       <c r="F72">
-        <v>2845.78</v>
+        <v>2886.434</v>
       </c>
       <c r="G72">
         <v>223.2</v>
@@ -7191,28 +7191,28 @@
         <v>473.5</v>
       </c>
       <c r="M72">
-        <v>232.6044289659063</v>
+        <v>235.927349379705</v>
       </c>
       <c r="N72">
-        <v>240.8955710340937</v>
+        <v>237.572650620295</v>
       </c>
       <c r="O72">
-        <v>60.22389275852343</v>
+        <v>59.39316265507376</v>
       </c>
       <c r="P72">
-        <v>180.6716782755703</v>
+        <v>178.1794879652213</v>
       </c>
       <c r="Q72">
-        <v>313.2716782755703</v>
+        <v>310.7794879652213</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1467442403602421</v>
+        <v>0.1499086366097795</v>
       </c>
       <c r="T72">
-        <v>1.967591132036896</v>
+        <v>2.029271104828021</v>
       </c>
       <c r="U72">
         <v>0.0817366166625341</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.035644815986727</v>
+        <v>2.006973762240435</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08699825298963546</v>
+        <v>0.09472951012336786</v>
       </c>
       <c r="C73">
-        <v>958.2411414540102</v>
+        <v>650.4360433405727</v>
       </c>
       <c r="D73">
-        <v>3621.47514145401</v>
+        <v>3354.324043340573</v>
       </c>
       <c r="E73">
-        <v>1916.534</v>
+        <v>1957.188</v>
       </c>
       <c r="F73">
-        <v>2886.434</v>
+        <v>2927.088</v>
       </c>
       <c r="G73">
         <v>223.2</v>
@@ -7273,45 +7273,45 @@
         <v>473.5</v>
       </c>
       <c r="M73">
-        <v>235.9273493797049</v>
+        <v>280.8149193935036</v>
       </c>
       <c r="N73">
-        <v>237.5726506202951</v>
+        <v>192.6850806064964</v>
       </c>
       <c r="O73">
-        <v>59.39316265507377</v>
+        <v>48.1712701516241</v>
       </c>
       <c r="P73">
-        <v>178.1794879652213</v>
+        <v>144.5138104548723</v>
       </c>
       <c r="Q73">
-        <v>310.7794879652213</v>
+        <v>277.1138104548724</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1499086366097794</v>
+        <v>0.1532990611628552</v>
       </c>
       <c r="T73">
-        <v>2.029271104828021</v>
+        <v>2.095356789961369</v>
       </c>
       <c r="U73">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.06130246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.006973762240436</v>
+        <v>1.686163972422307</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09472951012336786</v>
+        <v>0.09489926725710028</v>
       </c>
       <c r="C74">
-        <v>650.4360433405727</v>
+        <v>604.3576458696302</v>
       </c>
       <c r="D74">
-        <v>3354.324043340573</v>
+        <v>3348.899645869631</v>
       </c>
       <c r="E74">
-        <v>1957.188</v>
+        <v>1997.842</v>
       </c>
       <c r="F74">
-        <v>2927.088</v>
+        <v>2967.742</v>
       </c>
       <c r="G74">
         <v>223.2</v>
@@ -7355,28 +7355,28 @@
         <v>473.5</v>
       </c>
       <c r="M74">
-        <v>280.8149193935036</v>
+        <v>284.7151266073023</v>
       </c>
       <c r="N74">
-        <v>192.6850806064964</v>
+        <v>188.7848733926977</v>
       </c>
       <c r="O74">
-        <v>48.1712701516241</v>
+        <v>47.19621834817443</v>
       </c>
       <c r="P74">
-        <v>144.5138104548723</v>
+        <v>141.5886550445233</v>
       </c>
       <c r="Q74">
-        <v>277.1138104548724</v>
+        <v>274.1886550445233</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1532990611628552</v>
+        <v>0.156940628275418</v>
       </c>
       <c r="T74">
-        <v>2.095356789961369</v>
+        <v>2.166337711030521</v>
       </c>
       <c r="U74">
         <v>0.0959366166625341</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.686163972422307</v>
+        <v>1.663065835813782</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09489926725710028</v>
+        <v>0.0950690243908327</v>
       </c>
       <c r="C75">
-        <v>604.3576458696302</v>
+        <v>558.2967640481124</v>
       </c>
       <c r="D75">
-        <v>3348.899645869631</v>
+        <v>3343.492764048113</v>
       </c>
       <c r="E75">
-        <v>1997.842</v>
+        <v>2038.496</v>
       </c>
       <c r="F75">
-        <v>2967.742</v>
+        <v>3008.396</v>
       </c>
       <c r="G75">
         <v>223.2</v>
@@ -7437,28 +7437,28 @@
         <v>473.5</v>
       </c>
       <c r="M75">
-        <v>284.7151266073023</v>
+        <v>288.6153338211009</v>
       </c>
       <c r="N75">
-        <v>188.7848733926977</v>
+        <v>184.8846661788991</v>
       </c>
       <c r="O75">
-        <v>47.19621834817443</v>
+        <v>46.22116654472477</v>
       </c>
       <c r="P75">
-        <v>141.5886550445233</v>
+        <v>138.6634996341743</v>
       </c>
       <c r="Q75">
-        <v>274.1886550445233</v>
+        <v>271.2634996341743</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.156940628275418</v>
+        <v>0.1608623159351011</v>
       </c>
       <c r="T75">
-        <v>2.166337711030521</v>
+        <v>2.242778702951146</v>
       </c>
       <c r="U75">
         <v>0.0959366166625341</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.663065835813782</v>
+        <v>1.64059197316765</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0950690243908327</v>
+        <v>0.09523878152456514</v>
       </c>
       <c r="C76">
-        <v>558.2967640481124</v>
+        <v>512.2533131744167</v>
       </c>
       <c r="D76">
-        <v>3343.492764048113</v>
+        <v>3338.103313174417</v>
       </c>
       <c r="E76">
-        <v>2038.496</v>
+        <v>2079.15</v>
       </c>
       <c r="F76">
-        <v>3008.396</v>
+        <v>3049.05</v>
       </c>
       <c r="G76">
         <v>223.2</v>
@@ -7519,28 +7519,28 @@
         <v>473.5</v>
       </c>
       <c r="M76">
-        <v>288.6153338211009</v>
+        <v>292.5155410348996</v>
       </c>
       <c r="N76">
-        <v>184.8846661788991</v>
+        <v>180.9844589651004</v>
       </c>
       <c r="O76">
-        <v>46.22116654472477</v>
+        <v>45.24611474127509</v>
       </c>
       <c r="P76">
-        <v>138.6634996341743</v>
+        <v>135.7383442238253</v>
       </c>
       <c r="Q76">
-        <v>271.2634996341743</v>
+        <v>268.3383442238253</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1608623159351011</v>
+        <v>0.1650977386075588</v>
       </c>
       <c r="T76">
-        <v>2.242778702951146</v>
+        <v>2.325334974225422</v>
       </c>
       <c r="U76">
         <v>0.0959366166625341</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.64059197316765</v>
+        <v>1.618717413525415</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09523878152456514</v>
+        <v>0.09540853865829754</v>
       </c>
       <c r="C77">
-        <v>512.2533131744167</v>
+        <v>466.227209092192</v>
       </c>
       <c r="D77">
-        <v>3338.103313174417</v>
+        <v>3332.731209092192</v>
       </c>
       <c r="E77">
-        <v>2079.15</v>
+        <v>2119.804</v>
       </c>
       <c r="F77">
-        <v>3049.05</v>
+        <v>3089.704</v>
       </c>
       <c r="G77">
         <v>223.2</v>
@@ -7601,28 +7601,28 @@
         <v>473.5</v>
       </c>
       <c r="M77">
-        <v>292.5155410348996</v>
+        <v>296.4157482486983</v>
       </c>
       <c r="N77">
-        <v>180.9844589651004</v>
+        <v>177.0842517513017</v>
       </c>
       <c r="O77">
-        <v>45.24611474127509</v>
+        <v>44.27106293782543</v>
       </c>
       <c r="P77">
-        <v>135.7383442238253</v>
+        <v>132.8131888134763</v>
       </c>
       <c r="Q77">
-        <v>268.3383442238253</v>
+        <v>265.4131888134763</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1650977386075588</v>
+        <v>0.169686113169388</v>
       </c>
       <c r="T77">
-        <v>2.325334974225422</v>
+        <v>2.414770934772553</v>
       </c>
       <c r="U77">
         <v>0.0959366166625341</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.618717413525415</v>
+        <v>1.597418500189554</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09540853865829754</v>
+        <v>0.09557829579202998</v>
       </c>
       <c r="C78">
-        <v>466.227209092192</v>
+        <v>420.2183681859547</v>
       </c>
       <c r="D78">
-        <v>3332.731209092192</v>
+        <v>3327.376368185955</v>
       </c>
       <c r="E78">
-        <v>2119.804</v>
+        <v>2160.458</v>
       </c>
       <c r="F78">
-        <v>3089.704</v>
+        <v>3130.358</v>
       </c>
       <c r="G78">
         <v>223.2</v>
@@ -7683,28 +7683,28 @@
         <v>473.5</v>
       </c>
       <c r="M78">
-        <v>296.4157482486983</v>
+        <v>300.315955462497</v>
       </c>
       <c r="N78">
-        <v>177.0842517513017</v>
+        <v>173.184044537503</v>
       </c>
       <c r="O78">
-        <v>44.27106293782543</v>
+        <v>43.29601113437576</v>
       </c>
       <c r="P78">
-        <v>132.8131888134763</v>
+        <v>129.8880334031273</v>
       </c>
       <c r="Q78">
-        <v>265.4131888134763</v>
+        <v>262.4880334031273</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.169686113169388</v>
+        <v>0.1746734768235502</v>
       </c>
       <c r="T78">
-        <v>2.414770934772553</v>
+        <v>2.511983935367262</v>
       </c>
       <c r="U78">
         <v>0.0959366166625341</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.597418500189554</v>
+        <v>1.576672805381897</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09557829579202998</v>
+        <v>0.09574805292576238</v>
       </c>
       <c r="C79">
-        <v>420.2183681859547</v>
+        <v>374.2267073767566</v>
       </c>
       <c r="D79">
-        <v>3327.376368185955</v>
+        <v>3322.038707376757</v>
       </c>
       <c r="E79">
-        <v>2160.458</v>
+        <v>2201.112</v>
       </c>
       <c r="F79">
-        <v>3130.358</v>
+        <v>3171.012</v>
       </c>
       <c r="G79">
         <v>223.2</v>
@@ -7765,28 +7765,28 @@
         <v>473.5</v>
       </c>
       <c r="M79">
-        <v>300.315955462497</v>
+        <v>304.2161626762956</v>
       </c>
       <c r="N79">
-        <v>173.184044537503</v>
+        <v>169.2838373237044</v>
       </c>
       <c r="O79">
-        <v>43.29601113437576</v>
+        <v>42.3209593309261</v>
       </c>
       <c r="P79">
-        <v>129.8880334031273</v>
+        <v>126.9628779927783</v>
       </c>
       <c r="Q79">
-        <v>262.4880334031273</v>
+        <v>259.5628779927783</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1746734768235502</v>
+        <v>0.1801142371735452</v>
       </c>
       <c r="T79">
-        <v>2.511983935367262</v>
+        <v>2.61803448147058</v>
       </c>
       <c r="U79">
         <v>0.0959366166625341</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.576672805381897</v>
+        <v>1.556459051466745</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09574805292576238</v>
+        <v>0.09591781005949482</v>
       </c>
       <c r="C80">
-        <v>374.2267073767566</v>
+        <v>328.2521441178824</v>
       </c>
       <c r="D80">
-        <v>3322.038707376757</v>
+        <v>3316.718144117883</v>
       </c>
       <c r="E80">
-        <v>2201.112</v>
+        <v>2241.766</v>
       </c>
       <c r="F80">
-        <v>3171.012</v>
+        <v>3211.666</v>
       </c>
       <c r="G80">
         <v>223.2</v>
@@ -7847,28 +7847,28 @@
         <v>473.5</v>
       </c>
       <c r="M80">
-        <v>304.2161626762956</v>
+        <v>308.1163698900942</v>
       </c>
       <c r="N80">
-        <v>169.2838373237044</v>
+        <v>165.3836301099058</v>
       </c>
       <c r="O80">
-        <v>42.3209593309261</v>
+        <v>41.34590752747644</v>
       </c>
       <c r="P80">
-        <v>126.9628779927783</v>
+        <v>124.0377225824293</v>
       </c>
       <c r="Q80">
-        <v>259.5628779927783</v>
+        <v>256.6377225824293</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1801142371735452</v>
+        <v>0.1860731651759208</v>
       </c>
       <c r="T80">
-        <v>2.61803448147058</v>
+        <v>2.734185079583738</v>
       </c>
       <c r="U80">
         <v>0.0959366166625341</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.556459051466745</v>
+        <v>1.536757038157039</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09591781005949482</v>
+        <v>0.09608756719322724</v>
       </c>
       <c r="C81">
-        <v>328.2521441178824</v>
+        <v>282.2945963905995</v>
       </c>
       <c r="D81">
-        <v>3316.718144117883</v>
+        <v>3311.4145963906</v>
       </c>
       <c r="E81">
-        <v>2241.766</v>
+        <v>2282.42</v>
       </c>
       <c r="F81">
-        <v>3211.666</v>
+        <v>3252.32</v>
       </c>
       <c r="G81">
         <v>223.2</v>
@@ -7929,28 +7929,28 @@
         <v>473.5</v>
       </c>
       <c r="M81">
-        <v>308.1163698900942</v>
+        <v>312.0165771038929</v>
       </c>
       <c r="N81">
-        <v>165.3836301099058</v>
+        <v>161.4834228961071</v>
       </c>
       <c r="O81">
-        <v>41.34590752747644</v>
+        <v>40.37085572402677</v>
       </c>
       <c r="P81">
-        <v>124.0377225824293</v>
+        <v>121.1125671720803</v>
       </c>
       <c r="Q81">
-        <v>256.6377225824293</v>
+        <v>253.7125671720803</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1860731651759208</v>
+        <v>0.1926279859785339</v>
       </c>
       <c r="T81">
-        <v>2.734185079583738</v>
+        <v>2.861950737508212</v>
       </c>
       <c r="U81">
         <v>0.0959366166625341</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.536757038157039</v>
+        <v>1.517547575180076</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09608756719322724</v>
+        <v>0.1330101660175697</v>
       </c>
       <c r="C82">
-        <v>282.2945963905995</v>
+        <v>-612.859602256533</v>
       </c>
       <c r="D82">
-        <v>3311.4145963906</v>
+        <v>2456.914397743467</v>
       </c>
       <c r="E82">
-        <v>2282.42</v>
+        <v>2323.074</v>
       </c>
       <c r="F82">
-        <v>3252.32</v>
+        <v>3292.974</v>
       </c>
       <c r="G82">
         <v>223.2</v>
@@ -8011,45 +8011,45 @@
         <v>473.5</v>
       </c>
       <c r="M82">
-        <v>312.0165771038929</v>
+        <v>502.9577075176916</v>
       </c>
       <c r="N82">
-        <v>161.4834228961071</v>
+        <v>-29.45770751769157</v>
       </c>
       <c r="O82">
-        <v>40.37085572402677</v>
+        <v>-7.364426879422894</v>
       </c>
       <c r="P82">
-        <v>121.1125671720803</v>
+        <v>-22.09328063826868</v>
       </c>
       <c r="Q82">
-        <v>253.7125671720803</v>
+        <v>110.5067193617313</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1926279859785339</v>
+        <v>0.2021641185176785</v>
       </c>
       <c r="T82">
-        <v>2.861950737508212</v>
+        <v>3.047827710290302</v>
       </c>
       <c r="U82">
-        <v>0.0959366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V82">
-        <v>0.25</v>
+        <v>0.2353577611609345</v>
       </c>
       <c r="W82">
-        <v>0.07195246249690057</v>
+        <v>0.1167888685175442</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.517547575180076</v>
+        <v>0.9414310446437379</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1330101660175697</v>
+        <v>0.134079532184195</v>
       </c>
       <c r="C83">
-        <v>-612.859602256533</v>
+        <v>-671.739507835227</v>
       </c>
       <c r="D83">
-        <v>2456.914397743467</v>
+        <v>2438.688492164773</v>
       </c>
       <c r="E83">
-        <v>2323.074</v>
+        <v>2363.728</v>
       </c>
       <c r="F83">
-        <v>3292.974</v>
+        <v>3333.628</v>
       </c>
       <c r="G83">
         <v>223.2</v>
@@ -8093,37 +8093,37 @@
         <v>473.5</v>
       </c>
       <c r="M83">
-        <v>502.9577075176916</v>
+        <v>509.1670619314903</v>
       </c>
       <c r="N83">
-        <v>-29.45770751769157</v>
+        <v>-35.66706193149025</v>
       </c>
       <c r="O83">
-        <v>-7.364426879422894</v>
+        <v>-8.916765482872563</v>
       </c>
       <c r="P83">
-        <v>-22.09328063826868</v>
+        <v>-26.75029644861769</v>
       </c>
       <c r="Q83">
-        <v>110.5067193617313</v>
+        <v>105.8497035513823</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2021641185176785</v>
+        <v>0.2108510139908829</v>
       </c>
       <c r="T83">
-        <v>3.047827710290302</v>
+        <v>3.217151471973096</v>
       </c>
       <c r="U83">
         <v>0.1527366166625341</v>
       </c>
       <c r="V83">
-        <v>0.2353577611609345</v>
+        <v>0.2324875445614109</v>
       </c>
       <c r="W83">
-        <v>0.1167888685175442</v>
+        <v>0.1172272556900441</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.9414310446437379</v>
+        <v>0.9299501782456436</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.134079532184195</v>
+        <v>0.1351488983508204</v>
       </c>
       <c r="C84">
-        <v>-671.739507835227</v>
+        <v>-730.3509974104177</v>
       </c>
       <c r="D84">
-        <v>2438.688492164773</v>
+        <v>2420.731002589583</v>
       </c>
       <c r="E84">
-        <v>2363.728</v>
+        <v>2404.382</v>
       </c>
       <c r="F84">
-        <v>3333.628</v>
+        <v>3374.282</v>
       </c>
       <c r="G84">
         <v>223.2</v>
@@ -8175,37 +8175,37 @@
         <v>473.5</v>
       </c>
       <c r="M84">
-        <v>509.1670619314903</v>
+        <v>515.3764163452889</v>
       </c>
       <c r="N84">
-        <v>-35.66706193149025</v>
+        <v>-41.87641634528893</v>
       </c>
       <c r="O84">
-        <v>-8.916765482872563</v>
+        <v>-10.46910408632223</v>
       </c>
       <c r="P84">
-        <v>-26.75029644861769</v>
+        <v>-31.4073122589667</v>
       </c>
       <c r="Q84">
-        <v>105.8497035513823</v>
+        <v>101.1926877410333</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2108510139908829</v>
+        <v>0.2205598971668172</v>
       </c>
       <c r="T84">
-        <v>3.217151471973096</v>
+        <v>3.406395676206808</v>
       </c>
       <c r="U84">
         <v>0.1527366166625341</v>
       </c>
       <c r="V84">
-        <v>0.2324875445614109</v>
+        <v>0.2296864898076589</v>
       </c>
       <c r="W84">
-        <v>0.1172272556900441</v>
+        <v>0.1176550793162187</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9299501782456436</v>
+        <v>0.9187459592306357</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1351488983508204</v>
+        <v>0.1362182645174458</v>
       </c>
       <c r="C85">
-        <v>-730.3509974104177</v>
+        <v>-788.6999571508345</v>
       </c>
       <c r="D85">
-        <v>2420.731002589583</v>
+        <v>2403.036042849166</v>
       </c>
       <c r="E85">
-        <v>2404.382</v>
+        <v>2445.036000000001</v>
       </c>
       <c r="F85">
-        <v>3374.282</v>
+        <v>3414.936000000001</v>
       </c>
       <c r="G85">
         <v>223.2</v>
@@ -8257,37 +8257,37 @@
         <v>473.5</v>
       </c>
       <c r="M85">
-        <v>515.3764163452889</v>
+        <v>521.5857707590876</v>
       </c>
       <c r="N85">
-        <v>-41.87641634528893</v>
+        <v>-48.08577075908761</v>
       </c>
       <c r="O85">
-        <v>-10.46910408632223</v>
+        <v>-12.0214426897719</v>
       </c>
       <c r="P85">
-        <v>-31.4073122589667</v>
+        <v>-36.06432806931571</v>
       </c>
       <c r="Q85">
-        <v>101.1926877410333</v>
+        <v>96.53567193068432</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2205598971668172</v>
+        <v>0.2314823907397434</v>
       </c>
       <c r="T85">
-        <v>3.406395676206808</v>
+        <v>3.619295405969735</v>
       </c>
       <c r="U85">
         <v>0.1527366166625341</v>
       </c>
       <c r="V85">
-        <v>0.2296864898076589</v>
+        <v>0.2269521268337582</v>
       </c>
       <c r="W85">
-        <v>0.1176550793162187</v>
+        <v>0.1180727166655796</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9187459592306357</v>
+        <v>0.9078085073350329</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1362182645174458</v>
+        <v>0.1372876306840711</v>
       </c>
       <c r="C86">
-        <v>-788.6999571508341</v>
+        <v>-846.7921023682329</v>
       </c>
       <c r="D86">
-        <v>2403.036042849166</v>
+        <v>2385.597897631767</v>
       </c>
       <c r="E86">
-        <v>2445.036</v>
+        <v>2485.69</v>
       </c>
       <c r="F86">
-        <v>3414.936</v>
+        <v>3455.59</v>
       </c>
       <c r="G86">
         <v>223.2</v>
@@ -8339,37 +8339,37 @@
         <v>473.5</v>
       </c>
       <c r="M86">
-        <v>521.5857707590876</v>
+        <v>527.7951251728863</v>
       </c>
       <c r="N86">
-        <v>-48.08577075908761</v>
+        <v>-54.29512517288629</v>
       </c>
       <c r="O86">
-        <v>-12.0214426897719</v>
+        <v>-13.57378129322157</v>
       </c>
       <c r="P86">
-        <v>-36.06432806931571</v>
+        <v>-40.72134387966472</v>
       </c>
       <c r="Q86">
-        <v>96.53567193068432</v>
+        <v>91.87865612033531</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2314823907397432</v>
+        <v>0.2438612167890594</v>
       </c>
       <c r="T86">
-        <v>3.619295405969733</v>
+        <v>3.860581766367715</v>
       </c>
       <c r="U86">
         <v>0.1527366166625341</v>
       </c>
       <c r="V86">
-        <v>0.2269521268337582</v>
+        <v>0.2242821018121846</v>
       </c>
       <c r="W86">
-        <v>0.1180727166655796</v>
+        <v>0.118480527253779</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9078085073350329</v>
+        <v>0.8971284072487384</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1372876306840711</v>
+        <v>0.1383569968506964</v>
       </c>
       <c r="C87">
-        <v>-846.7921023682329</v>
+        <v>-904.6329836720365</v>
       </c>
       <c r="D87">
-        <v>2385.597897631767</v>
+        <v>2368.411016327964</v>
       </c>
       <c r="E87">
-        <v>2485.69</v>
+        <v>2526.344</v>
       </c>
       <c r="F87">
-        <v>3455.59</v>
+        <v>3496.244</v>
       </c>
       <c r="G87">
         <v>223.2</v>
@@ -8421,37 +8421,37 @@
         <v>473.5</v>
       </c>
       <c r="M87">
-        <v>527.7951251728863</v>
+        <v>534.0044795866849</v>
       </c>
       <c r="N87">
-        <v>-54.29512517288629</v>
+        <v>-60.50447958668485</v>
       </c>
       <c r="O87">
-        <v>-13.57378129322157</v>
+        <v>-15.12611989667121</v>
       </c>
       <c r="P87">
-        <v>-40.72134387966472</v>
+        <v>-45.37835969001364</v>
       </c>
       <c r="Q87">
-        <v>91.87865612033531</v>
+        <v>87.22164030998638</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2438612167890594</v>
+        <v>0.2580084465597065</v>
       </c>
       <c r="T87">
-        <v>3.860581766367715</v>
+        <v>4.136337606822551</v>
       </c>
       <c r="U87">
         <v>0.1527366166625341</v>
       </c>
       <c r="V87">
-        <v>0.2242821018121846</v>
+        <v>0.2216741703957639</v>
       </c>
       <c r="W87">
-        <v>0.118480527253779</v>
+        <v>0.118878853874811</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8971284072487384</v>
+        <v>0.8866966815830556</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1383569968506964</v>
+        <v>0.1394263630173218</v>
       </c>
       <c r="C88">
-        <v>-904.6329836720365</v>
+        <v>-962.2279928598364</v>
       </c>
       <c r="D88">
-        <v>2368.411016327964</v>
+        <v>2351.470007140164</v>
       </c>
       <c r="E88">
-        <v>2526.344</v>
+        <v>2566.998</v>
       </c>
       <c r="F88">
-        <v>3496.244</v>
+        <v>3536.898</v>
       </c>
       <c r="G88">
         <v>223.2</v>
@@ -8503,37 +8503,37 @@
         <v>473.5</v>
       </c>
       <c r="M88">
-        <v>534.0044795866849</v>
+        <v>540.2138340004835</v>
       </c>
       <c r="N88">
-        <v>-60.50447958668485</v>
+        <v>-66.71383400048353</v>
       </c>
       <c r="O88">
-        <v>-15.12611989667121</v>
+        <v>-16.67845850012088</v>
       </c>
       <c r="P88">
-        <v>-45.37835969001364</v>
+        <v>-50.03537550036265</v>
       </c>
       <c r="Q88">
-        <v>87.22164030998638</v>
+        <v>82.56462449963738</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2580084465597065</v>
+        <v>0.2743321732181455</v>
       </c>
       <c r="T88">
-        <v>4.136337606822551</v>
+        <v>4.454517422731978</v>
       </c>
       <c r="U88">
         <v>0.1527366166625341</v>
       </c>
       <c r="V88">
-        <v>0.2216741703957639</v>
+        <v>0.2191261914256976</v>
       </c>
       <c r="W88">
-        <v>0.118878853874811</v>
+        <v>0.1192680235620262</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8866966815830556</v>
+        <v>0.8765047657027906</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1394263630173218</v>
+        <v>0.1404957291839471</v>
       </c>
       <c r="C89">
-        <v>-962.2279928598364</v>
+        <v>-1019.582368556871</v>
       </c>
       <c r="D89">
-        <v>2351.470007140164</v>
+        <v>2334.76963144313</v>
       </c>
       <c r="E89">
-        <v>2566.998</v>
+        <v>2607.652</v>
       </c>
       <c r="F89">
-        <v>3536.898</v>
+        <v>3577.552</v>
       </c>
       <c r="G89">
         <v>223.2</v>
@@ -8585,37 +8585,37 @@
         <v>473.5</v>
       </c>
       <c r="M89">
-        <v>540.2138340004835</v>
+        <v>546.4231884142822</v>
       </c>
       <c r="N89">
-        <v>-66.71383400048353</v>
+        <v>-72.92318841428221</v>
       </c>
       <c r="O89">
-        <v>-16.67845850012088</v>
+        <v>-18.23079710357055</v>
       </c>
       <c r="P89">
-        <v>-50.03537550036265</v>
+        <v>-54.69239131071166</v>
       </c>
       <c r="Q89">
-        <v>82.56462449963738</v>
+        <v>77.90760868928837</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2743321732181455</v>
+        <v>0.2933765209863243</v>
       </c>
       <c r="T89">
-        <v>4.454517422731978</v>
+        <v>4.825727207959644</v>
       </c>
       <c r="U89">
         <v>0.1527366166625341</v>
       </c>
       <c r="V89">
-        <v>0.2191261914256976</v>
+        <v>0.2166361210685874</v>
       </c>
       <c r="W89">
-        <v>0.1192680235620262</v>
+        <v>0.1196483484836229</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8765047657027906</v>
+        <v>0.8665444842743497</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1404957291839471</v>
+        <v>0.1415650953505724</v>
       </c>
       <c r="C90">
-        <v>-1019.582368556871</v>
+        <v>-1076.701201616904</v>
       </c>
       <c r="D90">
-        <v>2334.76963144313</v>
+        <v>2318.304798383097</v>
       </c>
       <c r="E90">
-        <v>2607.652</v>
+        <v>2648.306</v>
       </c>
       <c r="F90">
-        <v>3577.552</v>
+        <v>3618.206</v>
       </c>
       <c r="G90">
         <v>223.2</v>
@@ -8667,37 +8667,37 @@
         <v>473.5</v>
       </c>
       <c r="M90">
-        <v>546.4231884142822</v>
+        <v>552.6325428280809</v>
       </c>
       <c r="N90">
-        <v>-72.92318841428221</v>
+        <v>-79.13254282808089</v>
       </c>
       <c r="O90">
-        <v>-18.23079710357055</v>
+        <v>-19.78313570702022</v>
       </c>
       <c r="P90">
-        <v>-54.69239131071166</v>
+        <v>-59.34940712106066</v>
       </c>
       <c r="Q90">
-        <v>77.90760868928837</v>
+        <v>73.25059287893936</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2933765209863243</v>
+        <v>0.3158834774396265</v>
       </c>
       <c r="T90">
-        <v>4.825727207959644</v>
+        <v>5.264429681410521</v>
       </c>
       <c r="U90">
         <v>0.1527366166625341</v>
       </c>
       <c r="V90">
-        <v>0.2166361210685874</v>
+        <v>0.2142020073487156</v>
       </c>
       <c r="W90">
-        <v>0.1196483484836229</v>
+        <v>0.120020126777768</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8665444842743497</v>
+        <v>0.8568080293948626</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1415650953505724</v>
+        <v>0.1426344615171978</v>
       </c>
       <c r="C91">
-        <v>-1076.701201616904</v>
+        <v>-1133.589440296165</v>
       </c>
       <c r="D91">
-        <v>2318.304798383097</v>
+        <v>2302.070559703835</v>
       </c>
       <c r="E91">
-        <v>2648.306</v>
+        <v>2688.96</v>
       </c>
       <c r="F91">
-        <v>3618.206</v>
+        <v>3658.86</v>
       </c>
       <c r="G91">
         <v>223.2</v>
@@ -8749,37 +8749,37 @@
         <v>473.5</v>
       </c>
       <c r="M91">
-        <v>552.6325428280809</v>
+        <v>558.8418972418796</v>
       </c>
       <c r="N91">
-        <v>-79.13254282808089</v>
+        <v>-85.34189724187956</v>
       </c>
       <c r="O91">
-        <v>-19.78313570702022</v>
+        <v>-21.33547431046989</v>
       </c>
       <c r="P91">
-        <v>-59.34940712106066</v>
+        <v>-64.00642293140967</v>
       </c>
       <c r="Q91">
-        <v>73.25059287893936</v>
+        <v>68.59357706859035</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3158834774396265</v>
+        <v>0.3428918251835892</v>
       </c>
       <c r="T91">
-        <v>5.264429681410521</v>
+        <v>5.790872649551573</v>
       </c>
       <c r="U91">
         <v>0.1527366166625341</v>
       </c>
       <c r="V91">
-        <v>0.2142020073487156</v>
+        <v>0.211821985044841</v>
       </c>
       <c r="W91">
-        <v>0.120020126777768</v>
+        <v>0.1203836433320432</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8568080293948626</v>
+        <v>0.8472879401793642</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1426344615171978</v>
+        <v>0.1437038276838231</v>
       </c>
       <c r="C92">
-        <v>-1133.589440296165</v>
+        <v>-1190.251895211427</v>
       </c>
       <c r="D92">
-        <v>2302.070559703835</v>
+        <v>2286.062104788573</v>
       </c>
       <c r="E92">
-        <v>2688.96</v>
+        <v>2729.614</v>
       </c>
       <c r="F92">
-        <v>3658.86</v>
+        <v>3699.514</v>
       </c>
       <c r="G92">
         <v>223.2</v>
@@ -8831,37 +8831,37 @@
         <v>473.5</v>
       </c>
       <c r="M92">
-        <v>558.8418972418796</v>
+        <v>565.0512516556782</v>
       </c>
       <c r="N92">
-        <v>-85.34189724187956</v>
+        <v>-91.55125165567824</v>
       </c>
       <c r="O92">
-        <v>-21.33547431046989</v>
+        <v>-22.88781291391956</v>
       </c>
       <c r="P92">
-        <v>-64.00642293140967</v>
+        <v>-68.66343874175868</v>
       </c>
       <c r="Q92">
-        <v>68.59357706859035</v>
+        <v>63.93656125824134</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3428918251835892</v>
+        <v>0.3759020279817658</v>
       </c>
       <c r="T92">
-        <v>5.790872649551573</v>
+        <v>6.434302943946193</v>
       </c>
       <c r="U92">
         <v>0.1527366166625341</v>
       </c>
       <c r="V92">
-        <v>0.211821985044841</v>
+        <v>0.2094942709234691</v>
       </c>
       <c r="W92">
-        <v>0.1203836433320432</v>
+        <v>0.1207391705114991</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8472879401793642</v>
+        <v>0.8379770836938766</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1437038276838231</v>
+        <v>0.1447731938504485</v>
       </c>
       <c r="C93">
-        <v>-1190.251895211427</v>
+        <v>-1246.693244092636</v>
       </c>
       <c r="D93">
-        <v>2286.062104788573</v>
+        <v>2270.274755907365</v>
       </c>
       <c r="E93">
-        <v>2729.614</v>
+        <v>2770.268</v>
       </c>
       <c r="F93">
-        <v>3699.514</v>
+        <v>3740.168</v>
       </c>
       <c r="G93">
         <v>223.2</v>
@@ -8913,37 +8913,37 @@
         <v>473.5</v>
       </c>
       <c r="M93">
-        <v>565.0512516556782</v>
+        <v>571.2606060694769</v>
       </c>
       <c r="N93">
-        <v>-91.55125165567824</v>
+        <v>-97.76060606947692</v>
       </c>
       <c r="O93">
-        <v>-22.88781291391956</v>
+        <v>-24.44015151736923</v>
       </c>
       <c r="P93">
-        <v>-68.66343874175868</v>
+        <v>-73.32045455210769</v>
       </c>
       <c r="Q93">
-        <v>63.93656125824134</v>
+        <v>59.27954544789233</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3759020279817658</v>
+        <v>0.4171647814794867</v>
       </c>
       <c r="T93">
-        <v>6.434302943946193</v>
+        <v>7.23859081193947</v>
       </c>
       <c r="U93">
         <v>0.1527366166625341</v>
       </c>
       <c r="V93">
-        <v>0.2094942709234691</v>
+        <v>0.2072171592829966</v>
       </c>
       <c r="W93">
-        <v>0.1207391705114991</v>
+        <v>0.1210869688392278</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8379770836938766</v>
+        <v>0.8288686371319866</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1447731938504485</v>
+        <v>0.1458425600170738</v>
       </c>
       <c r="C94">
-        <v>-1246.693244092636</v>
+        <v>-1302.918036339959</v>
       </c>
       <c r="D94">
-        <v>2270.274755907365</v>
+        <v>2254.703963660041</v>
       </c>
       <c r="E94">
-        <v>2770.268</v>
+        <v>2810.922</v>
       </c>
       <c r="F94">
-        <v>3740.168</v>
+        <v>3780.822</v>
       </c>
       <c r="G94">
         <v>223.2</v>
@@ -8995,37 +8995,37 @@
         <v>473.5</v>
       </c>
       <c r="M94">
-        <v>571.2606060694769</v>
+        <v>577.4699604832755</v>
       </c>
       <c r="N94">
-        <v>-97.76060606947692</v>
+        <v>-103.9699604832755</v>
       </c>
       <c r="O94">
-        <v>-24.44015151736923</v>
+        <v>-25.99249012081887</v>
       </c>
       <c r="P94">
-        <v>-73.32045455210769</v>
+        <v>-77.97747036245661</v>
       </c>
       <c r="Q94">
-        <v>59.27954544789233</v>
+        <v>54.62252963754341</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4171647814794867</v>
+        <v>0.4702168931194133</v>
       </c>
       <c r="T94">
-        <v>7.23859081193947</v>
+        <v>8.272675213645108</v>
       </c>
       <c r="U94">
         <v>0.1527366166625341</v>
       </c>
       <c r="V94">
-        <v>0.2072171592829966</v>
+        <v>0.20498901778533</v>
       </c>
       <c r="W94">
-        <v>0.1210869688392278</v>
+        <v>0.1214272876330268</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8288686371319866</v>
+        <v>0.8199560711413202</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1458425600170738</v>
+        <v>0.1469119261836991</v>
       </c>
       <c r="C95">
-        <v>-1302.918036339959</v>
+        <v>-1358.9306973946</v>
       </c>
       <c r="D95">
-        <v>2254.703963660041</v>
+        <v>2239.3453026054</v>
       </c>
       <c r="E95">
-        <v>2810.922</v>
+        <v>2851.576</v>
       </c>
       <c r="F95">
-        <v>3780.822</v>
+        <v>3821.476</v>
       </c>
       <c r="G95">
         <v>223.2</v>
@@ -9077,37 +9077,37 @@
         <v>473.5</v>
       </c>
       <c r="M95">
-        <v>577.4699604832755</v>
+        <v>583.6793148970742</v>
       </c>
       <c r="N95">
-        <v>-103.9699604832755</v>
+        <v>-110.1793148970742</v>
       </c>
       <c r="O95">
-        <v>-25.99249012081887</v>
+        <v>-27.54482872426854</v>
       </c>
       <c r="P95">
-        <v>-77.97747036245661</v>
+        <v>-82.63448617280562</v>
       </c>
       <c r="Q95">
-        <v>54.62252963754341</v>
+        <v>49.9655138271944</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4702168931194133</v>
+        <v>0.540953041972649</v>
       </c>
       <c r="T95">
-        <v>8.272675213645108</v>
+        <v>9.651454415919297</v>
       </c>
       <c r="U95">
         <v>0.1527366166625341</v>
       </c>
       <c r="V95">
-        <v>0.20498901778533</v>
+        <v>0.2028082835535712</v>
       </c>
       <c r="W95">
-        <v>0.1214272876330268</v>
+        <v>0.1217603656014258</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8199560711413202</v>
+        <v>0.8112331342142849</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1469119261836991</v>
+        <v>0.1479812923503245</v>
       </c>
       <c r="C96">
-        <v>-1358.9306973946</v>
+        <v>-1414.735532932164</v>
       </c>
       <c r="D96">
-        <v>2239.3453026054</v>
+        <v>2224.194467067837</v>
       </c>
       <c r="E96">
-        <v>2851.576</v>
+        <v>2892.23</v>
       </c>
       <c r="F96">
-        <v>3821.476</v>
+        <v>3862.130000000001</v>
       </c>
       <c r="G96">
         <v>223.2</v>
@@ -9159,37 +9159,37 @@
         <v>473.5</v>
       </c>
       <c r="M96">
-        <v>583.6793148970742</v>
+        <v>589.888669310873</v>
       </c>
       <c r="N96">
-        <v>-110.1793148970742</v>
+        <v>-116.388669310873</v>
       </c>
       <c r="O96">
-        <v>-27.54482872426854</v>
+        <v>-29.09716732771824</v>
       </c>
       <c r="P96">
-        <v>-82.63448617280562</v>
+        <v>-87.29150198315472</v>
       </c>
       <c r="Q96">
-        <v>49.9655138271944</v>
+        <v>45.30849801684531</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.540953041972649</v>
+        <v>0.6399836503671791</v>
       </c>
       <c r="T96">
-        <v>9.651454415919297</v>
+        <v>11.58174529910316</v>
       </c>
       <c r="U96">
         <v>0.1527366166625341</v>
       </c>
       <c r="V96">
-        <v>0.2028082835535712</v>
+        <v>0.2006734595161652</v>
       </c>
       <c r="W96">
-        <v>0.1217603656014258</v>
+        <v>0.122086431402069</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8112331342142849</v>
+        <v>0.8026938380646607</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1479812923503245</v>
+        <v>0.2027185009225149</v>
       </c>
       <c r="C97">
-        <v>-1414.735532932164</v>
+        <v>-2027.523441011835</v>
       </c>
       <c r="D97">
-        <v>2224.194467067837</v>
+        <v>1652.060558988165</v>
       </c>
       <c r="E97">
-        <v>2892.23</v>
+        <v>2932.884</v>
       </c>
       <c r="F97">
-        <v>3862.130000000001</v>
+        <v>3902.784000000001</v>
       </c>
       <c r="G97">
         <v>223.2</v>
@@ -9241,45 +9241,45 @@
         <v>473.5</v>
       </c>
       <c r="M97">
-        <v>589.888669310873</v>
+        <v>806.8483597246716</v>
       </c>
       <c r="N97">
-        <v>-116.388669310873</v>
+        <v>-333.3483597246716</v>
       </c>
       <c r="O97">
-        <v>-29.09716732771824</v>
+        <v>-83.3370899311679</v>
       </c>
       <c r="P97">
-        <v>-87.29150198315472</v>
+        <v>-250.0112697935037</v>
       </c>
       <c r="Q97">
-        <v>45.30849801684531</v>
+        <v>-117.4112697935037</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6399836503671791</v>
+        <v>0.8342256230981006</v>
       </c>
       <c r="T97">
-        <v>11.58174529910316</v>
+        <v>15.36788289002254</v>
       </c>
       <c r="U97">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.2006734595161652</v>
+        <v>0.1467128222710823</v>
       </c>
       <c r="W97">
-        <v>0.122086431402069</v>
+        <v>0.1764057041651989</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.8026938380646607</v>
+        <v>0.5868512890843292</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2027185009225149</v>
+        <v>0.2043278670891402</v>
       </c>
       <c r="C98">
-        <v>-2027.523441011835</v>
+        <v>-2080.578274660985</v>
       </c>
       <c r="D98">
-        <v>1652.060558988165</v>
+        <v>1639.659725339015</v>
       </c>
       <c r="E98">
-        <v>2932.884</v>
+        <v>2973.538</v>
       </c>
       <c r="F98">
-        <v>3902.784</v>
+        <v>3943.438</v>
       </c>
       <c r="G98">
         <v>223.2</v>
@@ -9323,37 +9323,37 @@
         <v>473.5</v>
       </c>
       <c r="M98">
-        <v>806.8483597246715</v>
+        <v>815.2530301384702</v>
       </c>
       <c r="N98">
-        <v>-333.3483597246715</v>
+        <v>-341.7530301384702</v>
       </c>
       <c r="O98">
-        <v>-83.33708993116787</v>
+        <v>-85.43825753461755</v>
       </c>
       <c r="P98">
-        <v>-250.0112697935036</v>
+        <v>-256.3147726038526</v>
       </c>
       <c r="Q98">
-        <v>-117.4112697935036</v>
+        <v>-123.7147726038526</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8342256230980984</v>
+        <v>1.097034164130798</v>
       </c>
       <c r="T98">
-        <v>15.3678828900225</v>
+        <v>20.49051052003</v>
       </c>
       <c r="U98">
         <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.1467128222710823</v>
+        <v>0.1452003189487</v>
       </c>
       <c r="W98">
-        <v>0.1764057041651989</v>
+        <v>0.176718393984759</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5868512890843292</v>
+        <v>0.5808012757948</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2043278670891402</v>
+        <v>0.2059372332557655</v>
       </c>
       <c r="C99">
-        <v>-2080.578274660985</v>
+        <v>-2133.448327003854</v>
       </c>
       <c r="D99">
-        <v>1639.659725339015</v>
+        <v>1627.443672996147</v>
       </c>
       <c r="E99">
-        <v>2973.538</v>
+        <v>3014.192</v>
       </c>
       <c r="F99">
-        <v>3943.438</v>
+        <v>3984.092</v>
       </c>
       <c r="G99">
         <v>223.2</v>
@@ -9405,37 +9405,37 @@
         <v>473.5</v>
       </c>
       <c r="M99">
-        <v>815.2530301384702</v>
+        <v>823.6577005522688</v>
       </c>
       <c r="N99">
-        <v>-341.7530301384702</v>
+        <v>-350.1577005522688</v>
       </c>
       <c r="O99">
-        <v>-85.43825753461755</v>
+        <v>-87.5394251380672</v>
       </c>
       <c r="P99">
-        <v>-256.3147726038526</v>
+        <v>-262.6182754142016</v>
       </c>
       <c r="Q99">
-        <v>-123.7147726038526</v>
+        <v>-130.0182754142016</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.097034164130798</v>
+        <v>1.622651246196197</v>
       </c>
       <c r="T99">
-        <v>20.49051052003</v>
+        <v>30.735765780045</v>
       </c>
       <c r="U99">
         <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.1452003189487</v>
+        <v>0.1437186830410602</v>
       </c>
       <c r="W99">
-        <v>0.176718393984759</v>
+        <v>0.1770247023794302</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5808012757948</v>
+        <v>0.5748747321642409</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2059372332557655</v>
+        <v>0.2075465994223909</v>
       </c>
       <c r="C100">
-        <v>-2133.448327003854</v>
+        <v>-2186.137697558345</v>
       </c>
       <c r="D100">
-        <v>1627.443672996147</v>
+        <v>1615.408302441655</v>
       </c>
       <c r="E100">
-        <v>3014.192</v>
+        <v>3054.846</v>
       </c>
       <c r="F100">
-        <v>3984.092</v>
+        <v>4024.746</v>
       </c>
       <c r="G100">
         <v>223.2</v>
@@ -9487,37 +9487,37 @@
         <v>473.5</v>
       </c>
       <c r="M100">
-        <v>823.6577005522688</v>
+        <v>832.0623709660674</v>
       </c>
       <c r="N100">
-        <v>-350.1577005522688</v>
+        <v>-358.5623709660674</v>
       </c>
       <c r="O100">
-        <v>-87.5394251380672</v>
+        <v>-89.64059274151685</v>
       </c>
       <c r="P100">
-        <v>-262.6182754142016</v>
+        <v>-268.9217782245506</v>
       </c>
       <c r="Q100">
-        <v>-130.0182754142016</v>
+        <v>-136.3217782245505</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.622651246196197</v>
+        <v>3.199502492392394</v>
       </c>
       <c r="T100">
-        <v>30.735765780045</v>
+        <v>61.47153156008999</v>
       </c>
       <c r="U100">
         <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.1437186830410602</v>
+        <v>0.1422669791719586</v>
       </c>
       <c r="W100">
-        <v>0.1770247023794302</v>
+        <v>0.1773248227257242</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5748747321642409</v>
+        <v>0.5690679166878344</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2075465994223909</v>
-      </c>
-      <c r="C101">
-        <v>-2186.137697558345</v>
-      </c>
-      <c r="D101">
-        <v>1615.408302441655</v>
-      </c>
-      <c r="E101">
-        <v>3054.846</v>
-      </c>
-      <c r="F101">
-        <v>4024.746</v>
-      </c>
-      <c r="G101">
-        <v>223.2</v>
-      </c>
-      <c r="H101">
-        <v>3095.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>606.1</v>
-      </c>
-      <c r="K101">
-        <v>132.6</v>
-      </c>
-      <c r="L101">
-        <v>473.5</v>
-      </c>
-      <c r="M101">
-        <v>832.0623709660674</v>
-      </c>
-      <c r="N101">
-        <v>-358.5623709660674</v>
-      </c>
-      <c r="O101">
-        <v>-89.64059274151685</v>
-      </c>
-      <c r="P101">
-        <v>-268.9217782245506</v>
-      </c>
-      <c r="Q101">
-        <v>-136.3217782245505</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.199502492392394</v>
-      </c>
-      <c r="T101">
-        <v>61.47153156008999</v>
-      </c>
-      <c r="U101">
-        <v>0.2067366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.1422669791719586</v>
-      </c>
-      <c r="W101">
-        <v>0.1773248227257242</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5690679166878344</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
